--- a/Results/Ammonia/ammonia particulate matter results.xlsx
+++ b/Results/Ammonia/ammonia particulate matter results.xlsx
@@ -515,37 +515,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.623970093307353e-08</v>
+        <v>7.62397009330728e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>7.806729315579941e-08</v>
+        <v>7.806729315579943e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>2.000431774040074e-07</v>
+        <v>2.000431774040072e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>7.949610666845081e-08</v>
+        <v>7.949610666845062e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>7.45117648022478e-08</v>
+        <v>7.451176480224772e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.332192704915654e-07</v>
+        <v>1.332192704915652e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>9.007993232100282e-08</v>
+        <v>9.007993232100284e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>7.578144385735906e-08</v>
+        <v>7.578144385735895e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>9.043526604826598e-08</v>
+        <v>9.043526604826603e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>9.293455892011425e-08</v>
+        <v>9.293455892011437e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>8.793000105745792e-08</v>
+        <v>8.793000105745795e-08</v>
       </c>
     </row>
     <row r="3">
@@ -555,37 +555,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.367963564936974e-08</v>
+        <v>8.36796356493705e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>8.542210657602617e-08</v>
+        <v>8.542210657602618e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>2.260792794038349e-07</v>
+        <v>2.26079279403835e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>8.686324034066234e-08</v>
+        <v>8.68632403406623e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>8.187889847445929e-08</v>
+        <v>8.187889847445935e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.492179439239121e-07</v>
+        <v>1.492179439239119e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>9.961485646252618e-08</v>
+        <v>9.96148564625263e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>8.308979778268505e-08</v>
+        <v>8.308979778268506e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>9.86321406771385e-08</v>
+        <v>9.863214067713833e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.009992461564341e-07</v>
+        <v>1.009992461564336e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>9.712888318649947e-08</v>
+        <v>9.712888318649951e-08</v>
       </c>
     </row>
     <row r="4">
@@ -595,37 +595,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.04939637534521e-07</v>
+        <v>5.528753432793689e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>9.741141136914647e-08</v>
+        <v>5.372514843404894e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>1.785355582981878e-07</v>
+        <v>1.288834550916042e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>9.862752223647862e-08</v>
+        <v>5.393919416748255e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>9.862752223647863e-08</v>
+        <v>5.393919416748256e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>1.383712972288968e-07</v>
+        <v>8.908198472540869e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>1.131783213201682e-07</v>
+        <v>6.352621811358449e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>1.017148475146596e-07</v>
+        <v>5.447492767089682e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>1.079352919067029e-07</v>
+        <v>5.828318870011919e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>1.074121490074178e-07</v>
+        <v>5.776004580083403e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>1.119038582075448e-07</v>
+        <v>6.225175500096104e-08</v>
       </c>
     </row>
     <row r="5">
@@ -635,37 +635,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.813214722760873e-07</v>
+        <v>1.215307368834994e-07</v>
       </c>
       <c r="C5" t="n">
-        <v>4.380611579623433e-07</v>
+        <v>1.136795035095828e-07</v>
       </c>
       <c r="D5" t="n">
-        <v>8.169819587444033e-06</v>
+        <v>1.535349436600186e-06</v>
       </c>
       <c r="E5" t="n">
-        <v>4.38061170367613e-07</v>
+        <v>1.136795159148534e-07</v>
       </c>
       <c r="F5" t="n">
-        <v>4.380611703676129e-07</v>
+        <v>1.136795159148534e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>4.114853355279864e-06</v>
+        <v>7.889428231501097e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>1.50842070395433e-06</v>
+        <v>3.090888761265902e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>4.380519036897111e-07</v>
+        <v>1.1367024923695e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>8.377460800078064e-07</v>
+        <v>1.86729886709911e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>7.452202950190999e-07</v>
+        <v>1.700142788906269e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>1.40117697021007e-06</v>
+        <v>2.590239996891048e-07</v>
       </c>
     </row>
     <row r="6">
@@ -675,37 +675,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.626421344341172e-07</v>
+        <v>5.472347090684172e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>9.290027247997641e-08</v>
+        <v>5.29311879938572e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.864105337446413e-07</v>
+        <v>1.302694159776215e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>9.226321520345347e-08</v>
+        <v>5.281907613573965e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>9.801323103366328e-08</v>
+        <v>5.383107891637288e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.960737941284929e-07</v>
+        <v>9.923762412470819e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.765215962846436e-07</v>
+        <v>7.467463444692336e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.594173444142555e-07</v>
+        <v>5.391086424980153e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.063564151846029e-07</v>
+        <v>5.800530639853543e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.005208676318405e-07</v>
+        <v>5.654718028530441e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.090145751008385e-07</v>
+        <v>6.174324117693617e-08</v>
       </c>
     </row>
     <row r="7">
@@ -715,37 +715,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.525692250232262e-07</v>
+        <v>6.367034168052626e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.493536892759979e-07</v>
+        <v>6.286698929611874e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>2.261568773771185e-07</v>
+        <v>1.372648072040807e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>1.492578313093207e-07</v>
+        <v>6.285012851601792e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.492578313093207e-07</v>
+        <v>6.285012851601792e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.860008847176023e-07</v>
+        <v>9.74647920779977e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.608079088088738e-07</v>
+        <v>7.190902546617354e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.49344435003365e-07</v>
+        <v>6.285773502348581e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.555648793954085e-07</v>
+        <v>6.666599605270825e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.550417364961231e-07</v>
+        <v>6.614285315342306e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.595334456962502e-07</v>
+        <v>7.063456235355008e-08</v>
       </c>
     </row>
     <row r="8">
@@ -755,37 +755,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.203695250157319e-07</v>
+        <v>7.560319441454777e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>3.109183197842933e-07</v>
+        <v>9.130236411149868e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>4.072478868189414e-07</v>
+        <v>1.691368246931396e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>2.852616682852708e-07</v>
+        <v>8.678680369408171e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>2.200759086585924e-07</v>
+        <v>7.531411006195238e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>3.476280201881038e-07</v>
+        <v>1.259111677666664e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>3.224350442793647e-07</v>
+        <v>1.003554011548404e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>3.109715704738666e-07</v>
+        <v>9.13041107121544e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>3.172104545194442e-07</v>
+        <v>9.511561712038125e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>2.21099154846585e-07</v>
+        <v>7.776895872010699e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>4.191705564935458e-07</v>
+        <v>1.16330693606265e-07</v>
       </c>
     </row>
     <row r="9">
@@ -795,37 +795,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.403924368854866e-07</v>
+        <v>9.672722678916206e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>4.112081408928381e-07</v>
+        <v>1.089533725309588e-07</v>
       </c>
       <c r="D9" t="n">
-        <v>4.880197671603146e-07</v>
+        <v>1.833526755561912e-07</v>
       </c>
       <c r="E9" t="n">
-        <v>4.966388006205924e-07</v>
+        <v>1.239891787835134e-07</v>
       </c>
       <c r="F9" t="n">
-        <v>4.112081636222544e-07</v>
+        <v>1.089533867532789e-07</v>
       </c>
       <c r="G9" t="n">
-        <v>4.478553363344424e-07</v>
+        <v>1.435511753128376e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>4.226623604257144e-07</v>
+        <v>1.179954087010134e-07</v>
       </c>
       <c r="I9" t="n">
-        <v>4.111988866202057e-07</v>
+        <v>1.089441182583259e-07</v>
       </c>
       <c r="J9" t="n">
-        <v>4.174193310122487e-07</v>
+        <v>1.127523792875482e-07</v>
       </c>
       <c r="K9" t="n">
-        <v>3.236775987351355e-07</v>
+        <v>1.046799065693687e-07</v>
       </c>
       <c r="L9" t="n">
-        <v>4.213878973130904e-07</v>
+        <v>1.167209455883901e-07</v>
       </c>
     </row>
   </sheetData>
@@ -911,34 +911,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.872167177202902e-08</v>
+        <v>6.8721671772029e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>7.692911791871417e-08</v>
+        <v>7.692911791871412e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>7.378459226593884e-08</v>
+        <v>7.378459226593882e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>7.812163222577264e-08</v>
+        <v>7.812163222577263e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>7.38733127558611e-08</v>
+        <v>7.387331275586106e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>7.219712239428984e-08</v>
+        <v>7.219712239428987e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>6.973702919483806e-08</v>
+        <v>6.973702919483804e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>7.42158349699056e-08</v>
+        <v>7.421583496990557e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>8.786849485596097e-08</v>
+        <v>8.786849485596093e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>8.292192099979112e-08</v>
+        <v>8.292192099979111e-08</v>
       </c>
       <c r="L2" t="n">
         <v>6.85878519998247e-08</v>
@@ -951,37 +951,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.522458311714517e-08</v>
+        <v>7.522458311714516e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>8.424706219098117e-08</v>
+        <v>8.424706219098114e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>8.104799046596218e-08</v>
+        <v>8.104799046596217e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>8.544765088823288e-08</v>
+        <v>8.544765088823283e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>8.119933141832132e-08</v>
+        <v>8.119933141832127e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>7.922207127017266e-08</v>
+        <v>7.922207127017261e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>7.640547163864365e-08</v>
+        <v>7.640547163864363e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>8.152254916338755e-08</v>
+        <v>8.152254916338751e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>9.595052453560107e-08</v>
+        <v>9.595052453560099e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>8.963302055146184e-08</v>
+        <v>8.963302055146181e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>7.507080746789684e-08</v>
+        <v>7.507080746789682e-08</v>
       </c>
     </row>
     <row r="4">
@@ -991,37 +991,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8.983717141937796e-08</v>
+        <v>4.927726322238817e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>9.093746750851246e-08</v>
+        <v>5.215510816109324e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>9.284686311886759e-08</v>
+        <v>5.228695492187779e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>9.169541792889297e-08</v>
+        <v>5.228850905368915e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>9.169541792889301e-08</v>
+        <v>5.228850905368917e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>9.160916180389499e-08</v>
+        <v>5.129152422748499e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>9.044233393790967e-08</v>
+        <v>4.988242574091987e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>9.110446191465268e-08</v>
+        <v>5.218360842168721e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>9.608666713815456e-08</v>
+        <v>5.552675894116473e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>9.066109403310331e-08</v>
+        <v>5.010118583611352e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>8.976032251621037e-08</v>
+        <v>4.920041431922052e-08</v>
       </c>
     </row>
     <row r="5">
@@ -1031,37 +1031,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.096405249311994e-07</v>
+        <v>7.036265332621533e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>4.709156163069261e-07</v>
+        <v>1.190312619872387e-07</v>
       </c>
       <c r="D5" t="n">
-        <v>4.625708111995394e-07</v>
+        <v>1.173583694314798e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>4.709156182721343e-07</v>
+        <v>1.190312639524471e-07</v>
       </c>
       <c r="F5" t="n">
-        <v>4.709156182721341e-07</v>
+        <v>1.190312639524471e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>3.942745731804911e-07</v>
+        <v>1.045606363411223e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>2.860458814629495e-07</v>
+        <v>8.430864991878471e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>4.709145352939082e-07</v>
+        <v>1.190301809742211e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>8.152951472339307e-07</v>
+        <v>1.821074507521306e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>2.741546902647184e-07</v>
+        <v>8.23960585978846e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>2.543064751799868e-07</v>
+        <v>7.292281017589376e-08</v>
       </c>
     </row>
     <row r="6">
@@ -1071,37 +1071,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.186739934177651e-07</v>
+        <v>5.435254386660332e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>8.350720855450759e-08</v>
+        <v>5.084738259227442e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>8.558909120670844e-08</v>
+        <v>5.754472036682011e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>8.304064763838717e-08</v>
+        <v>5.076526949081396e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>8.369750070526124e-08</v>
+        <v>5.088087562995737e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.204459838022821e-07</v>
+        <v>4.996975604641552e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.228390064377386e-07</v>
+        <v>5.558424006999386e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>8.359441539060927e-08</v>
+        <v>5.086184024061772e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.258149273959792e-07</v>
+        <v>6.075893271819074e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>8.276025314053878e-08</v>
+        <v>4.87106378465566e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>8.223896260397307e-08</v>
+        <v>4.78766549818397e-08</v>
       </c>
     </row>
     <row r="7">
@@ -1111,37 +1111,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.176792665217733e-07</v>
+        <v>5.417747193385741e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.189476380300654e-07</v>
+        <v>5.708489814617396e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.20681815887524e-07</v>
+        <v>5.718590658261583e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.189454913416846e-07</v>
+        <v>5.708452194835277e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.189454913416846e-07</v>
+        <v>5.708452194835277e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.194512569062902e-07</v>
+        <v>5.619173293895425e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.18284429040305e-07</v>
+        <v>5.478263445238912e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.18946557017048e-07</v>
+        <v>5.708381713315645e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.239287622405498e-07</v>
+        <v>6.042696765263399e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.185031891354986e-07</v>
+        <v>5.500139454758276e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.176024176186056e-07</v>
+        <v>5.410062303068977e-08</v>
       </c>
     </row>
     <row r="8">
@@ -1151,37 +1151,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.643656726582706e-07</v>
+        <v>6.239427936935726e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.280590839771369e-07</v>
+        <v>7.628851252880171e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.427210950473733e-07</v>
+        <v>7.866481959836352e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.109874768134971e-07</v>
+        <v>7.328391130361368e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>1.67615184240647e-07</v>
+        <v>6.565038785215511e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.285431992625207e-07</v>
+        <v>7.539191468961261e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.273763713965275e-07</v>
+        <v>7.398281620304604e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.280384993732785e-07</v>
+        <v>7.62839988838148e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.330329690693951e-07</v>
+        <v>7.962930795046084e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>1.640303803953434e-07</v>
+        <v>6.301418016589736e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>2.918821608238318e-07</v>
+        <v>8.47738576686034e-08</v>
       </c>
     </row>
     <row r="9">
@@ -1191,37 +1191,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.857856795661627e-07</v>
+        <v>6.616420056471861e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.201400472791188e-07</v>
+        <v>7.489476207750275e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>2.218814145540308e-07</v>
+        <v>7.499703585140949e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>2.583206477182261e-07</v>
+        <v>8.16145493377055e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.201400635063074e-07</v>
+        <v>7.489476655281965e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.206436661553436e-07</v>
+        <v>7.400159687028303e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.194768382893585e-07</v>
+        <v>7.259249838371788e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.201389662661015e-07</v>
+        <v>7.489368106448524e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.251211714896032e-07</v>
+        <v>7.823683158396272e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.005254620480626e-07</v>
+        <v>6.943731450197142e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>2.187948268676591e-07</v>
+        <v>7.191048696201857e-08</v>
       </c>
     </row>
   </sheetData>
@@ -1310,7 +1310,7 @@
         <v>7.451671573558339e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>7.096032991052799e-08</v>
+        <v>7.096032991052804e-08</v>
       </c>
       <c r="D2" t="n">
         <v>1.411597064554986e-07</v>
@@ -1322,19 +1322,19 @@
         <v>7.147434008698295e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.0315166295546e-07</v>
+        <v>1.031516629554599e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>7.964193500814235e-08</v>
+        <v>7.964193500814232e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>7.586766655466308e-08</v>
+        <v>7.586766655466306e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>9.374456618598321e-08</v>
+        <v>9.374456618598322e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>8.566183778900351e-08</v>
+        <v>8.566183778900352e-08</v>
       </c>
       <c r="L2" t="n">
         <v>7.759252101175685e-08</v>
@@ -1347,19 +1347,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.088325747554031e-08</v>
+        <v>8.08832574755403e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>7.769953989838418e-08</v>
+        <v>7.769953989838441e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.57536501857381e-07</v>
+        <v>1.575365018573811e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>7.804095760193955e-08</v>
+        <v>7.804095760193954e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>7.804095760193955e-08</v>
+        <v>7.804095760193954e-08</v>
       </c>
       <c r="G3" t="n">
         <v>1.13819378489845e-07</v>
@@ -1368,13 +1368,13 @@
         <v>8.679414283708416e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>8.239590517258375e-08</v>
+        <v>8.239590517258381e-08</v>
       </c>
       <c r="J3" t="n">
         <v>1.029474139313139e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>9.250838667879104e-08</v>
+        <v>9.250838667879101e-08</v>
       </c>
       <c r="L3" t="n">
         <v>8.442276690077895e-08</v>
@@ -1387,37 +1387,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9.623906818303555e-08</v>
+        <v>5.101076426153115e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>9.28118933926707e-08</v>
+        <v>5.165305778889678e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>1.358555022629635e-07</v>
+        <v>9.062719834145895e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>9.020736501486688e-08</v>
+        <v>5.060164169600506e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>9.020736501486691e-08</v>
+        <v>5.060164169600505e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>1.128951273832786e-07</v>
+        <v>6.796857519254176e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>9.929244435160556e-08</v>
+        <v>5.406414043010108e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>9.457745122292365e-08</v>
+        <v>5.136658017075201e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>1.074639915153757e-07</v>
+        <v>6.223568759387123e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>9.813873748726984e-08</v>
+        <v>5.291043356576541e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>9.807647677773414e-08</v>
+        <v>5.284817285622932e-08</v>
       </c>
     </row>
     <row r="5">
@@ -1427,37 +1427,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.944387639268389e-07</v>
+        <v>6.829391061878993e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>3.50122452094837e-07</v>
+        <v>9.69397158750877e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>4.053280273352472e-06</v>
+        <v>7.800939543172641e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>2.883038253476944e-07</v>
+        <v>8.54666185256635e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>2.883038253476944e-07</v>
+        <v>8.54666185256635e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>1.91485103241991e-06</v>
+        <v>3.851128127605109e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>5.643786930085823e-07</v>
+        <v>1.359193197501879e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>2.882987322728167e-07</v>
+        <v>8.546152545078668e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>1.364597622484185e-06</v>
+        <v>2.834912054454861e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>3.973854539701168e-07</v>
+        <v>1.055778553813626e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>4.379477391044139e-07</v>
+        <v>1.126655147015985e-07</v>
       </c>
     </row>
     <row r="6">
@@ -1467,37 +1467,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.364566983709229e-07</v>
+        <v>4.979137097890118e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>8.794077561976842e-08</v>
+        <v>5.079574106551141e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.346156329123646e-07</v>
+        <v>9.040893273290018e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>8.413684409168663e-08</v>
+        <v>4.95332300193146e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>8.742533461174632e-08</v>
+        <v>5.011200434770896e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.531127575711661e-07</v>
+        <v>7.504687806725545e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.488150497363714e-07</v>
+        <v>6.278011893059144e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.347950814108108e-07</v>
+        <v>5.844488304546569e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.502965322683121e-07</v>
+        <v>6.977421472553972e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>8.931217536049416e-08</v>
+        <v>5.135695863987046e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>9.120670786286681e-08</v>
+        <v>5.163909353376431e-08</v>
       </c>
     </row>
     <row r="7">
@@ -1507,37 +1507,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.343895189182313e-07</v>
+        <v>5.772524355454252e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.358532542797511e-07</v>
+        <v>5.922833726397547e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.73999042759123e-07</v>
+        <v>9.734046143240658e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.32705708637693e-07</v>
+        <v>5.808135013309285e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.32705708637693e-07</v>
+        <v>5.808135013309285e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.510455781184744e-07</v>
+        <v>7.468305448555311e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.374428950868012e-07</v>
+        <v>6.077861972311244e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.327279019581191e-07</v>
+        <v>5.808105946376336e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.456144422505714e-07</v>
+        <v>6.895016688688259e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.362891882224656e-07</v>
+        <v>5.962491285877675e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.362269275129295e-07</v>
+        <v>5.956265214924068e-08</v>
       </c>
     </row>
     <row r="8">
@@ -1547,37 +1547,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.934672662114731e-07</v>
+        <v>6.812292702181206e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.750192099783139e-07</v>
+        <v>8.372154533461981e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>3.297802345007305e-07</v>
+        <v>1.247579510303649e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>2.499931300394394e-07</v>
+        <v>7.872393618794617e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>1.943372992520755e-07</v>
+        <v>6.892851002244761e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.902127878490697e-07</v>
+        <v>9.917648326541757e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.766101048177093e-07</v>
+        <v>8.527204850303209e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.718951116887136e-07</v>
+        <v>8.25744882436278e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.847973918492862e-07</v>
+        <v>9.344636588352124e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>1.938792326302967e-07</v>
+        <v>6.976076061963282e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>3.590542777323043e-07</v>
+        <v>9.878026557534588e-08</v>
       </c>
     </row>
     <row r="9">
@@ -1587,37 +1587,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.458590269085538e-07</v>
+        <v>7.734387685453367e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.966710879314286e-07</v>
+        <v>8.753227583330282e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>3.348238918150766e-07</v>
+        <v>1.256456347128797e-07</v>
       </c>
       <c r="E9" t="n">
-        <v>3.504978660565782e-07</v>
+        <v>9.641276963111386e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.935508453607311e-07</v>
+        <v>8.639009404295361e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>3.118634117701518e-07</v>
+        <v>1.029869930548805e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>2.982607287384786e-07</v>
+        <v>8.90825582924398e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.935457356097963e-07</v>
+        <v>8.638499803309073e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>3.064322759022488e-07</v>
+        <v>9.725410545620995e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.349686439649548e-07</v>
+        <v>8.289655923007263e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>2.970447611646069e-07</v>
+        <v>8.786659071856802e-08</v>
       </c>
     </row>
   </sheetData>
@@ -1703,10 +1703,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.306935764224695e-08</v>
+        <v>7.306935764224693e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>6.992917574409693e-08</v>
+        <v>6.992917574409691e-08</v>
       </c>
       <c r="D2" t="n">
         <v>1.199856584171482e-07</v>
@@ -1715,25 +1715,25 @@
         <v>7.030742772437262e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>7.030742772437263e-08</v>
+        <v>7.030742772437262e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>8.980168553327862e-08</v>
+        <v>8.98016855332786e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>7.621811207065732e-08</v>
+        <v>7.62181120706573e-08</v>
       </c>
       <c r="I2" t="n">
         <v>7.42142919121795e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>8.980900802341043e-08</v>
+        <v>8.980900802341039e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>8.254844906458276e-08</v>
+        <v>8.254844906458277e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>7.403470060909942e-08</v>
+        <v>7.403470060909941e-08</v>
       </c>
     </row>
     <row r="3">
@@ -1743,10 +1743,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.931168384522878e-08</v>
+        <v>7.931168384522877e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>7.653243477873421e-08</v>
+        <v>7.653243477873406e-08</v>
       </c>
       <c r="D3" t="n">
         <v>1.332751484187921e-07</v>
@@ -1758,19 +1758,19 @@
         <v>7.671927448208666e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>9.855732701119588e-08</v>
+        <v>9.855732701119585e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>8.294878089704874e-08</v>
+        <v>8.294878089704873e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>8.059673161524306e-08</v>
+        <v>8.059673161524302e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>9.846192390852177e-08</v>
+        <v>9.846192390852171e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>8.89645046235403e-08</v>
+        <v>8.896450462354032e-08</v>
       </c>
       <c r="L3" t="n">
         <v>8.042306679246726e-08</v>
@@ -1783,37 +1783,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9.311866133510539e-08</v>
+        <v>4.99592848254892e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>9.146429090693613e-08</v>
+        <v>5.087209701391659e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>1.21008414133482e-07</v>
+        <v>7.784903762386589e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>9.003840984756003e-08</v>
+        <v>4.996997563962814e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>9.003840984756003e-08</v>
+        <v>4.996997563962815e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>1.02624991267429e-07</v>
+        <v>5.982844667000796e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>9.499477056041563e-08</v>
+        <v>5.183539405079948e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>9.083595454634571e-08</v>
+        <v>5.01073283654253e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>1.02658775947692e-07</v>
+        <v>5.949939943807598e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>9.380621010371841e-08</v>
+        <v>5.064683359410203e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>9.369871675296311e-08</v>
+        <v>5.053934024334714e-08</v>
       </c>
     </row>
     <row r="5">
@@ -1823,37 +1823,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.648958519626133e-07</v>
+        <v>6.259207030747857e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>3.073547538505467e-07</v>
+        <v>8.886881828610307e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>2.744567468048275e-06</v>
+        <v>5.395954286108487e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>2.419752681840042e-07</v>
+        <v>7.671086256194382e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>2.419752681840042e-07</v>
+        <v>7.671086256194382e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>1.125102458434385e-06</v>
+        <v>2.397844799162813e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>3.902791544971699e-07</v>
+        <v>1.038054453420634e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>2.419716090330034e-07</v>
+        <v>7.670720341094256e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>1.109905756533331e-06</v>
+        <v>2.367748670605628e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>2.454854671668139e-07</v>
+        <v>7.734238269255432e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>2.590181667857906e-07</v>
+        <v>7.963556329146381e-08</v>
       </c>
     </row>
     <row r="6">
@@ -1863,37 +1863,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.269763146479368e-07</v>
+        <v>5.591823177625853e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>8.534551114910839e-08</v>
+        <v>4.979519178237423e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.175684940275375e-07</v>
+        <v>8.429400797746313e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>8.114622144399472e-08</v>
+        <v>4.840495048908091e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>8.323202745870806e-08</v>
+        <v>4.877205234568128e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>9.512383413044142e-08</v>
+        <v>5.850824302105196e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.37908005154312e-07</v>
+        <v>5.938812329840003e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>8.333479740935869e-08</v>
+        <v>4.878712471646924e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>9.641957735062595e-08</v>
+        <v>5.840130049094246e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>8.504776727733052e-08</v>
+        <v>4.910534766501056e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>8.620403792407637e-08</v>
+        <v>4.922027677661053e-08</v>
       </c>
     </row>
     <row r="7">
@@ -1903,37 +1903,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.265815633554248e-07</v>
+        <v>5.584875554915277e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.28026076420379e-07</v>
+        <v>5.730697122941453e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.544648295823706e-07</v>
+        <v>8.373736671096378e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.24344149505695e-07</v>
+        <v>5.600778578674341e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.24344149505695e-07</v>
+        <v>5.600778578674341e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.360878932877485e-07</v>
+        <v>6.57179173936715e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.284576725807353e-07</v>
+        <v>5.772486477446307e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.242988565666654e-07</v>
+        <v>5.599679908908882e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.361216779680116e-07</v>
+        <v>6.538887016173941e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.27269112124038e-07</v>
+        <v>5.653630431776558e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.271616187732827e-07</v>
+        <v>5.642881096701072e-08</v>
       </c>
     </row>
     <row r="8">
@@ -1943,37 +1943,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.805991767802837e-07</v>
+        <v>6.535585546041271e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.545537179791217e-07</v>
+        <v>7.957583602350046e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.959588366181472e-07</v>
+        <v>1.086403118143211e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>2.310077345798015e-07</v>
+        <v>7.478057665806382e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>1.806453077376355e-07</v>
+        <v>6.59167895818719e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.62552961955309e-07</v>
+        <v>8.797576935855572e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.549227412489445e-07</v>
+        <v>7.998271673946116e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.507639252342263e-07</v>
+        <v>7.825465105397307e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.626009846286733e-07</v>
+        <v>8.764922801339593e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>1.799409768706624e-07</v>
+        <v>6.580655246293956e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>3.293041123996057e-07</v>
+        <v>9.200588965246543e-08</v>
       </c>
     </row>
     <row r="9">
@@ -1983,37 +1983,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.092201655607356e-07</v>
+        <v>7.039314945847713e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.501128935468259e-07</v>
+        <v>7.879425092723804e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>2.765582107182223e-07</v>
+        <v>1.052258016744363e-07</v>
       </c>
       <c r="E9" t="n">
-        <v>2.919118258005831e-07</v>
+        <v>8.549969665483862e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.463893483420771e-07</v>
+        <v>7.748774066555522e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.581747104141952e-07</v>
+        <v>8.720519709149505e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.505444897071818e-07</v>
+        <v>7.921214447228666e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.463856736931123e-07</v>
+        <v>7.748407878691239e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.582084950944584e-07</v>
+        <v>8.687614985956297e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.264995111701934e-07</v>
+        <v>7.400085445525542e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>2.492484358997295e-07</v>
+        <v>7.79160906648342e-08</v>
       </c>
     </row>
   </sheetData>
@@ -2099,34 +2099,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.197479790759349e-08</v>
+        <v>7.197479790759342e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>6.847602097685977e-08</v>
+        <v>6.847602097685976e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.037250717080672e-07</v>
+        <v>1.03725071708067e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>6.905371137573946e-08</v>
+        <v>6.90537113757394e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>6.905371137573946e-08</v>
+        <v>6.905371137573938e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>8.104449726298927e-08</v>
+        <v>8.104449726298922e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>7.426913967897294e-08</v>
+        <v>7.426913967897292e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>7.258587160868344e-08</v>
+        <v>7.258587160868331e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>8.419833757773125e-08</v>
+        <v>8.419833757773117e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>8.101303089161764e-08</v>
+        <v>8.101303089161747e-08</v>
       </c>
       <c r="L2" t="n">
         <v>7.258274584656234e-08</v>
@@ -2139,37 +2139,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.863899907989305e-08</v>
+        <v>7.863899907989293e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>7.53901126051586e-08</v>
+        <v>7.539011260515861e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.151583909998415e-07</v>
+        <v>1.151583909998413e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>7.580750904701097e-08</v>
+        <v>7.580750904701089e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>7.580750904701094e-08</v>
+        <v>7.580750904701089e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>8.907103212115971e-08</v>
+        <v>8.907103212115957e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>8.129252312407889e-08</v>
+        <v>8.129252312407887e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>7.93153870899049e-08</v>
+        <v>7.931538708990461e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>9.257843740793687e-08</v>
+        <v>9.257843740793684e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>8.77350461171213e-08</v>
+        <v>8.773504611712133e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>7.933882121556141e-08</v>
+        <v>7.933882121556139e-08</v>
       </c>
     </row>
     <row r="4">
@@ -2179,37 +2179,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9.259946181032409e-08</v>
+        <v>4.950483340119207e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>9.132780736892516e-08</v>
+        <v>5.012112626965047e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>1.114736542114799e-07</v>
+        <v>6.837902580234794e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>8.889964494614434e-08</v>
+        <v>4.914584433553719e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>8.889964494614433e-08</v>
+        <v>4.914584433553719e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>9.760785617321832e-08</v>
+        <v>5.482894961706773e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>9.396605453616808e-08</v>
+        <v>5.087142612703591e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>9.037859509960291e-08</v>
+        <v>4.940398680692984e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>9.939027734453242e-08</v>
+        <v>5.629564893540036e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>9.282826586514697e-08</v>
+        <v>4.973363745601498e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>9.296504462880957e-08</v>
+        <v>4.987041621967753e-08</v>
       </c>
     </row>
     <row r="5">
@@ -2219,37 +2219,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.444733092680953e-07</v>
+        <v>5.863463050428896e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>2.450716980786622e-07</v>
+        <v>7.718005088794263e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>1.896031632042585e-06</v>
+        <v>3.824612281987345e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>1.927441545686208e-07</v>
+        <v>6.742247793005895e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>1.927441545686208e-07</v>
+        <v>6.742247793005895e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>6.733871829196433e-07</v>
+        <v>1.561661105753321e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>3.145837062274468e-07</v>
+        <v>8.970013261430329e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>1.927415420028451e-07</v>
+        <v>6.741986536427845e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>8.228370499494327e-07</v>
+        <v>1.836222802239303e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>1.830264226960965e-07</v>
+        <v>6.560851297224243e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>2.131301249802416e-07</v>
+        <v>7.101947024693125e-08</v>
       </c>
     </row>
     <row r="6">
@@ -2259,37 +2259,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.241013201888917e-07</v>
+        <v>4.804898636957246e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>8.419671045442123e-08</v>
+        <v>4.886605321949798e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.060411212798552e-07</v>
+        <v>6.742290001155884e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>8.038149506302926e-08</v>
+        <v>4.764664996423248e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>8.205413608624695e-08</v>
+        <v>4.79410347827236e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>8.933599799419426e-08</v>
+        <v>6.037327666165315e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.353770093790463e-07</v>
+        <v>5.815975413988989e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>8.210673692057896e-08</v>
+        <v>5.494831385151522e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>9.224510115008806e-08</v>
+        <v>6.221415662434669e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>8.374558326517256e-08</v>
+        <v>4.813508532708134e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>8.468619867092707e-08</v>
+        <v>4.841333933898549e-08</v>
       </c>
     </row>
     <row r="7">
@@ -2299,37 +2299,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.248577552158812e-07</v>
+        <v>5.518229300980616e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.25879228737429e-07</v>
+        <v>5.620217639755632e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.437254638212211e-07</v>
+        <v>7.40553442629046e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.227043947968939e-07</v>
+        <v>5.509548027703032e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.227043947968939e-07</v>
+        <v>5.509548027703032e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.298661495787753e-07</v>
+        <v>6.050640922568187e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.262243479417251e-07</v>
+        <v>5.654888573565e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.2263688850516e-07</v>
+        <v>5.508144641554395e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.316485707500893e-07</v>
+        <v>6.197310854401444e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.25086559270704e-07</v>
+        <v>5.54110970646291e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.252233380343668e-07</v>
+        <v>5.554787582829165e-08</v>
       </c>
     </row>
     <row r="8">
@@ -2339,37 +2339,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.779216939689354e-07</v>
+        <v>6.452154617973798e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.499022937487736e-07</v>
+        <v>7.803023572079227e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.823668033390569e-07</v>
+        <v>9.8456219885825e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.272679589026139e-07</v>
+        <v>7.34986674599175e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>1.779926355459329e-07</v>
+        <v>6.482621059613428e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.538046940911002e-07</v>
+        <v>8.231959294165402e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.501628924551783e-07</v>
+        <v>7.836206945182083e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.465754330174852e-07</v>
+        <v>7.689463013151614e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.556010441431501e-07</v>
+        <v>8.378874374298292e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>1.768339658318446e-07</v>
+        <v>6.45186405700397e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>3.231963347001647e-07</v>
+        <v>9.039112305267038e-08</v>
       </c>
     </row>
     <row r="9">
@@ -2379,37 +2379,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.924404214293658e-07</v>
+        <v>6.70768421989276e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.283254839473587e-07</v>
+        <v>7.423271721680353e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>2.461782658956857e-07</v>
+        <v>9.208703733030369e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>2.653176741482178e-07</v>
+        <v>8.019541730685672e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.250857709849959e-07</v>
+        <v>7.311460238849782e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.323124047887052e-07</v>
+        <v>7.853695004492906e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.286706031516543e-07</v>
+        <v>7.457942655489725e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.250831437150892e-07</v>
+        <v>7.311198723479119e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.34094825960019e-07</v>
+        <v>8.000364936326166e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.065131955509624e-07</v>
+        <v>6.571532627401044e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>2.276695932442958e-07</v>
+        <v>7.357841664753885e-08</v>
       </c>
     </row>
   </sheetData>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.331720300105842e-08</v>
+        <v>7.331720300105837e-08</v>
       </c>
       <c r="C2" t="n">
         <v>6.721753937568879e-08</v>
@@ -2504,25 +2504,25 @@
         <v>1.098980895994576e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>7.065979463469847e-08</v>
+        <v>7.065979463469842e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>7.065979463469848e-08</v>
+        <v>7.065979463469842e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>9.043580651979764e-08</v>
+        <v>9.043580651979757e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>7.758179752652831e-08</v>
+        <v>7.758179752652827e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>7.478520469148966e-08</v>
+        <v>7.478520469148958e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>8.873304905845651e-08</v>
+        <v>8.873304905845647e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>8.352647968974808e-08</v>
+        <v>8.352647968974794e-08</v>
       </c>
       <c r="L2" t="n">
         <v>7.737061140140616e-08</v>
@@ -2535,37 +2535,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.950418037327436e-08</v>
+        <v>7.950418037327433e-08</v>
       </c>
       <c r="C3" t="n">
         <v>7.336321933640147e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.215797776692638e-07</v>
+        <v>1.215797776692636e-07</v>
       </c>
       <c r="E3" t="n">
+        <v>7.706476190355407e-08</v>
+      </c>
+      <c r="F3" t="n">
         <v>7.706476190355409e-08</v>
       </c>
-      <c r="F3" t="n">
-        <v>7.706476190355408e-08</v>
-      </c>
       <c r="G3" t="n">
-        <v>9.919412052786027e-08</v>
+        <v>9.919412052786026e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>8.442443269821831e-08</v>
+        <v>8.442443269821827e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>8.116140030530963e-08</v>
+        <v>8.116140030530959e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>9.71756872053974e-08</v>
+        <v>9.717568720539738e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>9.002178190484833e-08</v>
+        <v>9.002178190484825e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>8.41673453906007e-08</v>
+        <v>8.416734539060068e-08</v>
       </c>
     </row>
     <row r="4">
@@ -2575,37 +2575,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9.383749752559327e-08</v>
+        <v>5.011701351876175e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>8.918859675575086e-08</v>
+        <v>4.919273974628156e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>1.155832845446882e-07</v>
+        <v>7.186280053785675e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>8.887035541900515e-08</v>
+        <v>4.995367255261856e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>8.887035541900511e-08</v>
+        <v>4.995367255261856e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>1.036720904210637e-07</v>
+        <v>6.023316022675538e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>9.637674746201379e-08</v>
+        <v>5.265626345518226e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>9.240415433375829e-08</v>
+        <v>5.057273795904385e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>1.027644677509792e-07</v>
+        <v>5.904398374414769e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>9.505771943263551e-08</v>
+        <v>5.133723542580396e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>9.625265080233818e-08</v>
+        <v>5.253216679550669e-08</v>
       </c>
     </row>
     <row r="5">
@@ -2615,37 +2615,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.719768929917826e-07</v>
+        <v>6.386954704629153e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>1.637364734076906e-07</v>
+        <v>6.231316596592855e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>2.298084057372142e-06</v>
+        <v>4.559829344740937e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>2.728242695851083e-07</v>
+        <v>8.232956127042059e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>2.728242695851083e-07</v>
+        <v>8.232956127042059e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>1.20817113883863e-06</v>
+        <v>2.546249916949139e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>4.827959317809047e-07</v>
+        <v>1.206660395267891e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>2.728207705569554e-07</v>
+        <v>8.232606224226791e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>1.106548149607265e-06</v>
+        <v>2.357099107935711e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>3.08772063078636e-07</v>
+        <v>8.895095970368599e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>4.770654468572418e-07</v>
+        <v>1.195552185379983e-07</v>
       </c>
     </row>
     <row r="6">
@@ -2655,37 +2655,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.291689346035429e-07</v>
+        <v>4.865013753942317e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>8.314293137631346e-08</v>
+        <v>4.812870264526617e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.103339538727117e-07</v>
+        <v>7.093891834459518e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>8.162692418445316e-08</v>
+        <v>4.867882866224534e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>8.397172139376186e-08</v>
+        <v>4.909151296884747e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>9.533756776602393e-08</v>
+        <v>5.87662842474168e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.407571250606994e-07</v>
+        <v>6.046720987022649e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.277355914117079e-07</v>
+        <v>4.910586197970529e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.404068510268832e-07</v>
+        <v>6.566904316480821e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>8.549950682820896e-08</v>
+        <v>4.965499001654031e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>8.799504797327533e-08</v>
+        <v>5.107882870546668e-08</v>
       </c>
     </row>
     <row r="7">
@@ -2695,37 +2695,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.290900997311627e-07</v>
+        <v>5.632147147332247e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.289407513356947e-07</v>
+        <v>5.618911891444103e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.508289870929608e-07</v>
+        <v>7.806604415273974e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.277555659867893e-07</v>
+        <v>5.679746957546476e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.277555659867893e-07</v>
+        <v>5.679746957546476e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.389246926266333e-07</v>
+        <v>6.643761818131609e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.316293496675833e-07</v>
+        <v>5.886072140974296e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.276567565393277e-07</v>
+        <v>5.677719591360461e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.380170699565487e-07</v>
+        <v>6.524844169870839e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.30310321638205e-07</v>
+        <v>5.754169338036467e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.315052530079077e-07</v>
+        <v>5.873662475006739e-08</v>
       </c>
     </row>
     <row r="8">
@@ -2735,37 +2735,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.857663921557298e-07</v>
+        <v>6.629649888599557e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.618129349617814e-07</v>
+        <v>7.957462310591559e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.99368804388568e-07</v>
+        <v>1.04209051855108e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>2.397106702145791e-07</v>
+        <v>7.650156781278704e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>1.868091645082333e-07</v>
+        <v>6.719090285892097e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.716817649346279e-07</v>
+        <v>8.980286278091613e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.643864219758779e-07</v>
+        <v>8.222596600939583e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.604138288473222e-07</v>
+        <v>8.014244051320464e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.707890943127803e-07</v>
+        <v>8.861631785878389e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>1.855733745137649e-07</v>
+        <v>6.726799063376025e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>3.437350616775417e-07</v>
+        <v>9.608907087352495e-08</v>
       </c>
     </row>
     <row r="9">
@@ -2775,37 +2775,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.269680003219416e-07</v>
+        <v>7.354798188395591e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.713275134048733e-07</v>
+        <v>8.124918890282588e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>2.932227313344606e-07</v>
+        <v>1.031273430034464e-07</v>
       </c>
       <c r="E9" t="n">
-        <v>3.214093950950748e-07</v>
+        <v>9.088054331384027e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.700470340053101e-07</v>
+        <v>8.184076781102468e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.813114546958117e-07</v>
+        <v>9.149768816970098e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.740161117367619e-07</v>
+        <v>8.392079139812778e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.700435186085064e-07</v>
+        <v>8.18372659019894e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.804038320257273e-07</v>
+        <v>9.030851168709325e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.166524609162868e-07</v>
+        <v>7.27379098109648e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>2.738920150770863e-07</v>
+        <v>8.379669473845222e-08</v>
       </c>
     </row>
   </sheetData>
@@ -2891,37 +2891,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.146086932803489e-08</v>
+        <v>7.146086932803497e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>6.632685181473321e-08</v>
+        <v>6.632685181473322e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>7.210909038243093e-08</v>
+        <v>7.210909038243106e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>6.931703066584559e-08</v>
+        <v>6.931703066584557e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>6.931703066584559e-08</v>
+        <v>6.931703066584557e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>7.25157079015598e-08</v>
+        <v>7.251570790155979e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>7.224178615619887e-08</v>
+        <v>7.224178615619889e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>7.281291662751232e-08</v>
+        <v>7.281291662751241e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>8.175258253055463e-08</v>
+        <v>8.175258253055466e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>8.030642251904256e-08</v>
+        <v>8.030642251904261e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>7.250139217520645e-08</v>
+        <v>7.250139217520644e-08</v>
       </c>
     </row>
     <row r="3">
@@ -2931,10 +2931,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.745917223774209e-08</v>
+        <v>7.745917223774207e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>7.232846113682534e-08</v>
+        <v>7.232846113682535e-08</v>
       </c>
       <c r="D3" t="n">
         <v>7.820476072888442e-08</v>
@@ -2946,22 +2946,22 @@
         <v>7.551641480821052e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>7.867245510644795e-08</v>
+        <v>7.867245510644799e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>7.83718189951579e-08</v>
+        <v>7.837181899515792e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>7.899441162425883e-08</v>
+        <v>7.899441162425894e-08</v>
       </c>
       <c r="J3" t="n">
         <v>8.91849527797338e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>8.633392823280883e-08</v>
+        <v>8.633392823280893e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>7.865602753897662e-08</v>
+        <v>7.86560275389766e-08</v>
       </c>
     </row>
     <row r="4">
@@ -2971,37 +2971,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8.990010807539107e-08</v>
+        <v>4.880136289404707e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>8.75403999445216e-08</v>
+        <v>4.842036955958334e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>9.02854480247734e-08</v>
+        <v>4.918670284342945e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>8.803236484489849e-08</v>
+        <v>4.912837612167999e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>8.803236484489856e-08</v>
+        <v>4.912837612167999e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>9.012047569029657e-08</v>
+        <v>4.935684242641702e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>9.036547713064566e-08</v>
+        <v>4.92667319493017e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>8.795842525485585e-08</v>
+        <v>4.911414365663899e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>9.557555208900871e-08</v>
+        <v>5.447680690766475e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>9.00156806673583e-08</v>
+        <v>4.891693548601436e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>9.052051123179513e-08</v>
+        <v>4.94217660504512e-08</v>
       </c>
     </row>
     <row r="5">
@@ -3011,37 +3011,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.423478239195473e-07</v>
+        <v>5.803216083260054e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>1.501005076262072e-07</v>
+        <v>5.943094845189805e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>1.943793153546066e-07</v>
+        <v>6.750722339420847e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>2.309281618503355e-07</v>
+        <v>7.427803625836074e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>2.309281618503355e-07</v>
+        <v>7.427803625836074e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>2.197905668375316e-07</v>
+        <v>7.217877834466754e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>2.180948003009383e-07</v>
+        <v>7.174709270546111e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>2.30926682363366e-07</v>
+        <v>7.42765567713914e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>7.122892288597813e-07</v>
+        <v>1.630184134311766e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>1.699704969915273e-07</v>
+        <v>6.298898308281724e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>2.374599997762005e-07</v>
+        <v>7.52831158941341e-08</v>
       </c>
     </row>
     <row r="6">
@@ -3051,37 +3051,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.06508918148573e-08</v>
+        <v>4.717350084101389e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>7.996650797459761e-08</v>
+        <v>4.708736458009973e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.197601377183719e-07</v>
+        <v>4.75778208631281e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>7.788139379180443e-08</v>
+        <v>4.734180522601614e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>7.875711572400618e-08</v>
+        <v>4.74959322852485e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>8.087125942976291e-08</v>
+        <v>5.421494973169365e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.265521947958637e-07</v>
+        <v>5.563559422386973e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>7.870920899432222e-08</v>
+        <v>5.397225096191563e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>8.72903000013917e-08</v>
+        <v>5.30186025481456e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>8.044374709472292e-08</v>
+        <v>4.723227518635902e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>8.128297705706311e-08</v>
+        <v>4.779596004450794e-08</v>
       </c>
     </row>
     <row r="7">
@@ -3091,37 +3091,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.194645735854055e-07</v>
+        <v>5.400470879561476e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.195287309639141e-07</v>
+        <v>5.405031578848998e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.198434083530394e-07</v>
+        <v>5.438890383301561e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.176648435909037e-07</v>
+        <v>5.434369235271714e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.176648435909037e-07</v>
+        <v>5.434369235271714e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.196849412003111e-07</v>
+        <v>5.456018832798472e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.199299426406602e-07</v>
+        <v>5.447007785086943e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.175228907648704e-07</v>
+        <v>5.431748955820664e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.251400175990232e-07</v>
+        <v>5.968015280923241e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.195801461773727e-07</v>
+        <v>5.412028138758201e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.200849767418097e-07</v>
+        <v>5.462511195201892e-08</v>
       </c>
     </row>
     <row r="8">
@@ -3131,37 +3131,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.699908881069499e-07</v>
+        <v>6.289734010322086e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.370306128690541e-07</v>
+        <v>7.473064689173597e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.510512991294001e-07</v>
+        <v>7.748149248452527e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.167331091923999e-07</v>
+        <v>7.177970700410167e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>1.702564425198826e-07</v>
+        <v>6.359981371406219e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.370308488662181e-07</v>
+        <v>7.521306796527453e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.37275850307201e-07</v>
+        <v>7.512295748827081e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.348687984307773e-07</v>
+        <v>7.497036919549652e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.424990572249698e-07</v>
+        <v>8.033534367147667e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>1.688652524482349e-07</v>
+        <v>6.279446004425183e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>3.07229536813527e-07</v>
+        <v>8.756255434616619e-08</v>
       </c>
     </row>
     <row r="9">
@@ -3171,37 +3171,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.86597101510251e-07</v>
+        <v>6.582003364636498e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.203372085968583e-07</v>
+        <v>7.179260775574969e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>2.206584396946844e-07</v>
+        <v>7.213234925300045e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>2.57194242965203e-07</v>
+        <v>7.890086650952819e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.183328633211117e-07</v>
+        <v>7.206126372922919e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.204934188332553e-07</v>
+        <v>7.230248029524443e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.207384202736043e-07</v>
+        <v>7.221236981812915e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.183313683978146e-07</v>
+        <v>7.205978152546638e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.259484952319674e-07</v>
+        <v>7.742244477649211e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.008766667040315e-07</v>
+        <v>6.439946158169128e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>2.20893454374754e-07</v>
+        <v>7.236740391927863e-08</v>
       </c>
     </row>
   </sheetData>
@@ -3293,31 +3293,31 @@
         <v>6.631798005387278e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>7.152724983565956e-08</v>
+        <v>7.152724983565955e-08</v>
       </c>
       <c r="E2" t="n">
         <v>6.868265847326371e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>6.868265847326372e-08</v>
+        <v>6.868265847326371e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>7.131399039520414e-08</v>
+        <v>7.13139903952041e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>7.148798810451327e-08</v>
+        <v>7.148798810451325e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>7.172053203320087e-08</v>
+        <v>7.172053203320085e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>7.846544182324221e-08</v>
+        <v>7.846544182324219e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>8.002915841358755e-08</v>
+        <v>8.002915841358751e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>7.147081972635542e-08</v>
+        <v>7.147081972635541e-08</v>
       </c>
     </row>
     <row r="3">
@@ -3327,19 +3327,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.742392217289251e-08</v>
+        <v>7.742392217289249e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>7.286590628971345e-08</v>
+        <v>7.286590628971343e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>7.8155837795509e-08</v>
+        <v>7.815583779550898e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>7.533834449328266e-08</v>
+        <v>7.533834449328265e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>7.533834449328266e-08</v>
+        <v>7.533834449328265e-08</v>
       </c>
       <c r="G3" t="n">
         <v>7.791054526242523e-08</v>
@@ -3348,13 +3348,13 @@
         <v>7.812445436566666e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>7.83587757070266e-08</v>
+        <v>7.835877570702659e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>8.598085570783459e-08</v>
+        <v>8.598085570783461e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>8.6568768652282e-08</v>
+        <v>8.656876865228197e-08</v>
       </c>
       <c r="L3" t="n">
         <v>7.809094861217916e-08</v>
@@ -3367,37 +3367,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9.064688131446092e-08</v>
+        <v>4.889065410984155e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>8.895171895896937e-08</v>
+        <v>4.86635667181741e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>9.102515476197502e-08</v>
+        <v>4.926892755735557e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>8.767414025010837e-08</v>
+        <v>4.876751714644849e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>8.767414025010837e-08</v>
+        <v>4.876751714644849e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>9.053421160759258e-08</v>
+        <v>4.90780600330876e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>9.10028631971294e-08</v>
+        <v>4.924663599250997e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>8.867885508267059e-08</v>
+        <v>4.894319885940418e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>9.453484412395191e-08</v>
+        <v>5.277861691933251e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>9.067301782880959e-08</v>
+        <v>4.891679062419018e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>9.099340849934666e-08</v>
+        <v>4.923718129472722e-08</v>
       </c>
     </row>
     <row r="5">
@@ -3407,37 +3407,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.401548883986513e-07</v>
+        <v>5.760406330944447e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>1.522139255020043e-07</v>
+        <v>5.979771500941708e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>1.916581045796699e-07</v>
+        <v>6.698032662929881e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>2.003086052352048e-07</v>
+        <v>6.859118287640869e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>2.003086052352048e-07</v>
+        <v>6.859118287640869e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>1.82132125932977e-07</v>
+        <v>6.519929286700066e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>2.042761123468206e-07</v>
+        <v>6.918272773482986e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>2.003072119140694e-07</v>
+        <v>6.858978955527323e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>5.371442899387e-07</v>
+        <v>1.306778789606231e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>1.596341012961982e-07</v>
+        <v>6.105394124868409e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>2.058910144360435e-07</v>
+        <v>6.945915983001089e-08</v>
       </c>
     </row>
     <row r="6">
@@ -3447,37 +3447,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.186749675094299e-07</v>
+        <v>5.38235972534264e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>8.100047498571987e-08</v>
+        <v>4.726414778646508e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>8.189967873719219e-08</v>
+        <v>4.766284378569653e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>7.859079788035076e-08</v>
+        <v>4.716884889803364e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>7.958056478977971e-08</v>
+        <v>4.73430478731493e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.185622978025615e-07</v>
+        <v>5.401100317667227e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.285882500968254e-07</v>
+        <v>5.586166405101228e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>7.954842716944371e-08</v>
+        <v>4.733624355538384e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.243786394812651e-07</v>
+        <v>5.80311248737584e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>8.126671849438882e-08</v>
+        <v>4.72612819503028e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>8.186336090495931e-08</v>
+        <v>4.763029292682211e-08</v>
       </c>
     </row>
     <row r="7">
@@ -3487,37 +3487,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.201509169604215e-07</v>
+        <v>5.408336435539332e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.202608576662293e-07</v>
+        <v>5.417397510079316e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.205226707602903e-07</v>
+        <v>5.446049034492799e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.182981184666156e-07</v>
+        <v>5.415733728334849e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.182981184666156e-07</v>
+        <v>5.415733728334849e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.200382472535531e-07</v>
+        <v>5.427077027863921e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.205068988430899e-07</v>
+        <v>5.44393462380618e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.181828907286311e-07</v>
+        <v>5.413590910495611e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.240388797699125e-07</v>
+        <v>5.797132716488431e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.201770534747701e-07</v>
+        <v>5.410950086974195e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.204974441453072e-07</v>
+        <v>5.442989154027899e-08</v>
       </c>
     </row>
     <row r="8">
@@ -3527,37 +3527,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.70896993995528e-07</v>
+        <v>6.301467386517683e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.38111861277872e-07</v>
+        <v>7.491575162405079e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.521371679803761e-07</v>
+        <v>7.762464173014575e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.177024766773203e-07</v>
+        <v>7.165250423363309e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>1.71125141152933e-07</v>
+        <v>6.345489322576057e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.377586600154205e-07</v>
+        <v>7.498956281246086e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.382273116060816e-07</v>
+        <v>7.515813877208137e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.359033034904987e-07</v>
+        <v>7.485470163877786e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.417724548998879e-07</v>
+        <v>7.869243627548049e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>1.696790478360316e-07</v>
+        <v>6.282185183011515e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>3.081781508785265e-07</v>
+        <v>8.746169574633928e-08</v>
       </c>
     </row>
     <row r="9">
@@ -3567,37 +3567,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.802414799086908e-07</v>
+        <v>6.465930337698188e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.120864560445943e-07</v>
+        <v>7.033528032781366e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>2.123548362475278e-07</v>
+        <v>7.062295138310386e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>2.466315021694474e-07</v>
+        <v>7.674401269265862e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.100098975021189e-07</v>
+        <v>7.029861030613387e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.118638456319181e-07</v>
+        <v>7.043207550565976e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.123324972214551e-07</v>
+        <v>7.06006514650823e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.100084891069963e-07</v>
+        <v>7.029721433197666e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.158644781482777e-07</v>
+        <v>7.413263239190485e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>1.936152676538434e-07</v>
+        <v>6.690333026198241e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>2.123230425236721e-07</v>
+        <v>7.059119676729959e-08</v>
       </c>
     </row>
   </sheetData>
@@ -3683,37 +3683,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.237540213287528e-08</v>
+        <v>7.237540213287522e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>6.671095885331423e-08</v>
+        <v>6.671095885331424e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>7.740047729572741e-08</v>
+        <v>7.740047729572747e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>6.994000079150154e-08</v>
+        <v>6.994000079150143e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>6.994000079150154e-08</v>
+        <v>6.994000079150143e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>7.827073573133938e-08</v>
+        <v>7.827073573133937e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>7.591285675312363e-08</v>
+        <v>7.591285675312362e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>7.378553576910685e-08</v>
+        <v>7.378553576910682e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>8.527742767103922e-08</v>
+        <v>8.527742767103916e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>8.129504063505099e-08</v>
+        <v>8.129504063505104e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>7.595577941039288e-08</v>
+        <v>7.595577941039285e-08</v>
       </c>
     </row>
     <row r="3">
@@ -3723,37 +3723,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.842284250160436e-08</v>
+        <v>7.842284250160421e-08</v>
       </c>
       <c r="C3" t="n">
         <v>7.272990746366264e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>8.420271988006839e-08</v>
+        <v>8.420271988006828e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>7.619705529401058e-08</v>
+        <v>7.619705529401066e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>7.619705529401058e-08</v>
+        <v>7.61970552940105e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>8.520369735451398e-08</v>
+        <v>8.520369735451383e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>8.250603784151495e-08</v>
+        <v>8.250603784151496e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>8.002112524192226e-08</v>
+        <v>8.002112524192214e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>9.318965480467669e-08</v>
+        <v>9.318965480467666e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>8.742746377276709e-08</v>
+        <v>8.74274637727671e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>8.254122732480401e-08</v>
+        <v>8.254122732480398e-08</v>
       </c>
     </row>
     <row r="4">
@@ -3763,37 +3763,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9.198262940464178e-08</v>
+        <v>4.944535395849442e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>8.788052275071507e-08</v>
+        <v>4.865694678952564e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>9.496982365846047e-08</v>
+        <v>5.2432548212313e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>8.762495934917206e-08</v>
+        <v>4.936196628793353e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>8.76249593491721e-08</v>
+        <v>4.936196628793352e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>9.516885819831276e-08</v>
+        <v>5.28938596651611e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>9.408714364464979e-08</v>
+        <v>5.154986819850238e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>9.066665217282481e-08</v>
+        <v>4.989568113934518e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>9.936268234237174e-08</v>
+        <v>5.682540689622421e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>9.231895597329904e-08</v>
+        <v>4.978168052715147e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>9.411361128275429e-08</v>
+        <v>5.157633583660705e-08</v>
       </c>
     </row>
     <row r="5">
@@ -3803,37 +3803,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.630959971869969e-07</v>
+        <v>6.196130662036998e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>1.591856659911552e-07</v>
+        <v>6.120665193184127e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>4.69959646307882e-07</v>
+        <v>1.184307566409931e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>2.604490981367449e-07</v>
+        <v>7.977901454972904e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>2.604490981367449e-07</v>
+        <v>7.977901454972904e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>5.324478711874834e-07</v>
+        <v>1.298549655342328e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>4.24809780020169e-07</v>
+        <v>1.097570518851915e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>2.604471283762492e-07</v>
+        <v>7.977704478923309e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>9.390185479394469e-07</v>
+        <v>2.046048384405513e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>2.134768241668741e-07</v>
+        <v>7.110546521367552e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>4.348069880007816e-07</v>
+        <v>1.115383698140692e-07</v>
       </c>
     </row>
     <row r="6">
@@ -3843,37 +3843,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.230203167212726e-07</v>
+        <v>4.778631785098481e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>8.119660513164937e-08</v>
+        <v>4.74805772949444e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>8.585833244859576e-08</v>
+        <v>5.082892576806615e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>7.97484390128047e-08</v>
+        <v>4.79756987162445e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>8.124125580872955e-08</v>
+        <v>4.823843447090362e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.262065455149434e-07</v>
+        <v>5.835649260328825e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.33973249516633e-07</v>
+        <v>5.85698227939332e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>8.124031060180683e-08</v>
+        <v>5.53583140774723e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.324156495856463e-07</v>
+        <v>6.264272909951888e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>8.229774940558231e-08</v>
+        <v>4.801794818079035e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>8.475383682145265e-08</v>
+        <v>4.992901554034415e-08</v>
       </c>
     </row>
     <row r="7">
@@ -3883,37 +3883,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.245248146811365e-07</v>
+        <v>5.51727785361229e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.244536719236859e-07</v>
+        <v>5.509382100908966e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.275051203183845e-07</v>
+        <v>5.815876039343171e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.233379433661268e-07</v>
+        <v>5.5647451440859e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.233379433661268e-07</v>
+        <v>5.5647451440859e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.277110434748075e-07</v>
+        <v>5.86212842427895e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.266293289211443e-07</v>
+        <v>5.727729277613072e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.232088374493195e-07</v>
+        <v>5.562310571697362e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.319048676188664e-07</v>
+        <v>6.255283147385273e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.248611412497936e-07</v>
+        <v>5.550910510477989e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.266557965592492e-07</v>
+        <v>5.730376041423555e-08</v>
       </c>
     </row>
     <row r="8">
@@ -3923,37 +3923,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.788410271109521e-07</v>
+        <v>6.473243187197054e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.512153069512742e-07</v>
+        <v>7.740386865305587e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.691208729082427e-07</v>
+        <v>8.308313271419127e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.301813673328357e-07</v>
+        <v>7.445189395710601e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>1.798987906433562e-07</v>
+        <v>6.56021605077108e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.54327898259582e-07</v>
+        <v>8.090585056415871e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.532461837062139e-07</v>
+        <v>7.956185909755183e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.49825692234094e-07</v>
+        <v>7.790767203834275e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.585359315470493e-07</v>
+        <v>8.483989860444808e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>1.778343321258644e-07</v>
+        <v>6.483238664844939e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>3.28796717967701e-07</v>
+        <v>9.288056238934654e-08</v>
       </c>
     </row>
     <row r="9">
@@ -3963,37 +3963,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.093576705202594e-07</v>
+        <v>7.010336108290548e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.491951127967579e-07</v>
+        <v>7.704831448378761e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>2.522535092131957e-07</v>
+        <v>8.011447671994897e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>2.940059810452276e-07</v>
+        <v>8.568502590961902e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.479522627475584e-07</v>
+        <v>7.757957153314947e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.524524843478795e-07</v>
+        <v>8.05757777174874e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.513707697942161e-07</v>
+        <v>7.923178625082877e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.479502783223914e-07</v>
+        <v>7.757759919167161e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.56646308491938e-07</v>
+        <v>8.45073249485506e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.255412777463747e-07</v>
+        <v>7.339392140027934e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>2.513972374323209e-07</v>
+        <v>7.925825388893347e-08</v>
       </c>
     </row>
   </sheetData>
@@ -4079,13 +4079,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.095286594895175e-08</v>
+        <v>7.09528659489517e-08</v>
       </c>
       <c r="C2" t="n">
         <v>6.641095985330027e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>7.145924325592709e-08</v>
+        <v>7.145924325592706e-08</v>
       </c>
       <c r="E2" t="n">
         <v>6.92280732844471e-08</v>
@@ -4094,22 +4094,22 @@
         <v>6.92280732844471e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>7.132635383798678e-08</v>
+        <v>7.132635383798674e-08</v>
       </c>
       <c r="H2" t="n">
         <v>7.147000868285293e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>7.208630498054014e-08</v>
+        <v>7.208630498054025e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>8.192065791253367e-08</v>
+        <v>8.192065791253371e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>8.063596394860991e-08</v>
+        <v>8.063596394860993e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>7.156968525989202e-08</v>
+        <v>7.156968525989204e-08</v>
       </c>
     </row>
     <row r="3">
@@ -4119,37 +4119,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.697349841469876e-08</v>
+        <v>7.697349841469882e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>7.242180512935374e-08</v>
+        <v>7.242180512935373e-08</v>
       </c>
       <c r="D3" t="n">
         <v>7.755593721346364e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>7.541696650030839e-08</v>
+        <v>7.541696650030832e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>7.541696650030838e-08</v>
+        <v>7.541696650030832e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>7.740308685487227e-08</v>
+        <v>7.740308685487225e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>7.758249760952019e-08</v>
+        <v>7.75824976095202e-08</v>
       </c>
       <c r="I3" t="n">
         <v>7.825828648319453e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>8.93907298553106e-08</v>
+        <v>8.939072985531058e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>8.670628569446754e-08</v>
+        <v>8.670628569446757e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>7.768298176451234e-08</v>
+        <v>7.768298176451236e-08</v>
       </c>
     </row>
     <row r="4">
@@ -4159,37 +4159,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8.985927693102144e-08</v>
+        <v>4.88394459227288e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>8.740381852446096e-08</v>
+        <v>4.839898513690899e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>9.016029678299167e-08</v>
+        <v>4.9140465774699e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>8.795652744771158e-08</v>
+        <v>4.9053268802135e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>8.795652744771159e-08</v>
+        <v>4.9053268802135e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>8.967497930167954e-08</v>
+        <v>4.898995626493388e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>9.016774732416965e-08</v>
+        <v>4.914791631587705e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>8.778996995333344e-08</v>
+        <v>4.902278365740605e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>9.559555749232222e-08</v>
+        <v>5.457572648402944e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>9.005592650219677e-08</v>
+        <v>4.903609549390425e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>9.022772666701651e-08</v>
+        <v>4.920789565872381e-08</v>
       </c>
     </row>
     <row r="5">
@@ -4199,37 +4199,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.494542051093326e-07</v>
+        <v>5.932815322527738e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>1.5229429406922e-07</v>
+        <v>5.981970877090222e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>1.934556865409507e-07</v>
+        <v>6.732045427358967e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>2.257679207242715e-07</v>
+        <v>7.330807388738215e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>2.257679207242715e-07</v>
+        <v>7.330807388738215e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>1.884893264052713e-07</v>
+        <v>6.638128126092924e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>2.095069134477559e-07</v>
+        <v>7.015160943981745e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>2.257664995763638e-07</v>
+        <v>7.330665273947454e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>7.25364423174053e-07</v>
+        <v>1.654150462434194e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>1.843061315778495e-07</v>
+        <v>6.562413149733496e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>2.186117909522839e-07</v>
+        <v>7.180349085049424e-08</v>
       </c>
     </row>
     <row r="6">
@@ -4239,37 +4239,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.17493100133756e-07</v>
+        <v>4.723584292014714e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>8.004208149588902e-08</v>
+        <v>4.710331942690105e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>8.11890365690944e-08</v>
+        <v>4.756147684187261e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>7.787421663096763e-08</v>
+        <v>4.727878210800331e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>7.873102480025932e-08</v>
+        <v>4.742958034498151e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>8.056359855582206e-08</v>
+        <v>4.738635326235224e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.263454203733385e-07</v>
+        <v>5.551518673802908e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>7.867858920747577e-08</v>
+        <v>5.388633651473369e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>8.745195941362022e-08</v>
+        <v>5.973607769905432e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>8.07017043860664e-08</v>
+        <v>4.738975241038621e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>8.111780582661002e-08</v>
+        <v>4.760454959950024e-08</v>
       </c>
     </row>
     <row r="7">
@@ -4279,37 +4279,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.189628226069005e-07</v>
+        <v>5.396166993392822e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.189765584274179e-07</v>
+        <v>5.395578732971931e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.192573619899857e-07</v>
+        <v>5.426154922338088e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.17058714147358e-07</v>
+        <v>5.417525363351876e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.17058714147358e-07</v>
+        <v>5.417525363351876e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.187785249775583e-07</v>
+        <v>5.411218027613332e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.192712930000488e-07</v>
+        <v>5.427014032707651e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.168935156292125e-07</v>
+        <v>5.414500766860549e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.246991031682012e-07</v>
+        <v>5.969795049522888e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.191594721780759e-07</v>
+        <v>5.415831950510368e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.193312723428955e-07</v>
+        <v>5.433011966992322e-08</v>
       </c>
     </row>
     <row r="8">
@@ -4319,37 +4319,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.691040356664095e-07</v>
+        <v>6.278652338458341e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.355345811219692e-07</v>
+        <v>7.446999921280185e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.493787977122472e-07</v>
+        <v>7.716292178640525e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.153163563269266e-07</v>
+        <v>7.146859856341696e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>1.692373818379499e-07</v>
+        <v>6.335869909730144e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.351584514903406e-07</v>
+        <v>7.459504723139435e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.356512195134508e-07</v>
+        <v>7.475300728244658e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.332734421419946e-07</v>
+        <v>7.462787462386652e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.410920474802081e-07</v>
+        <v>8.018310858314107e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>1.680702671255022e-07</v>
+        <v>6.276661936920566e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>3.049030738505497e-07</v>
+        <v>8.699075655829529e-08</v>
       </c>
     </row>
     <row r="9">
@@ -4359,37 +4359,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.857028710298799e-07</v>
+        <v>6.570791839272431e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.191376871880809e-07</v>
+        <v>7.158414589607488e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>2.194250187305111e-07</v>
+        <v>7.189105671418606e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>2.556233461018766e-07</v>
+        <v>7.856262872536846e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.170560811752705e-07</v>
+        <v>7.177479013506643e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.189396537382214e-07</v>
+        <v>7.17405388424888e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.194324217607115e-07</v>
+        <v>7.189849889343208e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.170546443898752e-07</v>
+        <v>7.177336623496104e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.248602319288641e-07</v>
+        <v>7.732630906158443e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>1.77237482838034e-07</v>
+        <v>6.837856389130631e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>2.194924011035588e-07</v>
+        <v>7.195847823627882e-08</v>
       </c>
     </row>
   </sheetData>
@@ -4475,22 +4475,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.076548180108736e-08</v>
+        <v>7.076548180108735e-08</v>
       </c>
       <c r="C2" t="n">
         <v>6.642025172779733e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>7.127457610449907e-08</v>
+        <v>7.127457610449904e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>6.869668297927513e-08</v>
+        <v>6.869668297927515e-08</v>
       </c>
       <c r="F2" t="n">
         <v>6.869668297927514e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>7.111769315210348e-08</v>
+        <v>7.111769315210347e-08</v>
       </c>
       <c r="H2" t="n">
         <v>7.128684410605926e-08</v>
@@ -4499,13 +4499,13 @@
         <v>7.152421278887792e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>7.851493395719341e-08</v>
+        <v>7.85149339571934e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>8.039595999597195e-08</v>
+        <v>8.039595999597186e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>7.127499567165224e-08</v>
+        <v>7.127499567165222e-08</v>
       </c>
     </row>
     <row r="3">
@@ -4521,13 +4521,13 @@
         <v>7.301247950370892e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>7.794042026932388e-08</v>
+        <v>7.794042026932386e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>7.539809114349836e-08</v>
+        <v>7.539809114349835e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>7.539809114349836e-08</v>
+        <v>7.539809114349835e-08</v>
       </c>
       <c r="G3" t="n">
         <v>7.775997237586325e-08</v>
@@ -4536,16 +4536,16 @@
         <v>7.796815294687149e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>7.820831783948621e-08</v>
+        <v>7.820831783948619e-08</v>
       </c>
       <c r="J3" t="n">
         <v>8.608678731168081e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>8.702599635517845e-08</v>
+        <v>8.702599635517838e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>7.794091619130012e-08</v>
+        <v>7.794091619130011e-08</v>
       </c>
     </row>
     <row r="4">
@@ -4555,37 +4555,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9.06920919938526e-08</v>
+        <v>4.893527138193985e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>8.884588047470695e-08</v>
+        <v>4.864243055280412e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>9.099472698507534e-08</v>
+        <v>4.923790637316255e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>8.767584431090028e-08</v>
+        <v>4.876975902017694e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>8.767584431090032e-08</v>
+        <v>4.876975902017694e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>9.053549589040402e-08</v>
+        <v>4.908023524042565e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>9.100307315527127e-08</v>
+        <v>4.924625254335853e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>8.867005596840489e-08</v>
+        <v>4.894358684979079e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>9.458033575686877e-08</v>
+        <v>5.282351514495596e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>9.085301453514819e-08</v>
+        <v>4.909619392323538e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>9.099677766848248e-08</v>
+        <v>4.923995705656967e-08</v>
       </c>
     </row>
     <row r="5">
@@ -4595,37 +4595,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.445680985929612e-07</v>
+        <v>5.841744849200283e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>1.521433662079742e-07</v>
+        <v>5.978278798149392e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>1.889614457378732e-07</v>
+        <v>6.648004878022669e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>2.006830891593415e-07</v>
+        <v>6.865903400573023e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>2.006830891593415e-07</v>
+        <v>6.865903400573023e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>1.825269078965855e-07</v>
+        <v>6.527072366578329e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>2.04413022093016e-07</v>
+        <v>6.920640344824545e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>2.006816893763827e-07</v>
+        <v>6.865763422277238e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>5.416510648963076e-07</v>
+        <v>1.315079630471374e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>1.763441314537896e-07</v>
+        <v>6.414263041938559e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>2.063662324215847e-07</v>
+        <v>6.954498098309083e-08</v>
       </c>
     </row>
     <row r="6">
@@ -4635,37 +4635,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.190151430623971e-07</v>
+        <v>4.736296906811927e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>8.117007845816733e-08</v>
+        <v>4.72914894052134e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>8.207285127640818e-08</v>
+        <v>4.766765625694569e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>7.87560974313983e-08</v>
+        <v>4.719988357789109e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>7.976825700726787e-08</v>
+        <v>4.737802366227887e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.188585469589484e-07</v>
+        <v>5.406509220147848e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.288398440199372e-07</v>
+        <v>5.590552417945581e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>7.973652004601712e-08</v>
+        <v>5.392844381084361e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.24711745432363e-07</v>
+        <v>5.141545249662641e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>8.169517502304057e-08</v>
+        <v>4.748441417783804e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>8.206439631819223e-08</v>
+        <v>4.766785794743705e-08</v>
       </c>
     </row>
     <row r="7">
@@ -4675,37 +4675,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.19842865311554e-07</v>
+        <v>5.406580745805493e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.199047860338909e-07</v>
+        <v>5.410879790160043e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2013901198491e-07</v>
+        <v>5.436730050533927e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.179410661168787e-07</v>
+        <v>5.409643802916596e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.179410661168787e-07</v>
+        <v>5.409643802916596e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.196862692081053e-07</v>
+        <v>5.421077131654074e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.201538464729728e-07</v>
+        <v>5.437678861947361e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.178208292861064e-07</v>
+        <v>5.407412292590587e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.237311090745701e-07</v>
+        <v>5.795405122107104e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.200037878528495e-07</v>
+        <v>5.422672999935047e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.201475509861839e-07</v>
+        <v>5.437049313268477e-08</v>
       </c>
     </row>
     <row r="8">
@@ -4715,37 +4715,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.70322839350467e-07</v>
+        <v>6.29502828407622e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.370992962768397e-07</v>
+        <v>7.473503159259401e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.510104107769215e-07</v>
+        <v>7.740066656792464e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.167914924235612e-07</v>
+        <v>7.149411296487101e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>1.704874263793301e-07</v>
+        <v>6.334459738524528e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.367455307039977e-07</v>
+        <v>7.481320122818138e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.372131079699754e-07</v>
+        <v>7.497921853130971e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.348800907819986e-07</v>
+        <v>7.467655283754653e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.408034552985787e-07</v>
+        <v>7.855878404484769e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>1.692470174424957e-07</v>
+        <v>6.289353836016619e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>3.067544455006703e-07</v>
+        <v>8.721330638927218e-08</v>
       </c>
     </row>
     <row r="9">
@@ -4755,37 +4755,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.800842138162895e-07</v>
+        <v>6.466828473743771e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.118245164362386e-07</v>
+        <v>7.02866703647521e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>2.120652781796193e-07</v>
+        <v>7.054632326794038e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>2.462982027092012e-07</v>
+        <v>7.668729394700378e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.097419749131726e-07</v>
+        <v>7.025339788976551e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.116059996104531e-07</v>
+        <v>7.038864377969245e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.120735768753201e-07</v>
+        <v>7.055466108262528e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.097405596884539e-07</v>
+        <v>7.025199538905753e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.156508394769175e-07</v>
+        <v>7.41319236842227e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>1.928242897741613e-07</v>
+        <v>6.704313826805428e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>2.120672813885311e-07</v>
+        <v>7.054836559583641e-08</v>
       </c>
     </row>
   </sheetData>
@@ -4871,34 +4871,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.477941465824339e-08</v>
+        <v>7.477941465824342e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>7.610639860815357e-08</v>
+        <v>7.610639860815361e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.949241750190751e-07</v>
+        <v>1.94924175019075e-07</v>
       </c>
       <c r="E2" t="n">
         <v>7.752914300018178e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>7.260307376560528e-08</v>
+        <v>7.260307376560527e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.330963656393463e-07</v>
+        <v>1.330963656393464e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>8.038921043608389e-08</v>
+        <v>8.038921043608393e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>7.39613140594455e-08</v>
+        <v>7.396131405944551e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>9.52792074331077e-08</v>
+        <v>9.527920743310768e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>9.073601515791852e-08</v>
+        <v>9.073601515791855e-08</v>
       </c>
       <c r="L2" t="n">
         <v>8.477766149972917e-08</v>
@@ -4926,22 +4926,22 @@
         <v>7.979092002363586e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.49170661295964e-07</v>
+        <v>1.491706612959641e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>8.856313557577528e-08</v>
+        <v>8.856313557577534e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>8.108893147047907e-08</v>
+        <v>8.10889314704791e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.043206133612352e-07</v>
+        <v>1.043206133612353e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>9.858832656923554e-08</v>
+        <v>9.858832656923555e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>9.359731333021043e-08</v>
+        <v>9.359731333021046e-08</v>
       </c>
     </row>
     <row r="4">
@@ -4951,37 +4951,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.008907185693141e-07</v>
+        <v>5.385637423259198e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>9.234462441581599e-08</v>
+        <v>5.193866059774508e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>1.723116876384776e-07</v>
+        <v>1.252773433017556e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>9.353359480666584e-08</v>
+        <v>5.214793307232843e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>9.353359480666585e-08</v>
+        <v>5.214793307232843e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>1.350934327629828e-07</v>
+        <v>8.8441623888895e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>1.042389708002231e-07</v>
+        <v>5.720462646350092e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>9.729283662121487e-08</v>
+        <v>5.280170920539308e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>1.077244128825648e-07</v>
+        <v>6.069006854584255e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>1.030184697435606e-07</v>
+        <v>5.598412540683837e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>1.06849765389955e-07</v>
+        <v>5.981542105323281e-08</v>
       </c>
     </row>
     <row r="5">
@@ -4991,37 +4991,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.779939329208776e-07</v>
+        <v>1.02626539694201e-07</v>
       </c>
       <c r="C5" t="n">
-        <v>3.176998416087563e-07</v>
+        <v>9.160117860878702e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>7.290295445930184e-06</v>
+        <v>1.378042477972858e-06</v>
       </c>
       <c r="E5" t="n">
-        <v>3.176998582191045e-07</v>
+        <v>9.160119521913613e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>3.176998582191044e-07</v>
+        <v>9.160119521913613e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>3.822690403982174e-06</v>
+        <v>7.374586873067062e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>7.870556045749002e-07</v>
+        <v>1.773803533566599e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>3.176903310070882e-07</v>
+        <v>9.159166800711932e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>1.10234448430807e-06</v>
+        <v>2.357432001681875e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>5.874440474600832e-07</v>
+        <v>1.41243026622962e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>5.32172959350138e-07</v>
+        <v>1.346723027846053e-07</v>
       </c>
     </row>
     <row r="6">
@@ -5031,37 +5031,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.541236764096477e-07</v>
+        <v>6.32253747617238e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>8.87859065029157e-08</v>
+        <v>5.13123262484685e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.792875747261275e-07</v>
+        <v>1.26505099422529e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>8.819911875616166e-08</v>
+        <v>5.120906529252704e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>9.374235407900801e-08</v>
+        <v>5.218467470406156e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.320515996893068e-07</v>
+        <v>9.781062441802671e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.013517489744282e-07</v>
+        <v>6.74836084003576e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.505257944615484e-07</v>
+        <v>6.217070973452487e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.635736121757294e-07</v>
+        <v>7.051952756817765e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>9.605580254158222e-08</v>
+        <v>5.475869598593029e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.04100152552508e-07</v>
+        <v>5.933148919646436e-08</v>
       </c>
     </row>
     <row r="7">
@@ -5071,37 +5071,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.445471336906472e-07</v>
+        <v>6.153990325231265e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.409587623442157e-07</v>
+        <v>6.049474882678138e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>2.159604925730897e-07</v>
+        <v>1.329595329286205e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>1.408529334062007e-07</v>
+        <v>6.04761366207193e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.408529334062007e-07</v>
+        <v>6.04761366207193e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.78749847884316e-07</v>
+        <v>9.612515290861562e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.478953859215562e-07</v>
+        <v>6.48881554832216e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.409492517425479e-07</v>
+        <v>6.048523822511369e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.513808280038978e-07</v>
+        <v>6.837359756556318e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.466748848648937e-07</v>
+        <v>6.366765442655899e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.505061805112881e-07</v>
+        <v>6.74989500729535e-08</v>
       </c>
     </row>
     <row r="8">
@@ -5111,37 +5111,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.071176063398825e-07</v>
+        <v>7.255230637890621e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.899725140823734e-07</v>
+        <v>8.672116899058664e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>3.829961635668829e-07</v>
+        <v>1.623578108642307e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>2.663163179494407e-07</v>
+        <v>8.25576921806784e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>2.062131237767986e-07</v>
+        <v>7.197953006361223e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>3.278379206891009e-07</v>
+        <v>1.223646535800764e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>2.96983458726317e-07</v>
+        <v>9.112765615467808e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.900373245473333e-07</v>
+        <v>8.672473889657446e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>3.004859039874922e-07</v>
+        <v>9.461609079647821e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>2.076382486710482e-07</v>
+        <v>7.439720639830304e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>3.899691211593168e-07</v>
+        <v>1.096444273986369e-07</v>
       </c>
     </row>
     <row r="9">
@@ -5151,37 +5151,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.97473927386822e-07</v>
+        <v>8.845501879699705e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>3.565309801335261e-07</v>
+        <v>9.843545895211437e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>4.315404889908244e-07</v>
+        <v>1.709016120925487e-07</v>
       </c>
       <c r="E9" t="n">
-        <v>4.288226632761837e-07</v>
+        <v>1.11158808803207e-07</v>
       </c>
       <c r="F9" t="n">
-        <v>3.565310152707916e-07</v>
+        <v>9.843547882320068e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>3.943220656736264e-07</v>
+        <v>1.340658630339485e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>3.634676037108666e-07</v>
+        <v>1.028288656085545e-07</v>
       </c>
       <c r="I9" t="n">
-        <v>3.565214695318586e-07</v>
+        <v>9.842594835044669e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>3.669530457932078e-07</v>
+        <v>1.063143076908961e-07</v>
       </c>
       <c r="K9" t="n">
-        <v>3.259501687530001e-07</v>
+        <v>9.522010421989545e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>3.660783983005988e-07</v>
+        <v>1.054396601982863e-07</v>
       </c>
     </row>
   </sheetData>
@@ -5267,37 +5267,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.314214778163712e-08</v>
+        <v>7.314214778163716e-08</v>
       </c>
       <c r="C2" t="n">
         <v>7.606840292786619e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.855871651087701e-07</v>
+        <v>1.855871651087698e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>7.746708587262094e-08</v>
+        <v>7.746708587262097e-08</v>
       </c>
       <c r="F2" t="n">
         <v>7.260828542904617e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.313817204089991e-07</v>
+        <v>1.31381720408999e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>7.917665847109864e-08</v>
+        <v>7.917665847109863e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>7.397025338599866e-08</v>
+        <v>7.397025338599867e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>9.168020866993604e-08</v>
+        <v>9.168020866993602e-08</v>
       </c>
       <c r="K2" t="n">
         <v>9.035824080858667e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>8.392932186123221e-08</v>
+        <v>8.392932186123218e-08</v>
       </c>
     </row>
     <row r="3">
@@ -5307,19 +5307,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.034667298752555e-08</v>
+        <v>8.034667298752558e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>8.338144406570816e-08</v>
+        <v>8.338144406570814e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>2.096817358288952e-07</v>
+        <v>2.096817358288948e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>8.479218012564772e-08</v>
+        <v>8.479218012564776e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>7.99333796820729e-08</v>
+        <v>7.993337968207293e-08</v>
       </c>
       <c r="G3" t="n">
         <v>1.473342458001166e-07</v>
@@ -5328,16 +5328,16 @@
         <v>8.730461043473848e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>8.12373594692948e-08</v>
+        <v>8.123735946929483e-08</v>
       </c>
       <c r="J3" t="n">
         <v>1.003418347550277e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>9.82963646336486e-08</v>
+        <v>9.829636463364861e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>9.275729888219306e-08</v>
+        <v>9.275729888219308e-08</v>
       </c>
     </row>
     <row r="4">
@@ -5347,37 +5347,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9.757088293834097e-08</v>
+        <v>5.24729099934337e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>9.174073666843454e-08</v>
+        <v>5.183997777512812e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>1.644146810397592e-07</v>
+        <v>1.193167080948518e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>9.277563701025815e-08</v>
+        <v>5.202212845419867e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>9.277563701025817e-08</v>
+        <v>5.202212845419867e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>1.317589060021086e-07</v>
+        <v>8.701767153318416e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>1.01171481862777e-07</v>
+        <v>5.60735089178697e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>9.515980234080049e-08</v>
+        <v>5.243412568872031e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>1.033374841532853e-07</v>
+        <v>5.82395112083779e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>1.004741621477533e-07</v>
+        <v>5.537618920284602e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>1.039986375259292e-07</v>
+        <v>5.890066458102193e-08</v>
       </c>
     </row>
     <row r="5">
@@ -5387,37 +5387,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.783157143740806e-07</v>
+        <v>8.428400015375219e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>3.069325812006412e-07</v>
+        <v>8.971374220757357e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>6.204673129202758e-06</v>
+        <v>1.182402189211097e-06</v>
       </c>
       <c r="E5" t="n">
-        <v>3.069325911762429e-07</v>
+        <v>8.97137521831762e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>3.069325911762429e-07</v>
+        <v>8.97137521831762e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>3.438257694834045e-06</v>
+        <v>6.689614552142816e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>6.737148752079334e-07</v>
+        <v>1.568411456005973e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>3.069233486260351e-07</v>
+        <v>8.970450963296835e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>8.443363338976382e-07</v>
+        <v>1.886553080567127e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>5.236103789351302e-07</v>
+        <v>1.298481629538902e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>9.986274797724978e-07</v>
+        <v>1.463539870233441e-07</v>
       </c>
     </row>
     <row r="6">
@@ -5427,37 +5427,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.481960375475133e-08</v>
+        <v>6.115473377713201e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>8.75425006933005e-08</v>
+        <v>5.110108824750824e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.70083181449048e-07</v>
+        <v>1.203143641614795e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>8.69743194815156e-08</v>
+        <v>5.100109657467255e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>9.192186746847087e-08</v>
+        <v>5.187186501565833e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.290076268185189e-07</v>
+        <v>9.569949531688251e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.548596344012159e-07</v>
+        <v>6.552262371343387e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>9.240852315721076e-08</v>
+        <v>6.111594947241857e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.01991222893297e-07</v>
+        <v>6.732605647418746e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>9.410568909319855e-08</v>
+        <v>5.425533795131775e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.015968060576706e-07</v>
+        <v>5.847794224489899e-08</v>
       </c>
     </row>
     <row r="7">
@@ -5467,37 +5467,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.370939193762837e-07</v>
+        <v>5.942896436881953e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.346920713533485e-07</v>
+        <v>5.939941263871139e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>2.039306201271354e-07</v>
+        <v>1.262715133365446e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>1.345727534407153e-07</v>
+        <v>5.937842090609831e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.345727534407153e-07</v>
+        <v>5.937842090609831e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.712819424400515e-07</v>
+        <v>9.397372590857017e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.406945183007198e-07</v>
+        <v>6.302956329325552e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.346828387787432e-07</v>
+        <v>5.939018006410614e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.42860520591228e-07</v>
+        <v>6.519556558376371e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.399971985856962e-07</v>
+        <v>6.233224357823185e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.43521673963872e-07</v>
+        <v>6.585671895640773e-08</v>
       </c>
     </row>
     <row r="8">
@@ -5507,37 +5507,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.943206689976052e-07</v>
+        <v>6.950087224759639e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.708274144739043e-07</v>
+        <v>8.335923289843774e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>3.565431693850358e-07</v>
+        <v>1.531313218603923e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>2.492295258415203e-07</v>
+        <v>7.955801273929468e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>1.943559933578483e-07</v>
+        <v>6.990027107449991e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>3.075066526047401e-07</v>
+        <v>1.179492747676413e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>2.769192284653637e-07</v>
+        <v>8.700511215231884e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.709075489434324e-07</v>
+        <v>8.336572892317737e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.791007561089516e-07</v>
+        <v>8.917384690495421e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>1.957565205306656e-07</v>
+        <v>7.214588418737019e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>3.622663596133463e-07</v>
+        <v>1.043557834221039e-07</v>
       </c>
     </row>
     <row r="9">
@@ -5547,37 +5547,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.62431719727983e-07</v>
+        <v>8.148841711118714e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>3.132503179748519e-07</v>
+        <v>9.082566387380952e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>3.824961180342575e-07</v>
+        <v>1.576990407979048e-07</v>
       </c>
       <c r="E9" t="n">
-        <v>3.746657560571483e-07</v>
+        <v>1.016347891376201e-07</v>
       </c>
       <c r="F9" t="n">
-        <v>3.132503458808938e-07</v>
+        <v>9.082567700516951e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>3.498401890615553e-07</v>
+        <v>1.253999771436683e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>3.192527649222233e-07</v>
+        <v>9.445581452835366e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>3.13241085400247e-07</v>
+        <v>9.081643129920426e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>3.21418767212731e-07</v>
+        <v>9.662181681886189e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.515413636408018e-07</v>
+        <v>8.196401652155359e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>3.220799205853755e-07</v>
+        <v>9.728297019150595e-08</v>
       </c>
     </row>
   </sheetData>
@@ -5663,7 +5663,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.228273434517552e-08</v>
+        <v>7.228273434517538e-08</v>
       </c>
       <c r="C2" t="n">
         <v>7.630860717897071e-08</v>
@@ -5672,28 +5672,28 @@
         <v>1.678669485437351e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>7.762813723627719e-08</v>
+        <v>7.762813723627725e-08</v>
       </c>
       <c r="F2" t="n">
         <v>7.300436776257855e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.231727602926512e-07</v>
+        <v>1.231727602926511e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>7.852823702956854e-08</v>
+        <v>7.85282370295685e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>7.423343876668433e-08</v>
+        <v>7.423343876668437e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>8.575272583266639e-08</v>
+        <v>8.575272583266635e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>8.891880891616993e-08</v>
+        <v>8.891880891616994e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>8.17710284784951e-08</v>
+        <v>8.177102847849522e-08</v>
       </c>
     </row>
     <row r="3">
@@ -5703,37 +5703,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.94072898379474e-08</v>
+        <v>7.940728983794723e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>8.371131815631627e-08</v>
+        <v>8.371131815631629e-08</v>
       </c>
       <c r="D3" t="n">
         <v>1.893489363766117e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>8.504212621983474e-08</v>
+        <v>8.504212621983472e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>8.041835674613602e-08</v>
+        <v>8.04183567461361e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.379413615146608e-07</v>
+        <v>1.37941361514661e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>8.660685463197811e-08</v>
+        <v>8.660685463197803e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>8.159518788957786e-08</v>
+        <v>8.159518788957798e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>9.361913437034007e-08</v>
+        <v>9.361913437033989e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>9.66824461113551e-08</v>
+        <v>9.668244611135502e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>9.032348073045509e-08</v>
+        <v>9.0323480730455e-08</v>
       </c>
     </row>
     <row r="4">
@@ -5743,37 +5743,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9.654506639674028e-08</v>
+        <v>5.191951935040643e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>9.258623620314766e-08</v>
+        <v>5.216661762423479e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>1.533658314910555e-07</v>
+        <v>1.087402844447217e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>9.35636896364775e-08</v>
+        <v>5.233865424467053e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>9.356368963647752e-08</v>
+        <v>5.233865424467052e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>1.263988193840741e-07</v>
+        <v>8.210139823929859e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>1.002693075159151e-07</v>
+        <v>5.564376046958116e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>9.502990774702785e-08</v>
+        <v>5.259006779002646e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>9.948101320117812e-08</v>
+        <v>5.485546615484415e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>9.907428683314556e-08</v>
+        <v>5.444873978681149e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>1.021989473207356e-07</v>
+        <v>5.757340027440159e-08</v>
       </c>
     </row>
     <row r="5">
@@ -5783,37 +5783,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.54787630875863e-07</v>
+        <v>7.977021054781959e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>3.386675453613366e-07</v>
+        <v>9.547692780139447e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>5.110879889906009e-06</v>
+        <v>9.812627539978979e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>3.386675512073338e-07</v>
+        <v>9.547693364739171e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>3.386675512073338e-07</v>
+        <v>9.547693364739171e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>2.944212799512583e-06</v>
+        <v>5.78036656054636e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>6.437444757125307e-07</v>
+        <v>1.512953895538872e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>3.386594919346452e-07</v>
+        <v>9.546887437470277e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>5.472387711144784e-07</v>
+        <v>1.336608311205698e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>4.55313576490073e-07</v>
+        <v>1.171468544266947e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>8.784171650769881e-07</v>
+        <v>1.941878058592438e-07</v>
       </c>
     </row>
     <row r="6">
@@ -5823,37 +5823,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.314116918740573e-08</v>
+        <v>5.132043344480967e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>8.750961731384267e-08</v>
+        <v>5.127313270455857e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>2.027044382970881e-07</v>
+        <v>1.174238791955305e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>8.695215804407244e-08</v>
+        <v>5.117502469071261e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>9.123985837174311e-08</v>
+        <v>5.192965994429356e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.229949221747394e-07</v>
+        <v>8.150231233370174e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.509634154012779e-07</v>
+        <v>6.456592340905938e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.415455001827197e-07</v>
+        <v>6.077681201434756e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.48056339332673e-07</v>
+        <v>5.448015292097285e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>9.246035927381792e-08</v>
+        <v>5.328468854267736e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>9.895946841959796e-08</v>
+        <v>5.700325199089085e-08</v>
       </c>
     </row>
     <row r="7">
@@ -5863,37 +5863,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.345519818105774e-07</v>
+        <v>5.860873642699554e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.330448765875556e-07</v>
+        <v>5.928733829330632e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.91365653928017e-07</v>
+        <v>1.154282531573875e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>1.32928545900757e-07</v>
+        <v>5.926686890964251e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.32928545900757e-07</v>
+        <v>5.926686890964251e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.644057347979111e-07</v>
+        <v>8.879061531588738e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.382762229297522e-07</v>
+        <v>6.233297754617023e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.330368231608649e-07</v>
+        <v>5.927928486661558e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.374879286150152e-07</v>
+        <v>6.154468323143326e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.370812022469825e-07</v>
+        <v>6.113795686340058e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.402058627345727e-07</v>
+        <v>6.426261735099077e-08</v>
       </c>
     </row>
     <row r="8">
@@ -5903,37 +5903,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.89996360721396e-07</v>
+        <v>6.836694706242371e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.649963248611095e-07</v>
+        <v>8.251079306361294e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>3.392934445290702e-07</v>
+        <v>1.414635441620977e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>2.440556199651741e-07</v>
+        <v>7.88252338390009e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>1.908520052081671e-07</v>
+        <v>6.946139769250664e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.964441583101098e-07</v>
+        <v>1.120293777281127e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>2.703146464419036e-07</v>
+        <v>8.557173995838723e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.650752466730632e-07</v>
+        <v>8.251804727884079e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.695414050416934e-07</v>
+        <v>8.47860949565925e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>1.91102807454246e-07</v>
+        <v>7.06457593283599e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>3.522531705178046e-07</v>
+        <v>1.015829433186153e-07</v>
       </c>
     </row>
     <row r="9">
@@ -5943,37 +5943,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.416960525446259e-07</v>
+        <v>7.746609277400745e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.878244520590558e-07</v>
+        <v>8.652854342868096e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>3.461524602569789e-07</v>
+        <v>1.426707309236685e-07</v>
       </c>
       <c r="E9" t="n">
-        <v>3.427949657939429e-07</v>
+        <v>9.620335861069904e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.878244745583226e-07</v>
+        <v>8.652855220565379e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>3.191853102694116e-07</v>
+        <v>1.160318204512621e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>2.930557984012523e-07</v>
+        <v>8.9574182681545e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.878163986323652e-07</v>
+        <v>8.652049000199029e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.922675040865152e-07</v>
+        <v>8.878588836680798e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.642606371865772e-07</v>
+        <v>8.352153729148155e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>2.949854382060728e-07</v>
+        <v>9.150382248636543e-08</v>
       </c>
     </row>
   </sheetData>
@@ -6059,34 +6059,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.010198369925726e-08</v>
+        <v>7.010198369925728e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>7.25949442836547e-08</v>
+        <v>7.259494428365472e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>9.962623415853236e-08</v>
+        <v>9.962623415853243e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>7.386272452973239e-08</v>
+        <v>7.386272452973236e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>6.938708226252295e-08</v>
+        <v>6.938708226252291e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>8.375405908324885e-08</v>
+        <v>8.375405908324879e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>7.235590776077556e-08</v>
+        <v>7.235590776077554e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>7.004075342797719e-08</v>
+        <v>7.004075342797718e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>8.195290877166224e-08</v>
+        <v>8.195290877166216e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>8.57647916325454e-08</v>
+        <v>8.576479163254537e-08</v>
       </c>
       <c r="L2" t="n">
         <v>1.167799342743018e-07</v>
@@ -6099,34 +6099,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.6628995995983e-08</v>
+        <v>7.662899599598296e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>7.90998878087708e-08</v>
+        <v>7.909988780877079e-08</v>
       </c>
       <c r="D3" t="n">
         <v>1.105879999542071e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>8.037785466298597e-08</v>
+        <v>8.037785466298594e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>7.590221239577652e-08</v>
+        <v>7.590221239577649e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>9.233171070646925e-08</v>
+        <v>9.233171070646926e-08</v>
       </c>
       <c r="H3" t="n">
         <v>7.92352598792179e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>7.652467602130589e-08</v>
+        <v>7.652467602130585e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>8.894826625630826e-08</v>
+        <v>8.894826625630819e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>9.272829857187713e-08</v>
+        <v>9.272829857187708e-08</v>
       </c>
       <c r="L3" t="n">
         <v>1.303167311170781e-07</v>
@@ -6139,37 +6139,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9.265659558066544e-08</v>
+        <v>5.038288483321616e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>8.715746511980677e-08</v>
+        <v>4.937627805755003e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>1.102075114300891e-07</v>
+        <v>6.793380068263977e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>8.816492791724197e-08</v>
+        <v>4.95536029947802e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>8.816492791724196e-08</v>
+        <v>4.95536029947802e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>1.004014455880389e-07</v>
+        <v>5.843321662536783e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>9.4000157137727e-08</v>
+        <v>5.172644639027768e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>9.011544750879896e-08</v>
+        <v>4.989417237455132e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>9.451011167431546e-08</v>
+        <v>5.223640092686615e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>9.438406042012434e-08</v>
+        <v>5.211034967267504e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>1.203994138751091e-07</v>
+        <v>7.812570312765974e-08</v>
       </c>
     </row>
     <row r="5">
@@ -6179,37 +6179,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.649942990850666e-07</v>
+        <v>8.071432048563672e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>2.456846954832733e-07</v>
+        <v>7.727707045033685e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>1.792137235498114e-06</v>
+        <v>3.639534305145984e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>2.456847094224027e-07</v>
+        <v>7.727708438946591e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>2.456847094224027e-07</v>
+        <v>7.727708438946591e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>1.022570619209968e-06</v>
+        <v>2.207349903033788e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>4.207513799249784e-07</v>
+        <v>1.092346612892197e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>2.456814059436651e-07</v>
+        <v>7.727378091072851e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>4.687579186347124e-07</v>
+        <v>1.181040145949855e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>4.198116894258534e-07</v>
+        <v>1.093856120673313e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>7.818084194522708e-07</v>
+        <v>6.419524863487127e-07</v>
       </c>
     </row>
     <row r="6">
@@ -6219,37 +6219,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.486952277063361e-08</v>
+        <v>4.901236002607687e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>8.053790320613381e-08</v>
+        <v>4.821123516705647e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.050393875761931e-07</v>
+        <v>7.455466049710182e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>8.010987394295954e-08</v>
+        <v>4.813591350298838e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>8.215707153100579e-08</v>
+        <v>4.849622027653215e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.362007667798648e-07</v>
+        <v>5.706269181822856e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.343262905111064e-07</v>
+        <v>5.882384582553446e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.259147687006248e-07</v>
+        <v>4.852364756741204e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.317457549356316e-07</v>
+        <v>5.878987410534709e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>8.57021762719773e-08</v>
+        <v>5.058233807088085e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.135616008091694e-07</v>
+        <v>7.69222480345754e-08</v>
       </c>
     </row>
     <row r="7">
@@ -6259,37 +6259,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.252073200506458e-07</v>
+        <v>5.611181230888991e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.226694615183877e-07</v>
+        <v>5.562638938983344e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.427506621002713e-07</v>
+        <v>7.366139516955631e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.226348666525347e-07</v>
+        <v>5.562031217931865e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.226348666525347e-07</v>
+        <v>5.562031217931865e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.329521700580194e-07</v>
+        <v>6.416214410104162e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.265508816077074e-07</v>
+        <v>5.745537386595147e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.226661719787795e-07</v>
+        <v>5.562309985022509e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.270608361442959e-07</v>
+        <v>5.796532840253992e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.269347848901047e-07</v>
+        <v>5.783927714834879e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.529501383450895e-07</v>
+        <v>8.38546306033336e-08</v>
       </c>
     </row>
     <row r="8">
@@ -6299,37 +6299,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.780908964177512e-07</v>
+        <v>6.541932169906671e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.465783718132553e-07</v>
+        <v>7.74343574832042e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.814059028874667e-07</v>
+        <v>9.806471741587081e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.271497178611226e-07</v>
+        <v>7.401492589235704e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>1.77788611359713e-07</v>
+        <v>6.532737119518335e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.568703493757607e-07</v>
+        <v>8.597174354278657e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.504690609254376e-07</v>
+        <v>7.926497330769442e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.465843512965208e-07</v>
+        <v>7.743269929196999e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.509929757922787e-07</v>
+        <v>7.977738486239404e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>1.784988570357722e-07</v>
+        <v>6.69145537968109e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>3.510699002622909e-07</v>
+        <v>1.187237085118193e-07</v>
       </c>
     </row>
     <row r="9">
@@ -6339,37 +6339,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.246806319154834e-07</v>
+        <v>7.361911510223613e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.659453934145173e-07</v>
+        <v>8.084295326691364e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>2.860342392650899e-07</v>
+        <v>9.887930461391841e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>3.164927804713257e-07</v>
+        <v>8.973930482654859e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.659454183622656e-07</v>
+        <v>8.084296914355962e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.762281019541488e-07</v>
+        <v>8.93787079781218e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.698268135038372e-07</v>
+        <v>8.267193774303162e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.659421038749088e-07</v>
+        <v>8.083966372730534e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.703367680404252e-07</v>
+        <v>8.318189227962008e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.15055380903619e-07</v>
+        <v>7.858907016738739e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>2.962260702412191e-07</v>
+        <v>1.090711944804137e-07</v>
       </c>
     </row>
   </sheetData>
@@ -6455,34 +6455,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.066168539526611e-08</v>
+        <v>7.066168539526616e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>7.351568982881217e-08</v>
+        <v>7.351568982881216e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>7.207479117662656e-08</v>
+        <v>7.207479117662667e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>7.474272068678224e-08</v>
+        <v>7.474272068678219e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>7.038423990045544e-08</v>
+        <v>7.03842399004554e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>7.228840844812314e-08</v>
+        <v>7.228840844812318e-08</v>
       </c>
       <c r="H2" t="n">
         <v>6.920640476224364e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>7.083946823641139e-08</v>
+        <v>7.083946823641146e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>8.429872081344551e-08</v>
+        <v>8.429872081344552e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>8.67975146438619e-08</v>
+        <v>8.679751464386184e-08</v>
       </c>
       <c r="L2" t="n">
         <v>6.806235728109338e-08</v>
@@ -6495,22 +6495,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.735065155874751e-08</v>
+        <v>7.735065155874761e-08</v>
       </c>
       <c r="C3" t="n">
         <v>8.022056789677593e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>7.89760159312928e-08</v>
+        <v>7.897601593129287e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>8.145612816229677e-08</v>
+        <v>8.145612816229687e-08</v>
       </c>
       <c r="F3" t="n">
         <v>7.709764737597e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>7.922172004419831e-08</v>
+        <v>7.922172004419847e-08</v>
       </c>
       <c r="H3" t="n">
         <v>7.569022567096964e-08</v>
@@ -6519,13 +6519,13 @@
         <v>7.753033680793419e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>9.173181304176583e-08</v>
+        <v>9.173181304176581e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>9.397232045343078e-08</v>
+        <v>9.397232045343072e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>7.436110965057935e-08</v>
+        <v>7.436110965057936e-08</v>
       </c>
     </row>
     <row r="4">
@@ -6535,37 +6535,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9.009679392172855e-08</v>
+        <v>5.026599594819931e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>8.70267476555105e-08</v>
+        <v>4.980536710163577e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>9.093682543037601e-08</v>
+        <v>5.110602745684682e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>8.782996682495357e-08</v>
+        <v>4.994673873173852e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>8.782996682495357e-08</v>
+        <v>4.994673873173852e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>9.074578226125122e-08</v>
+        <v>5.117704066631075e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>8.923340959489053e-08</v>
+        <v>4.940261162136135e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>8.804467874722548e-08</v>
+        <v>4.9983228695038e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>9.304173639676029e-08</v>
+        <v>5.321093842323103e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>9.201954582819086e-08</v>
+        <v>5.218874785466166e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>8.855446579855056e-08</v>
+        <v>4.872366782502136e-08</v>
       </c>
     </row>
     <row r="5">
@@ -6575,37 +6575,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.155635472497115e-07</v>
+        <v>8.994814431890248e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>3.019266462428118e-07</v>
+        <v>8.762774904805633e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>3.707447584579337e-07</v>
+        <v>1.003522234028512e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>3.019266523800047e-07</v>
+        <v>8.762775518524904e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>3.019266523800047e-07</v>
+        <v>8.762775518524904e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>3.937734679647658e-07</v>
+        <v>1.045099130611394e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>2.54145533374254e-07</v>
+        <v>7.842714524925685e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>3.019250755173663e-07</v>
+        <v>8.762617832261054e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>5.90247785794061e-07</v>
+        <v>1.407192026429833e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>4.672954776626219e-07</v>
+        <v>1.182373114996304e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>3.340089074605708e-07</v>
+        <v>9.192364932345316e-08</v>
       </c>
     </row>
     <row r="6">
@@ -6615,37 +6615,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.225669581699957e-08</v>
+        <v>5.533995905920246e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>7.962145852618649e-08</v>
+        <v>4.850203622193701e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>8.330122571424514e-08</v>
+        <v>4.976213006242229e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>7.920009588223616e-08</v>
+        <v>4.842788145405034e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>8.01648120626766e-08</v>
+        <v>4.859767150088785e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>8.29056841565223e-08</v>
+        <v>4.979718340735536e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.216213454355415e-07</v>
+        <v>4.801422541513149e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>8.02045806424966e-08</v>
+        <v>4.860337143608259e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>8.605787025203019e-08</v>
+        <v>5.843690350157736e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>8.417785503663051e-08</v>
+        <v>5.080861028282545e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>8.081370242500678e-08</v>
+        <v>4.736129347865982e-08</v>
       </c>
     </row>
     <row r="7">
@@ -6655,37 +6655,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.175109303121425e-07</v>
+        <v>5.5090883926768e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.154603858630851e-07</v>
+        <v>5.48096873990525e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.18343861137933e-07</v>
+        <v>5.592966571523947e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.154460081262055e-07</v>
+        <v>5.480716197442216e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.154460081262055e-07</v>
+        <v>5.480716197442216e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.18159918651665e-07</v>
+        <v>5.600192864487944e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.166475459853044e-07</v>
+        <v>5.422749959993002e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.154588151376393e-07</v>
+        <v>5.480811667360664e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.20455872787174e-07</v>
+        <v>5.803582640179969e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.194336822186047e-07</v>
+        <v>5.701363583323032e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.159686021889644e-07</v>
+        <v>5.354855580359002e-08</v>
       </c>
     </row>
     <row r="8">
@@ -6695,37 +6695,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.641014515294889e-07</v>
+        <v>6.329081561658875e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.24075856025088e-07</v>
+        <v>7.392601004398115e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.398184474447818e-07</v>
+        <v>7.730919278939764e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.071117084239241e-07</v>
+        <v>7.094032513940137e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>1.640124203857991e-07</v>
+        <v>6.335485048579408e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.267677177099115e-07</v>
+        <v>7.51169011755544e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.252553450435414e-07</v>
+        <v>7.33424721306033e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.240666141958858e-07</v>
+        <v>7.392308920428155e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.290758600140469e-07</v>
+        <v>7.71529440501412e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>1.648722006580416e-07</v>
+        <v>6.501081503523767e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>2.893586337537645e-07</v>
+        <v>8.406520119363715e-08</v>
       </c>
     </row>
     <row r="9">
@@ -6735,37 +6735,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.908933388806305e-07</v>
+        <v>6.800618776483898e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.232454186612035e-07</v>
+        <v>7.377985306872947e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>2.261360436452284e-07</v>
+        <v>7.490108973372475e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>2.629453852020467e-07</v>
+        <v>8.076705219910379e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.232454385402888e-07</v>
+        <v>7.377986162449524e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.259449514497835e-07</v>
+        <v>7.497209431455646e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.24432578783423e-07</v>
+        <v>7.319766526960706e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.232438479357578e-07</v>
+        <v>7.377828234328368e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.282409055852925e-07</v>
+        <v>7.700599207147671e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.064770112747727e-07</v>
+        <v>7.233326166410492e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>2.237536349870829e-07</v>
+        <v>7.2518721473267e-08</v>
       </c>
     </row>
   </sheetData>
@@ -6851,37 +6851,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.298456393562655e-08</v>
+        <v>7.298456393562656e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>7.77145086761941e-08</v>
+        <v>7.771450867619412e-08</v>
       </c>
       <c r="D2" t="n">
         <v>7.024086202471419e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>7.888840940847023e-08</v>
+        <v>7.888840940847024e-08</v>
       </c>
       <c r="F2" t="n">
         <v>7.469304925050069e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>7.14222831321211e-08</v>
+        <v>7.142228313212111e-08</v>
       </c>
       <c r="H2" t="n">
         <v>6.893653115962936e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>7.501124745562658e-08</v>
+        <v>7.50112474556266e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>8.598414254427408e-08</v>
+        <v>8.598414254427412e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>8.543491209774295e-08</v>
+        <v>8.543491209774297e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>6.892624499789766e-08</v>
+        <v>6.892624499789767e-08</v>
       </c>
     </row>
     <row r="3">
@@ -6897,31 +6897,31 @@
         <v>8.516704174234375e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>7.698689927680898e-08</v>
+        <v>7.698689927680899e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>8.63488810232601e-08</v>
+        <v>8.634888102326013e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>8.215352086529057e-08</v>
+        <v>8.215352086529059e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>7.834577828097197e-08</v>
+        <v>7.834577828097203e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>7.549966234102657e-08</v>
+        <v>7.549966234102658e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>8.245276052861086e-08</v>
+        <v>8.245276052861089e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>9.381348801508421e-08</v>
+        <v>9.381348801508423e-08</v>
       </c>
       <c r="K3" t="n">
         <v>9.252641981615056e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>7.547489466122448e-08</v>
+        <v>7.547489466122447e-08</v>
       </c>
     </row>
     <row r="4">
@@ -6931,37 +6931,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9.237677065574921e-08</v>
+        <v>5.182140932460063e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>9.148594143657101e-08</v>
+        <v>5.265047227199603e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>9.074575613022361e-08</v>
+        <v>5.019039479907524e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>9.224019618783163e-08</v>
+        <v>5.278322271283739e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>9.224019618783163e-08</v>
+        <v>5.278322271283739e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>9.115694410282773e-08</v>
+        <v>5.084146302726175e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>8.997196390764201e-08</v>
+        <v>4.941660257649306e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>9.160162636247996e-08</v>
+        <v>5.267011849840305e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>9.503304095680286e-08</v>
+        <v>5.44776796256541e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>9.211298501547246e-08</v>
+        <v>5.155762368432319e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>8.996668543130956e-08</v>
+        <v>4.94113241001607e-08</v>
       </c>
     </row>
     <row r="5">
@@ -6971,37 +6971,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.331223154315986e-07</v>
+        <v>1.117926248801898e-07</v>
       </c>
       <c r="C5" t="n">
-        <v>5.145568553962062e-07</v>
+        <v>1.271109527254194e-07</v>
       </c>
       <c r="D5" t="n">
-        <v>2.882763426782181e-07</v>
+        <v>8.49557778431424e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>5.145568573444327e-07</v>
+        <v>1.271109546736465e-07</v>
       </c>
       <c r="F5" t="n">
-        <v>5.145568573444327e-07</v>
+        <v>1.271109546736465e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>3.542380331834562e-07</v>
+        <v>9.71437344545594e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>2.416024053042361e-07</v>
+        <v>7.610356011768763e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>5.145559885024667e-07</v>
+        <v>1.271100858316802e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>6.97235772038232e-07</v>
+        <v>1.604653597216805e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>3.935484818424284e-07</v>
+        <v>1.046102708383964e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>3.635221825861792e-07</v>
+        <v>7.6963824860143e-08</v>
       </c>
     </row>
     <row r="6">
@@ -7011,37 +7011,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.502218019951444e-08</v>
+        <v>5.052700141131707e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>8.418026685774151e-08</v>
+        <v>5.136467355308936e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.205121397861462e-07</v>
+        <v>4.885924138248339e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>8.371333336771194e-08</v>
+        <v>5.128249486462815e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>8.42808672171468e-08</v>
+        <v>5.138238082158744e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>8.380235364659124e-08</v>
+        <v>5.59370070858617e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.22293613472528e-07</v>
+        <v>5.510521286908875e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>8.424703590624482e-08</v>
+        <v>5.13757105851195e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>8.854493052693901e-08</v>
+        <v>5.969773115895344e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>8.455190804953016e-08</v>
+        <v>5.022687414552815e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>8.251126534421718e-08</v>
+        <v>4.809917017194249e-08</v>
       </c>
     </row>
     <row r="7">
@@ -7051,37 +7051,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.197617055071904e-07</v>
+        <v>5.664115783233788e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.189874281076608e-07</v>
+        <v>5.74907338998804e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.181235510788281e-07</v>
+        <v>5.500888668392026e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.189836662542557e-07</v>
+        <v>5.749007341902348e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.189836662542557e-07</v>
+        <v>5.749007341902348e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.185418789542694e-07</v>
+        <v>5.566121153499902e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.173568987590833e-07</v>
+        <v>5.423635108423039e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.189865612139207e-07</v>
+        <v>5.748986700614032e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.224179758082441e-07</v>
+        <v>5.929742813339138e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.194979198669116e-07</v>
+        <v>5.637737219206051e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.173516202827508e-07</v>
+        <v>5.423107260789793e-08</v>
       </c>
     </row>
     <row r="8">
@@ -7091,37 +7091,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.660081723338189e-07</v>
+        <v>6.478053594972028e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.270094392385262e-07</v>
+        <v>7.65026077562245e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.389407387045648e-07</v>
+        <v>7.627271159082927e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.101151838137696e-07</v>
+        <v>7.352922042258814e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>1.671935351308983e-07</v>
+        <v>6.597501029533608e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.265460619209752e-07</v>
+        <v>7.466994763413881e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.25361081725786e-07</v>
+        <v>7.324508718336932e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.269907441806287e-07</v>
+        <v>7.64986031052801e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.304342959321985e-07</v>
+        <v>7.830830037219506e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>1.645972054074657e-07</v>
+        <v>6.431484640418796e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>2.898669018552793e-07</v>
+        <v>8.459376200013994e-08</v>
       </c>
     </row>
     <row r="9">
@@ -7131,37 +7131,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.874896649851017e-07</v>
+        <v>6.856127863586008e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.1953642346813e-07</v>
+        <v>7.518735698743201e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>2.186797319482826e-07</v>
+        <v>7.270677442104621e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>2.574112650418978e-07</v>
+        <v>8.185333067363361e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.195364405431173e-07</v>
+        <v>7.518736159796853e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.190908743147369e-07</v>
+        <v>7.335783462255062e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.179058941195506e-07</v>
+        <v>7.193297417178195e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.195355565743899e-07</v>
+        <v>7.518649009369192e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.22966971168711e-07</v>
+        <v>7.699405122094301e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.010302973206428e-07</v>
+        <v>7.059128125627387e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>2.17900615643218e-07</v>
+        <v>7.192769569544953e-08</v>
       </c>
     </row>
   </sheetData>
@@ -7247,10 +7247,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.359981867394295e-08</v>
+        <v>7.359981867394297e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>7.510235281877163e-08</v>
+        <v>7.510235281877167e-08</v>
       </c>
       <c r="D2" t="n">
         <v>1.883421453113034e-07</v>
@@ -7265,19 +7265,19 @@
         <v>1.217688078045667e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>8.008908364305737e-08</v>
+        <v>8.008908364305739e-08</v>
       </c>
       <c r="I2" t="n">
         <v>7.294211728330266e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>8.47937320313639e-08</v>
+        <v>8.479373203136393e-08</v>
       </c>
       <c r="K2" t="n">
         <v>8.961365637163067e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>8.21819631207092e-08</v>
+        <v>8.218196312070921e-08</v>
       </c>
     </row>
     <row r="3">
@@ -7287,16 +7287,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.069579665166969e-08</v>
+        <v>8.069579665166972e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>8.208326429354267e-08</v>
+        <v>8.208326429354268e-08</v>
       </c>
       <c r="D3" t="n">
         <v>2.126732410859906e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>8.345314663541831e-08</v>
+        <v>8.345314663541832e-08</v>
       </c>
       <c r="F3" t="n">
         <v>7.87148445251131e-08</v>
@@ -7305,19 +7305,19 @@
         <v>1.361001123279249e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>8.817553022100135e-08</v>
+        <v>8.817553022100138e-08</v>
       </c>
       <c r="I3" t="n">
         <v>7.988249120016346e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>9.226312039720193e-08</v>
+        <v>9.226312039720197e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>9.72488613065926e-08</v>
+        <v>9.724886130659257e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>9.056962234499873e-08</v>
+        <v>9.056962234499874e-08</v>
       </c>
     </row>
     <row r="4">
@@ -7327,37 +7327,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9.877244908462552e-08</v>
+        <v>5.297225752257066e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>9.09041931753946e-08</v>
+        <v>5.12532729816905e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>1.669819002257207e-07</v>
+        <v>1.211817086636662e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>9.205154082813394e-08</v>
+        <v>5.145521935899711e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>9.205154082813394e-08</v>
+        <v>5.145521935899709e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>1.269631877157292e-07</v>
+        <v>8.152859202870292e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>1.026409124584592e-07</v>
+        <v>5.684072089640446e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>9.540312217293274e-08</v>
+        <v>5.203841083669049e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>1.002502525974014e-07</v>
+        <v>5.445006103534648e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>1.009064858360298e-07</v>
+        <v>5.51062942739749e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>1.038872179160791e-07</v>
+        <v>5.808702635402427e-08</v>
       </c>
     </row>
     <row r="5">
@@ -7367,37 +7367,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.474921539711231e-07</v>
+        <v>9.674692534539691e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>2.967402004383297e-07</v>
+        <v>8.748041006366656e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>6.633989514749824e-06</v>
+        <v>1.259375042652487e-06</v>
       </c>
       <c r="E5" t="n">
-        <v>2.967402164474544e-07</v>
+        <v>8.748042607279114e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>2.967402164474543e-07</v>
+        <v>8.748042607279114e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>3.103597058024359e-06</v>
+        <v>6.05416150364282e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>7.713732847440864e-07</v>
+        <v>1.745376177809222e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>2.967321013554795e-07</v>
+        <v>8.747231098081648e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>5.168236308623958e-07</v>
+        <v>1.277669752127102e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>5.499842096879267e-07</v>
+        <v>1.34143973243635e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>9.761698833200779e-07</v>
+        <v>2.116087746332546e-07</v>
       </c>
     </row>
     <row r="6">
@@ -7407,37 +7407,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.454059245754e-08</v>
+        <v>5.222745076023946e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>8.654796108308262e-08</v>
+        <v>5.048657613759799e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.728399623197542e-07</v>
+        <v>1.2221272758663e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>8.601962085443444e-08</v>
+        <v>5.039360144937851e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>9.074509502831532e-08</v>
+        <v>5.122528489947494e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.758851267706207e-07</v>
+        <v>9.013885325570819e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.567033150085057e-07</v>
+        <v>6.635570369365473e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>9.117126554584723e-08</v>
+        <v>6.064867206369585e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.516045021270527e-07</v>
+        <v>6.348840890358992e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>9.346840308557184e-08</v>
+        <v>5.379719171698783e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>9.990757800548782e-08</v>
+        <v>5.738660973355552e-08</v>
       </c>
     </row>
     <row r="7">
@@ -7447,37 +7447,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.393524997822488e-07</v>
+        <v>6.011434640665222e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.359912719534062e-07</v>
+        <v>5.918859880362216e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>2.075543578694319e-07</v>
+        <v>1.283224611702661e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>1.359014247652084e-07</v>
+        <v>5.917279889010372e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.359014247652084e-07</v>
+        <v>5.917279889010372e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.675432384133526e-07</v>
+        <v>8.867068091278443e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.432209631560825e-07</v>
+        <v>6.398280978048597e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.35983172870556e-07</v>
+        <v>5.918049972077206e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.408303032950247e-07</v>
+        <v>6.159214991942807e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.41486536533653e-07</v>
+        <v>6.224838315805648e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.444672686137024e-07</v>
+        <v>6.522911523810585e-08</v>
       </c>
     </row>
     <row r="8">
@@ -7487,37 +7487,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.99298024647833e-07</v>
+        <v>7.066475872582657e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.781534240730124e-07</v>
+        <v>8.42091374414602e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>3.668445621104842e-07</v>
+        <v>1.563575369647805e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>2.556555931852975e-07</v>
+        <v>8.024953241783297e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>1.98495773176291e-07</v>
+        <v>7.018940415075965e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>3.09765278241115e-07</v>
+        <v>1.137017597868372e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>2.854430029838259e-07</v>
+        <v>8.901388865453536e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.782052126983187e-07</v>
+        <v>8.42115785948248e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.830685128076037e-07</v>
+        <v>8.662607465799305e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>1.99903732890917e-07</v>
+        <v>7.252980966122392e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>3.726340081672054e-07</v>
+        <v>1.053864611819257e-07</v>
       </c>
     </row>
     <row r="9">
@@ -7527,37 +7527,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.805661912849118e-07</v>
+        <v>8.496795597644911e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>3.35491088132576e-07</v>
+        <v>9.430056626089829e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>4.070619123037384e-07</v>
+        <v>1.634357905604391e-07</v>
       </c>
       <c r="E9" t="n">
-        <v>4.027522077109406e-07</v>
+        <v>1.061385364340638e-07</v>
       </c>
       <c r="F9" t="n">
-        <v>3.354911203810517e-07</v>
+        <v>9.430058512814867e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>3.670430545925226e-07</v>
+        <v>1.237826483700606e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>3.427207793352528e-07</v>
+        <v>9.909477723776212e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>3.354829890497262e-07</v>
+        <v>9.429246717804813e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>3.403301194741947e-07</v>
+        <v>9.670411737670416e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>3.058450601951229e-07</v>
+        <v>9.141662851615491e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>3.439670847928722e-07</v>
+        <v>1.003410826953819e-07</v>
       </c>
     </row>
   </sheetData>
@@ -7646,16 +7646,16 @@
         <v>7.044821442145308e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>7.425726287923822e-08</v>
+        <v>7.425726287923821e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.592524333916831e-07</v>
+        <v>1.592524333916835e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>7.555171712163269e-08</v>
+        <v>7.555171712163268e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>7.09986761491248e-08</v>
+        <v>7.099867614912481e-08</v>
       </c>
       <c r="G2" t="n">
         <v>9.514312942832905e-08</v>
@@ -7664,16 +7664,16 @@
         <v>7.206665580789734e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>7.182534700940733e-08</v>
+        <v>7.182534700940732e-08</v>
       </c>
       <c r="J2" t="n">
         <v>8.495843822158751e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>8.401738704237201e-08</v>
+        <v>8.401738704237199e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>3.625306622359938e-07</v>
+        <v>3.625306622359936e-07</v>
       </c>
     </row>
     <row r="3">
@@ -7689,31 +7689,31 @@
         <v>8.118100421788154e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.793213815168544e-07</v>
+        <v>1.793213815168548e-07</v>
       </c>
       <c r="E3" t="n">
         <v>8.248558806703203e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>7.793254709452415e-08</v>
+        <v>7.793254709452414e-08</v>
       </c>
       <c r="G3" t="n">
         <v>1.055824017566892e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>7.905438094682562e-08</v>
+        <v>7.905438094682561e-08</v>
       </c>
       <c r="I3" t="n">
         <v>7.872291807057618e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>9.255850920013086e-08</v>
+        <v>9.255850920013089e-08</v>
       </c>
       <c r="K3" t="n">
         <v>9.09052056355734e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>4.131201786266189e-07</v>
+        <v>4.131201786266186e-07</v>
       </c>
     </row>
     <row r="4">
@@ -7723,37 +7723,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9.276343634475698e-08</v>
+        <v>5.050597871993366e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>8.917325303879201e-08</v>
+        <v>5.053919601907513e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>1.455537815685985e-07</v>
+        <v>1.032963239437754e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>9.006687317442142e-08</v>
+        <v>5.069647941334014e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>9.006687317442145e-08</v>
+        <v>5.069647941334014e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>1.070779087043531e-07</v>
+        <v>6.512171223641323e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>9.373198917890231e-08</v>
+        <v>5.147453155407904e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>9.111508221807561e-08</v>
+        <v>5.087719309427698e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>9.620713499869785e-08</v>
+        <v>5.394967737387454e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>9.338833533336109e-08</v>
+        <v>5.113087770853785e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>2.663353080440009e-07</v>
+        <v>2.240778504191772e-07</v>
       </c>
     </row>
     <row r="5">
@@ -7763,37 +7763,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.362851809890447e-07</v>
+        <v>7.57658056404553e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>2.918073415808447e-07</v>
+        <v>8.620279540922947e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>4.574636646398012e-06</v>
+        <v>8.828149039298497e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>2.918073491673085e-07</v>
+        <v>8.620280299569357e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>2.918073491673085e-07</v>
+        <v>8.620280299569357e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>1.513024868150342e-06</v>
+        <v>3.125683757580924e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>3.488912824665313e-07</v>
+        <v>9.638256692936275e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>2.918027725778157e-07</v>
+        <v>8.619822640620055e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>5.763239292822768e-07</v>
+        <v>1.384502327099093e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>2.883210305100255e-07</v>
+        <v>8.543903187372842e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>1.817946059274111e-05</v>
+        <v>2.653063491519063e-07</v>
       </c>
     </row>
     <row r="6">
@@ -7803,37 +7803,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.670070564715851e-08</v>
+        <v>5.796333779972396e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>8.282483076466875e-08</v>
+        <v>4.942187370488376e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.475602841881361e-07</v>
+        <v>1.036494684028996e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>8.235805459164076e-08</v>
+        <v>4.933972735012246e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>8.485001622215156e-08</v>
+        <v>4.977831259471581e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.494492673418461e-07</v>
+        <v>6.40546716394178e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.397755802956964e-07</v>
+        <v>5.957820354672424e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.334864408555686e-07</v>
+        <v>5.833455217406729e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.398017503367743e-07</v>
+        <v>5.306509731980984e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>8.553316151287663e-08</v>
+        <v>4.97483671236239e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>2.658684648227348e-07</v>
+        <v>2.2399568601268e-07</v>
       </c>
     </row>
     <row r="7">
@@ -7843,37 +7843,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.248544639931032e-07</v>
+        <v>5.615399955543819e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.232106788694507e-07</v>
+        <v>5.652978293281045e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.776377131655221e-07</v>
+        <v>1.089430958742364e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>1.231601363540148e-07</v>
+        <v>5.652089370138839e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.231601363540148e-07</v>
+        <v>5.652089370138839e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.391689363526994e-07</v>
+        <v>7.076973307191781e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.258230168272485e-07</v>
+        <v>5.712255238958362e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.232061098664218e-07</v>
+        <v>5.652521392978156e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.282981626470441e-07</v>
+        <v>5.95976982093791e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.254793629817075e-07</v>
+        <v>5.677889854404244e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>2.984263356923476e-07</v>
+        <v>2.297258712546817e-07</v>
       </c>
     </row>
     <row r="8">
@@ -7883,37 +7883,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.764645047376415e-07</v>
+        <v>6.523736667725783e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.439642751815893e-07</v>
+        <v>7.778241576891961e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>3.127665820633758e-07</v>
+        <v>1.327257766713895e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>2.250477068911154e-07</v>
+        <v>7.445310601875057e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>1.769873575921314e-07</v>
+        <v>6.599448458796323e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.59948051107983e-07</v>
+        <v>9.202685715366379e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.466021315825112e-07</v>
+        <v>7.837967647132592e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.439852246217059e-07</v>
+        <v>7.778233801152759e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.490908711017328e-07</v>
+        <v>8.085721478220735e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>1.758045526629549e-07</v>
+        <v>6.563613187994812e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>4.914583320753902e-07</v>
+        <v>2.636995024340076e-07</v>
       </c>
     </row>
     <row r="9">
@@ -7923,37 +7923,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.197161063565307e-07</v>
+        <v>7.284964852093437e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.601397880197224e-07</v>
+        <v>8.062930601267255e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>3.145739871020496e-07</v>
+        <v>1.330438799564726e-07</v>
       </c>
       <c r="E9" t="n">
-        <v>3.086848154511861e-07</v>
+        <v>8.917323704556046e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.601397900162047e-07</v>
+        <v>8.062931261529985e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.760980455029713e-07</v>
+        <v>9.486925615177981e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.627521259775201e-07</v>
+        <v>8.122207546944568e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.601352190166936e-07</v>
+        <v>8.062473700964361e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.65227271797316e-07</v>
+        <v>8.369722128924114e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.380344455735944e-07</v>
+        <v>7.155561939169505e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>4.353554448426181e-07</v>
+        <v>2.538253943345439e-07</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Ammonia/ammonia particulate matter results.xlsx
+++ b/Results/Ammonia/ammonia particulate matter results.xlsx
@@ -515,37 +515,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.62397009330728e-08</v>
+        <v>2.040823968884726e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>7.806729315579943e-08</v>
+        <v>2.223095900589507e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>2.000431774040072e-07</v>
+        <v>2.69237707620027e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>7.949610666845062e-08</v>
+        <v>2.347221151046379e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>7.451176480224772e-08</v>
+        <v>1.932403850751237e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.332192704915652e-07</v>
+        <v>2.340696126417024e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>9.007993232100284e-08</v>
+        <v>2.105684961868247e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>7.578144385735895e-08</v>
+        <v>2.038273241857663e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>9.043526604826603e-08</v>
+        <v>2.829483828086047e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>9.293455892011437e-08</v>
+        <v>3.106137233322736e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>8.793000105745795e-08</v>
+        <v>2.096967577176797e-08</v>
       </c>
     </row>
     <row r="3">
@@ -555,37 +555,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.36796356493705e-08</v>
+        <v>1.779182883768701e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>8.542210657602618e-08</v>
+        <v>2.072910740715594e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>2.26079279403835e-07</v>
+        <v>6.417867621039789e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>8.68632403406623e-08</v>
+        <v>2.272288015241924e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>8.187889847445935e-08</v>
+        <v>1.587514411353929e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.492179439239119e-07</v>
+        <v>3.916925853729064e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>9.96148564625263e-08</v>
+        <v>2.295310511006134e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>8.308979778268506e-08</v>
+        <v>1.760720128336733e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>9.863214067713833e-08</v>
+        <v>3.22733349347713e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.009992461564336e-07</v>
+        <v>3.657550886819317e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>9.712888318649951e-08</v>
+        <v>2.218314733769421e-08</v>
       </c>
     </row>
     <row r="4">
@@ -595,10 +595,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.528753432793689e-08</v>
+        <v>5.528753432793724e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>5.372514843404894e-08</v>
+        <v>5.372514843404891e-08</v>
       </c>
       <c r="D4" t="n">
         <v>1.288834550916042e-07</v>
@@ -607,25 +607,25 @@
         <v>5.393919416748255e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>5.393919416748256e-08</v>
+        <v>5.393919416748254e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>8.908198472540869e-08</v>
+        <v>8.908198472540882e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>6.352621811358449e-08</v>
+        <v>6.352621811358441e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>5.447492767089682e-08</v>
+        <v>5.44749276708968e-08</v>
       </c>
       <c r="J4" t="n">
         <v>5.828318870011919e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>5.776004580083403e-08</v>
+        <v>5.776004580083404e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>6.225175500096104e-08</v>
+        <v>6.225175500096102e-08</v>
       </c>
     </row>
     <row r="5">
@@ -635,37 +635,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.215307368834994e-07</v>
+        <v>1.215307368835029e-07</v>
       </c>
       <c r="C5" t="n">
-        <v>1.136795035095828e-07</v>
+        <v>1.136795035095826e-07</v>
       </c>
       <c r="D5" t="n">
-        <v>1.535349436600186e-06</v>
+        <v>1.535349436600189e-06</v>
       </c>
       <c r="E5" t="n">
-        <v>1.136795159148534e-07</v>
+        <v>1.136795159148537e-07</v>
       </c>
       <c r="F5" t="n">
-        <v>1.136795159148534e-07</v>
+        <v>1.136795159148537e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>7.889428231501097e-07</v>
+        <v>7.889428231501095e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>3.090888761265902e-07</v>
+        <v>3.090888761265892e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>1.1367024923695e-07</v>
+        <v>1.136702492369496e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>1.86729886709911e-07</v>
+        <v>1.86729886709912e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>1.700142788906269e-07</v>
+        <v>1.70014278890628e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>2.590239996891048e-07</v>
+        <v>2.891638214838586e-07</v>
       </c>
     </row>
     <row r="6">
@@ -675,34 +675,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.472347090684172e-08</v>
+        <v>5.472347090684191e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>5.29311879938572e-08</v>
+        <v>5.293118799385709e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.302694159776215e-07</v>
+        <v>1.302694507626698e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>5.281907613573965e-08</v>
+        <v>5.281907613573967e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>5.383107891637288e-08</v>
+        <v>5.383107891637284e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>9.923762412470819e-08</v>
+        <v>9.923762412470814e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>7.467463444692336e-08</v>
+        <v>7.467463444692327e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>5.391086424980153e-08</v>
+        <v>6.463056707019629e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>5.800530639853543e-08</v>
+        <v>6.888410536280107e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>5.654718028530441e-08</v>
+        <v>5.654718028530438e-08</v>
       </c>
       <c r="L6" t="n">
         <v>6.174324117693617e-08</v>
@@ -715,37 +715,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.367034168052626e-08</v>
+        <v>6.367034168052623e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>6.286698929611874e-08</v>
+        <v>6.286698929611871e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.372648072040807e-07</v>
+        <v>1.372648072040806e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>6.285012851601792e-08</v>
+        <v>6.28501285160179e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>6.285012851601792e-08</v>
+        <v>6.28501285160179e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>9.74647920779977e-08</v>
+        <v>9.746479207799767e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>7.190902546617354e-08</v>
+        <v>7.190902546617347e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>6.285773502348581e-08</v>
+        <v>6.285773502348579e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>6.666599605270825e-08</v>
+        <v>6.666599605270821e-08</v>
       </c>
       <c r="K7" t="n">
         <v>6.614285315342306e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>7.063456235355008e-08</v>
+        <v>7.063456235355005e-08</v>
       </c>
     </row>
     <row r="8">
@@ -755,37 +755,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7.560319441454777e-08</v>
+        <v>7.560319441454774e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>9.130236411149868e-08</v>
+        <v>9.130236411189394e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>1.691368246931396e-07</v>
+        <v>1.691368246931395e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>8.678680369408171e-08</v>
+        <v>8.678680369408168e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>7.531411006195238e-08</v>
+        <v>7.531411006195234e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>1.259111677666664e-07</v>
+        <v>1.259111677666663e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>1.003554011548404e-07</v>
+        <v>1.003554011548402e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>9.13041107121544e-08</v>
+        <v>9.130411071215442e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>9.511561712038125e-08</v>
+        <v>9.51156171203812e-08</v>
       </c>
       <c r="K8" t="n">
         <v>7.776895872010699e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>1.16330693606265e-07</v>
+        <v>1.163306936062647e-07</v>
       </c>
     </row>
     <row r="9">
@@ -795,16 +795,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.672722678916206e-08</v>
+        <v>9.672722678916187e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>1.089533725309588e-07</v>
+        <v>1.089533725309587e-07</v>
       </c>
       <c r="D9" t="n">
         <v>1.833526755561912e-07</v>
       </c>
       <c r="E9" t="n">
-        <v>1.239891787835134e-07</v>
+        <v>1.239891787835133e-07</v>
       </c>
       <c r="F9" t="n">
         <v>1.089533867532789e-07</v>
@@ -813,7 +813,7 @@
         <v>1.435511753128376e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>1.179954087010134e-07</v>
+        <v>1.179954087010133e-07</v>
       </c>
       <c r="I9" t="n">
         <v>1.089441182583259e-07</v>
@@ -822,10 +822,10 @@
         <v>1.127523792875482e-07</v>
       </c>
       <c r="K9" t="n">
-        <v>1.046799065693687e-07</v>
+        <v>9.582276474666547e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>1.167209455883901e-07</v>
+        <v>1.1672094558839e-07</v>
       </c>
     </row>
   </sheetData>
@@ -911,37 +911,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.8721671772029e-08</v>
+        <v>1.506557507927707e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>7.692911791871412e-08</v>
+        <v>1.758248912433048e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>7.378459226593882e-08</v>
+        <v>1.533202652910149e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>7.812163222577263e-08</v>
+        <v>1.859239851511687e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>7.387331275586106e-08</v>
+        <v>1.50568356618639e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>7.219712239428987e-08</v>
+        <v>1.524848114272573e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>6.973702919483804e-08</v>
+        <v>1.508015303377582e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>7.421583496990557e-08</v>
+        <v>1.535396683339122e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>8.786849485596093e-08</v>
+        <v>2.280543308815512e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>8.292192099979111e-08</v>
+        <v>2.580470167556699e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>6.85878519998247e-08</v>
+        <v>1.504677257818111e-08</v>
       </c>
     </row>
     <row r="3">
@@ -951,37 +951,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.522458311714516e-08</v>
+        <v>1.220585658527314e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>8.424706219098114e-08</v>
+        <v>1.795744522915992e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>8.104799046596217e-08</v>
+        <v>1.409550115440599e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>8.544765088823283e-08</v>
+        <v>1.960915267665436e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>8.119933141832127e-08</v>
+        <v>1.377266293803804e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>7.922207127017261e-08</v>
+        <v>1.350684535265944e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>7.640547163864363e-08</v>
+        <v>1.255548878913497e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>8.152254916338751e-08</v>
+        <v>1.424753575629844e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>9.595052453560099e-08</v>
+        <v>2.80197178318292e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>8.963302055146181e-08</v>
+        <v>3.032804259467328e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>7.507080746789682e-08</v>
+        <v>1.215286357953272e-08</v>
       </c>
     </row>
     <row r="4">
@@ -991,37 +991,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.927726322238817e-08</v>
+        <v>4.927726322238818e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>5.215510816109324e-08</v>
+        <v>5.215510816109326e-08</v>
       </c>
       <c r="D4" t="n">
         <v>5.228695492187779e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>5.228850905368915e-08</v>
+        <v>5.228850905368918e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>5.228850905368917e-08</v>
+        <v>5.228850905368916e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>5.129152422748499e-08</v>
+        <v>5.129152422748503e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>4.988242574091987e-08</v>
+        <v>4.988242574091989e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>5.218360842168721e-08</v>
+        <v>5.218360842168723e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>5.552675894116473e-08</v>
+        <v>5.552675894116472e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>5.010118583611352e-08</v>
+        <v>5.010118583611354e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>4.920041431922052e-08</v>
+        <v>4.920041431922054e-08</v>
       </c>
     </row>
     <row r="5">
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.036265332621533e-08</v>
+        <v>7.036265332621532e-08</v>
       </c>
       <c r="C5" t="n">
         <v>1.190312619872387e-07</v>
@@ -1040,28 +1040,28 @@
         <v>1.173583694314798e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>1.190312639524471e-07</v>
+        <v>1.190312639524472e-07</v>
       </c>
       <c r="F5" t="n">
-        <v>1.190312639524471e-07</v>
+        <v>1.190312639524472e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>1.045606363411223e-07</v>
+        <v>1.045606363411217e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>8.430864991878471e-08</v>
+        <v>8.430864991878477e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>1.190301809742211e-07</v>
+        <v>1.190301809742212e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>1.821074507521306e-07</v>
+        <v>1.821074507521309e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>8.23960585978846e-08</v>
+        <v>8.239605859788458e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>7.292281017589376e-08</v>
+        <v>7.292281017589381e-08</v>
       </c>
     </row>
     <row r="6">
@@ -1071,34 +1071,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.435254386660332e-08</v>
+        <v>4.795549504131869e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>5.084738259227442e-08</v>
+        <v>5.084738259227437e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>5.754472036682011e-08</v>
+        <v>5.754472036682009e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>5.076526949081396e-08</v>
+        <v>5.076526949081392e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>5.088087562995737e-08</v>
+        <v>5.088087562995739e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>4.996975604641552e-08</v>
+        <v>5.63668048717002e-08</v>
       </c>
       <c r="H6" t="n">
         <v>5.558424006999386e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>5.086184024061772e-08</v>
+        <v>5.086184024061773e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>6.075893271819074e-08</v>
+        <v>5.43807353017255e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>4.87106378465566e-08</v>
+        <v>4.871063784655699e-08</v>
       </c>
       <c r="L6" t="n">
         <v>4.78766549818397e-08</v>
@@ -1111,37 +1111,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.417747193385741e-08</v>
+        <v>5.417747193385743e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>5.708489814617396e-08</v>
+        <v>5.708489814617399e-08</v>
       </c>
       <c r="D7" t="n">
         <v>5.718590658261583e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>5.708452194835277e-08</v>
+        <v>5.708452194835279e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>5.708452194835277e-08</v>
+        <v>5.708452194835279e-08</v>
       </c>
       <c r="G7" t="n">
         <v>5.619173293895425e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>5.478263445238912e-08</v>
+        <v>5.478263445238914e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>5.708381713315645e-08</v>
+        <v>5.708381713315649e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>6.042696765263399e-08</v>
+        <v>6.0426967652634e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>5.500139454758276e-08</v>
+        <v>5.500139454758277e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>5.410062303068977e-08</v>
+        <v>5.410062303068978e-08</v>
       </c>
     </row>
     <row r="8">
@@ -1151,37 +1151,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.239427936935726e-08</v>
+        <v>6.239427936935728e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>7.628851252880171e-08</v>
+        <v>7.628851252913154e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>7.866481959836352e-08</v>
+        <v>7.86648195983635e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>7.328391130361368e-08</v>
+        <v>7.328391130361371e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>6.565038785215511e-08</v>
+        <v>6.565038785215515e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>7.539191468961261e-08</v>
+        <v>7.539191468961265e-08</v>
       </c>
       <c r="H8" t="n">
         <v>7.398281620304604e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>7.62839988838148e-08</v>
+        <v>7.628399888381483e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>7.962930795046084e-08</v>
+        <v>7.962930795046086e-08</v>
       </c>
       <c r="K8" t="n">
         <v>6.301418016589736e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>8.47738576686034e-08</v>
+        <v>8.477385766860338e-08</v>
       </c>
     </row>
     <row r="9">
@@ -1191,37 +1191,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.616420056471861e-08</v>
+        <v>6.616420056471865e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>7.489476207750275e-08</v>
+        <v>7.489476207750277e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>7.499703585140949e-08</v>
+        <v>7.499703585140951e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>8.16145493377055e-08</v>
+        <v>8.161454933770552e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>7.489476655281965e-08</v>
+        <v>7.489476655281966e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>7.400159687028303e-08</v>
+        <v>7.400159687028299e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>7.259249838371788e-08</v>
+        <v>7.259249838371785e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>7.489368106448524e-08</v>
+        <v>7.489368106448528e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>7.823683158396272e-08</v>
+        <v>7.823683158396267e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>6.943731450197142e-08</v>
+        <v>6.943731450197146e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>7.191048696201857e-08</v>
+        <v>7.191048696201853e-08</v>
       </c>
     </row>
   </sheetData>
@@ -1307,37 +1307,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.451671573558339e-08</v>
+        <v>2.069823739391963e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>7.096032991052804e-08</v>
+        <v>1.569802751590717e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.411597064554986e-07</v>
+        <v>2.420552563186794e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>7.147434008698295e-08</v>
+        <v>1.710278982698044e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>7.147434008698295e-08</v>
+        <v>1.710341722575339e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.031516629554599e-07</v>
+        <v>2.220523779251569e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>7.964193500814232e-08</v>
+        <v>2.090911772785777e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>7.586766655466306e-08</v>
+        <v>2.076833785651072e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>9.374456618598322e-08</v>
+        <v>2.197934377297924e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>8.566183778900352e-08</v>
+        <v>2.748332804386626e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>7.759252101175685e-08</v>
+        <v>2.082711269395995e-08</v>
       </c>
     </row>
     <row r="3">
@@ -1347,37 +1347,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.08832574755403e-08</v>
+        <v>1.997248678596577e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>7.769953989838441e-08</v>
+        <v>1.250436882219181e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.575365018573811e-07</v>
+        <v>4.495711534802914e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>7.804095760193954e-08</v>
+        <v>1.444328104155773e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>7.804095760193954e-08</v>
+        <v>1.444390844033071e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.13819378489845e-07</v>
+        <v>3.07279791788436e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>8.679414283708416e-08</v>
+        <v>2.186203045347334e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>8.239590517258381e-08</v>
+        <v>2.047802854843809e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.029474139313139e-07</v>
+        <v>2.755066213970103e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>9.250838667879101e-08</v>
+        <v>3.209872200852945e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>8.442276690077895e-08</v>
+        <v>2.111824028692408e-08</v>
       </c>
     </row>
     <row r="4">
@@ -1387,37 +1387,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.101076426153115e-08</v>
+        <v>5.101076426153118e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>5.165305778889678e-08</v>
+        <v>5.165305778889675e-08</v>
       </c>
       <c r="D4" t="n">
         <v>9.062719834145895e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>5.060164169600506e-08</v>
+        <v>5.060164169600504e-08</v>
       </c>
       <c r="F4" t="n">
         <v>5.060164169600505e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>6.796857519254176e-08</v>
+        <v>6.79685751925418e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>5.406414043010108e-08</v>
+        <v>5.406414043010113e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>5.136658017075201e-08</v>
+        <v>5.136658017075203e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>6.223568759387123e-08</v>
+        <v>6.223568759387127e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>5.291043356576541e-08</v>
+        <v>5.291043356576542e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>5.284817285622932e-08</v>
+        <v>5.284817285622934e-08</v>
       </c>
     </row>
     <row r="5">
@@ -1427,37 +1427,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.829391061878993e-08</v>
+        <v>6.829391061878999e-08</v>
       </c>
       <c r="C5" t="n">
         <v>9.69397158750877e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>7.800939543172641e-07</v>
+        <v>7.80093954317264e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>8.54666185256635e-08</v>
+        <v>8.546661852566332e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>8.54666185256635e-08</v>
+        <v>8.546661852566332e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>3.851128127605109e-07</v>
+        <v>3.851128127605107e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>1.359193197501879e-07</v>
+        <v>1.359193197501878e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>8.546152545078668e-08</v>
+        <v>8.546152545078631e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>2.834912054454861e-07</v>
+        <v>2.834912054454857e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>1.055778553813626e-07</v>
+        <v>1.055778553813625e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>1.126655147015985e-07</v>
+        <v>1.126655147015984e-07</v>
       </c>
     </row>
     <row r="6">
@@ -1467,37 +1467,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.979137097890118e-08</v>
+        <v>5.808906713624483e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>5.079574106551141e-08</v>
+        <v>5.079574106551142e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>9.040893273290018e-08</v>
+        <v>9.040898133693587e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>4.95332300193146e-08</v>
+        <v>4.953323001931459e-08</v>
       </c>
       <c r="F6" t="n">
         <v>5.011200434770896e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>7.504687806725545e-08</v>
+        <v>6.674918190991181e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>6.278011893059144e-08</v>
+        <v>6.278011893059147e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>5.844488304546569e-08</v>
+        <v>5.014718688812201e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>6.977421472553972e-08</v>
+        <v>6.977421472553974e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>5.135695863987046e-08</v>
+        <v>5.135695863987047e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>5.163909353376431e-08</v>
+        <v>5.163909353376433e-08</v>
       </c>
     </row>
     <row r="7">
@@ -1507,37 +1507,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.772524355454252e-08</v>
+        <v>5.772524355454253e-08</v>
       </c>
       <c r="C7" t="n">
         <v>5.922833726397547e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>9.734046143240658e-08</v>
+        <v>9.73404614324066e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>5.808135013309285e-08</v>
+        <v>5.808135013309283e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>5.808135013309285e-08</v>
+        <v>5.808135013309283e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>7.468305448555311e-08</v>
+        <v>7.468305448555313e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>6.077861972311244e-08</v>
+        <v>6.077861972311245e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>5.808105946376336e-08</v>
+        <v>5.808105946376337e-08</v>
       </c>
       <c r="J7" t="n">
         <v>6.895016688688259e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>5.962491285877675e-08</v>
+        <v>5.962491285877677e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>5.956265214924068e-08</v>
+        <v>5.956265214924067e-08</v>
       </c>
     </row>
     <row r="8">
@@ -1547,37 +1547,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.812292702181206e-08</v>
+        <v>6.812292702181216e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>8.372154533461981e-08</v>
+        <v>8.372154533461988e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>1.247579510303649e-07</v>
+        <v>1.24757951030365e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>7.872393618794617e-08</v>
+        <v>7.872393618794621e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>6.892851002244761e-08</v>
+        <v>6.892851002244766e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>9.917648326541757e-08</v>
+        <v>9.917648326541773e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>8.527204850303209e-08</v>
+        <v>8.527204850303213e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>8.25744882436278e-08</v>
+        <v>8.257448824362784e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>9.344636588352124e-08</v>
+        <v>9.344636588352126e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>6.976076061963282e-08</v>
+        <v>6.976076061963292e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>9.878026557534588e-08</v>
+        <v>9.878026557534601e-08</v>
       </c>
     </row>
     <row r="9">
@@ -1593,10 +1593,10 @@
         <v>8.753227583330282e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>1.256456347128797e-07</v>
+        <v>1.256456347128799e-07</v>
       </c>
       <c r="E9" t="n">
-        <v>9.641276963111386e-08</v>
+        <v>9.641276963111391e-08</v>
       </c>
       <c r="F9" t="n">
         <v>8.639009404295361e-08</v>
@@ -1605,19 +1605,19 @@
         <v>1.029869930548805e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>8.90825582924398e-08</v>
+        <v>8.908255829243983e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>8.638499803309073e-08</v>
+        <v>8.638499803309078e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>9.725410545620995e-08</v>
+        <v>9.725410545620998e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>8.289655923007263e-08</v>
+        <v>8.289655923007262e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>8.786659071856802e-08</v>
+        <v>8.786659071856809e-08</v>
       </c>
     </row>
   </sheetData>
@@ -1703,37 +1703,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.306935764224693e-08</v>
+        <v>1.935025009730624e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>6.992917574409691e-08</v>
+        <v>1.476969625252255e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.199856584171482e-07</v>
+        <v>2.181936182381049e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>7.030742772437262e-08</v>
+        <v>1.614685739775441e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>7.030742772437262e-08</v>
+        <v>1.614747688377916e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>8.98016855332786e-08</v>
+        <v>2.023083928113127e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>7.62181120706573e-08</v>
+        <v>1.94664960702024e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>7.42142919121795e-08</v>
+        <v>1.940964494061217e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>8.980900802341039e-08</v>
+        <v>2.077019389273735e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>8.254844906458277e-08</v>
+        <v>2.633850866026521e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>7.403470060909941e-08</v>
+        <v>1.937764367283886e-08</v>
       </c>
     </row>
     <row r="3">
@@ -1743,37 +1743,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.931168384522877e-08</v>
+        <v>1.855406013818204e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>7.653243477873406e-08</v>
+        <v>1.174597895752984e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.332751484187921e-07</v>
+        <v>3.614483229503034e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>7.671927448208666e-08</v>
+        <v>1.361339258853412e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>7.671927448208666e-08</v>
+        <v>1.361401207455886e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>9.855732701119585e-08</v>
+        <v>2.484146794137974e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>8.294878089704873e-08</v>
+        <v>1.970513155463271e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>8.059673161524302e-08</v>
+        <v>1.89833134125333e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>9.846192390852171e-08</v>
+        <v>2.554222460597867e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>8.896450462354032e-08</v>
+        <v>3.042841012203385e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>8.042306679246726e-08</v>
+        <v>1.890970079023211e-08</v>
       </c>
     </row>
     <row r="4">
@@ -1783,13 +1783,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.99592848254892e-08</v>
+        <v>4.995928482548929e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>5.087209701391659e-08</v>
+        <v>5.087209701391661e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>7.784903762386589e-08</v>
+        <v>7.784903762386593e-08</v>
       </c>
       <c r="E4" t="n">
         <v>4.996997563962814e-08</v>
@@ -1798,22 +1798,22 @@
         <v>4.996997563962815e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>5.982844667000796e-08</v>
+        <v>5.9828446670008e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>5.183539405079948e-08</v>
+        <v>5.183539405079953e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>5.01073283654253e-08</v>
+        <v>5.010732836542532e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>5.949939943807598e-08</v>
+        <v>5.949939943807603e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>5.064683359410203e-08</v>
+        <v>5.064683359410209e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>5.053934024334714e-08</v>
+        <v>5.053934024334718e-08</v>
       </c>
     </row>
     <row r="5">
@@ -1823,37 +1823,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.259207030747857e-08</v>
+        <v>6.259207030747862e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>8.886881828610307e-08</v>
+        <v>8.886881828610334e-08</v>
       </c>
       <c r="D5" t="n">
         <v>5.395954286108487e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>7.671086256194382e-08</v>
+        <v>7.671086256194387e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>7.671086256194382e-08</v>
+        <v>7.671086256194386e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>2.397844799162813e-07</v>
+        <v>2.397844799162831e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>1.038054453420634e-07</v>
+        <v>1.038054453420633e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>7.670720341094256e-08</v>
+        <v>7.670720341094264e-08</v>
       </c>
       <c r="J5" t="n">
         <v>2.367748670605628e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>7.734238269255432e-08</v>
+        <v>7.734238269255427e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>7.963556329146381e-08</v>
+        <v>7.963556329146385e-08</v>
       </c>
     </row>
     <row r="6">
@@ -1863,37 +1863,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.591823177625853e-08</v>
+        <v>5.591823177625851e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>4.979519178237423e-08</v>
+        <v>4.979519178237418e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>8.429400797746313e-08</v>
+        <v>8.429400797746331e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>4.840495048908091e-08</v>
+        <v>4.84049504890809e-08</v>
       </c>
       <c r="F6" t="n">
         <v>4.877205234568128e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>5.850824302105196e-08</v>
+        <v>6.578739362077717e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>5.938812329840003e-08</v>
+        <v>5.93881232984001e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>4.878712471646924e-08</v>
+        <v>4.878712471646926e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>5.840130049094246e-08</v>
+        <v>5.84013004909426e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>4.910534766501056e-08</v>
+        <v>4.910534766501055e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>4.922027677661053e-08</v>
+        <v>4.922027677661059e-08</v>
       </c>
     </row>
     <row r="7">
@@ -1903,34 +1903,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.584875554915277e-08</v>
+        <v>5.584875554915284e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>5.730697122941453e-08</v>
+        <v>5.730697122941454e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>8.373736671096378e-08</v>
+        <v>8.373736671096385e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>5.600778578674341e-08</v>
+        <v>5.60077857867434e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>5.600778578674341e-08</v>
+        <v>5.60077857867434e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>6.57179173936715e-08</v>
+        <v>6.57179173936716e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>5.772486477446307e-08</v>
+        <v>5.772486477446309e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>5.599679908908882e-08</v>
+        <v>5.599679908908886e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>6.538887016173941e-08</v>
+        <v>6.538887016173953e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>5.653630431776558e-08</v>
+        <v>5.653630431776564e-08</v>
       </c>
       <c r="L7" t="n">
         <v>5.642881096701072e-08</v>
@@ -1943,37 +1943,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.535585546041271e-08</v>
+        <v>6.535585546041272e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>7.957583602350046e-08</v>
+        <v>7.957583602308709e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>1.086403118143211e-07</v>
+        <v>1.086403118143212e-07</v>
       </c>
       <c r="E8" t="n">
         <v>7.478057665806382e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>6.59167895818719e-08</v>
+        <v>6.591678958187195e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>8.797576935855572e-08</v>
+        <v>8.79757693585558e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>7.998271673946116e-08</v>
+        <v>7.998271673946135e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>7.825465105397307e-08</v>
+        <v>7.825465105397308e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>8.764922801339593e-08</v>
+        <v>8.764922801339589e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>6.580655246293956e-08</v>
+        <v>6.580655246293972e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>9.200588965246543e-08</v>
+        <v>9.200588965246539e-08</v>
       </c>
     </row>
     <row r="9">
@@ -1983,37 +1983,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7.039314945847713e-08</v>
+        <v>7.039314945847723e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>7.879425092723804e-08</v>
+        <v>7.879425092723806e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>1.052258016744363e-07</v>
+        <v>1.052258016744364e-07</v>
       </c>
       <c r="E9" t="n">
-        <v>8.549969665483862e-08</v>
+        <v>8.549969665483871e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>7.748774066555522e-08</v>
+        <v>7.748774066555525e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>8.720519709149505e-08</v>
+        <v>8.720519709149517e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>7.921214447228666e-08</v>
+        <v>7.921214447228669e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>7.748407878691239e-08</v>
+        <v>7.748407878691248e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>8.687614985956297e-08</v>
+        <v>8.687614985956316e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>7.400085445525542e-08</v>
+        <v>7.400085445525553e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>7.79160906648342e-08</v>
+        <v>7.791609066483435e-08</v>
       </c>
     </row>
   </sheetData>
@@ -2099,37 +2099,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.197479790759342e-08</v>
+        <v>1.842258782021466e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>6.847602097685976e-08</v>
+        <v>1.412744209411019e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.03725071708067e-07</v>
+        <v>2.009354166921053e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>6.90537113757394e-08</v>
+        <v>1.550159541092735e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>6.905371137573938e-08</v>
+        <v>1.550221699200821e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>8.104449726298922e-08</v>
+        <v>1.889990808341525e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>7.426913967897292e-08</v>
+        <v>1.850019297054267e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>7.258587160868331e-08</v>
+        <v>1.845397970673609e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>8.419833757773117e-08</v>
+        <v>1.968967470664196e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>8.101303089161747e-08</v>
+        <v>2.5645618074128e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>7.258274584656234e-08</v>
+        <v>1.843809812600366e-08</v>
       </c>
     </row>
     <row r="3">
@@ -2139,37 +2139,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.863899907989293e-08</v>
+        <v>1.751899089764295e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>7.539011260515861e-08</v>
+        <v>1.096261479969329e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.151583909998413e-07</v>
+        <v>2.942538551207649e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>7.580750904701089e-08</v>
+        <v>1.289123358097966e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>7.580750904701089e-08</v>
+        <v>1.289185516206049e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>8.907103212115957e-08</v>
+        <v>2.09299726767933e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>8.129252312407887e-08</v>
+        <v>1.835239841518518e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>7.931538708990461e-08</v>
+        <v>1.774876597972574e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>9.257843740793684e-08</v>
+        <v>2.291836462384335e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>8.773504611712133e-08</v>
+        <v>2.955870639215162e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>7.933882121556139e-08</v>
+        <v>1.774455117923195e-08</v>
       </c>
     </row>
     <row r="4">
@@ -2182,7 +2182,7 @@
         <v>4.950483340119207e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>5.012112626965047e-08</v>
+        <v>5.012112626965045e-08</v>
       </c>
       <c r="D4" t="n">
         <v>6.837902580234794e-08</v>
@@ -2191,25 +2191,25 @@
         <v>4.914584433553719e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>4.914584433553719e-08</v>
+        <v>4.91458443355372e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>5.482894961706773e-08</v>
+        <v>5.482894961706776e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>5.087142612703591e-08</v>
+        <v>5.087142612703589e-08</v>
       </c>
       <c r="I4" t="n">
         <v>4.940398680692984e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>5.629564893540036e-08</v>
+        <v>5.629564893540032e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>4.973363745601498e-08</v>
+        <v>4.9733637456015e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>4.987041621967753e-08</v>
+        <v>4.987041621967751e-08</v>
       </c>
     </row>
     <row r="5">
@@ -2219,37 +2219,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.863463050428896e-08</v>
+        <v>5.863463050428898e-08</v>
       </c>
       <c r="C5" t="n">
         <v>7.718005088794263e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>3.824612281987345e-07</v>
+        <v>3.824612281987348e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>6.742247793005895e-08</v>
+        <v>6.742247793005891e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>6.742247793005895e-08</v>
+        <v>6.742247793005891e-08</v>
       </c>
       <c r="G5" t="n">
         <v>1.561661105753321e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>8.970013261430329e-08</v>
+        <v>8.970013261430342e-08</v>
       </c>
       <c r="I5" t="n">
         <v>6.741986536427845e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>1.836222802239303e-07</v>
+        <v>1.836222802239302e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>6.560851297224243e-08</v>
+        <v>6.560851297224234e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>7.101947024693125e-08</v>
+        <v>7.101947024693122e-08</v>
       </c>
     </row>
     <row r="6">
@@ -2265,31 +2265,31 @@
         <v>4.886605321949798e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>6.742290001155884e-08</v>
+        <v>6.742284947521767e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>4.764664996423248e-08</v>
+        <v>4.764664996423244e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>4.79410347827236e-08</v>
+        <v>4.794103478272359e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>6.037327666165315e-08</v>
+        <v>6.037327666165316e-08</v>
       </c>
       <c r="H6" t="n">
         <v>5.815975413988989e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>5.494831385151522e-08</v>
+        <v>5.494831385151523e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>6.221415662434669e-08</v>
+        <v>6.221415662434666e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>4.813508532708134e-08</v>
+        <v>4.813508532708116e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>4.841333933898549e-08</v>
+        <v>4.841333933898541e-08</v>
       </c>
     </row>
     <row r="7">
@@ -2302,34 +2302,34 @@
         <v>5.518229300980616e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>5.620217639755632e-08</v>
+        <v>5.62021763975563e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>7.40553442629046e-08</v>
+        <v>7.405534426290459e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>5.509548027703032e-08</v>
+        <v>5.509548027703031e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>5.509548027703032e-08</v>
+        <v>5.509548027703031e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>6.050640922568187e-08</v>
+        <v>6.050640922568184e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>5.654888573565e-08</v>
+        <v>5.654888573565002e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>5.508144641554395e-08</v>
+        <v>5.508144641554392e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>6.197310854401444e-08</v>
+        <v>6.197310854401447e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>5.54110970646291e-08</v>
+        <v>5.541109706462906e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>5.554787582829165e-08</v>
+        <v>5.554787582829163e-08</v>
       </c>
     </row>
     <row r="8">
@@ -2339,37 +2339,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.452154617973798e-08</v>
+        <v>6.452154617973799e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>7.803023572079227e-08</v>
+        <v>7.803023572127533e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>9.8456219885825e-08</v>
+        <v>9.845621988582497e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>7.34986674599175e-08</v>
+        <v>7.349866745991743e-08</v>
       </c>
       <c r="F8" t="n">
         <v>6.482621059613428e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>8.231959294165402e-08</v>
+        <v>8.231959294165397e-08</v>
       </c>
       <c r="H8" t="n">
         <v>7.836206945182083e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>7.689463013151614e-08</v>
+        <v>7.689463013151617e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>8.378874374298292e-08</v>
+        <v>8.378874374298287e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>6.45186405700397e-08</v>
+        <v>6.451864057003965e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>9.039112305267038e-08</v>
+        <v>9.039112305267034e-08</v>
       </c>
     </row>
     <row r="9">
@@ -2379,37 +2379,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.70768421989276e-08</v>
+        <v>6.707684219892759e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>7.423271721680353e-08</v>
+        <v>7.423271721680352e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>9.208703733030369e-08</v>
+        <v>9.20870373303037e-08</v>
       </c>
       <c r="E9" t="n">
         <v>8.019541730685672e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>7.311460238849782e-08</v>
+        <v>7.311460238849779e-08</v>
       </c>
       <c r="G9" t="n">
         <v>7.853695004492906e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>7.457942655489725e-08</v>
+        <v>7.457942655489728e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>7.311198723479119e-08</v>
+        <v>7.311198723479113e-08</v>
       </c>
       <c r="J9" t="n">
         <v>8.000364936326166e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>6.571532627401044e-08</v>
+        <v>6.974218497230005e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>7.357841664753885e-08</v>
+        <v>7.357841664753882e-08</v>
       </c>
     </row>
   </sheetData>
@@ -2495,37 +2495,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.331720300105837e-08</v>
+        <v>1.955231787715327e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>6.721753937568879e-08</v>
+        <v>1.459352659456333e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.098980895994576e-07</v>
+        <v>2.147749728333419e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>7.065979463469842e-08</v>
+        <v>1.61843237884856e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>7.065979463469842e-08</v>
+        <v>1.618494254754477e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>9.043580651979757e-08</v>
+        <v>2.045323598005937e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>7.758179752652827e-08</v>
+        <v>1.972760331229568e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>7.478520469148958e-08</v>
+        <v>1.96286949027809e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>8.873304905845647e-08</v>
+        <v>2.067461997814725e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>8.352647968974794e-08</v>
+        <v>2.644966072449833e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>7.737061140140616e-08</v>
+        <v>1.974422332152109e-08</v>
       </c>
     </row>
     <row r="3">
@@ -2535,37 +2535,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.950418037327433e-08</v>
+        <v>1.885115666479901e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>7.336321933640147e-08</v>
+        <v>1.06481761079438e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.215797776692636e-07</v>
+        <v>3.256798480518647e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>7.706476190355407e-08</v>
+        <v>1.373172217028537e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>7.706476190355409e-08</v>
+        <v>1.373234092934451e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>9.919412052786026e-08</v>
+        <v>2.528354187492439e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>8.442443269821827e-08</v>
+        <v>2.042347233731743e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>8.116140030530959e-08</v>
+        <v>1.94013848836081e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>9.717568720539738e-08</v>
+        <v>2.504999612883459e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>9.002178190484825e-08</v>
+        <v>3.083348418683232e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>8.416734539060068e-08</v>
+        <v>2.037486054273029e-08</v>
       </c>
     </row>
     <row r="4">
@@ -2575,7 +2575,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.011701351876175e-08</v>
+        <v>5.011701351876177e-08</v>
       </c>
       <c r="C4" t="n">
         <v>4.919273974628156e-08</v>
@@ -2590,22 +2590,22 @@
         <v>4.995367255261856e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>6.023316022675538e-08</v>
+        <v>6.02331602267554e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>5.265626345518226e-08</v>
+        <v>5.265626345518228e-08</v>
       </c>
       <c r="I4" t="n">
         <v>5.057273795904385e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>5.904398374414769e-08</v>
+        <v>5.90439837441477e-08</v>
       </c>
       <c r="K4" t="n">
         <v>5.133723542580396e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>5.253216679550669e-08</v>
+        <v>5.253216679550671e-08</v>
       </c>
     </row>
     <row r="5">
@@ -2615,34 +2615,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.386954704629153e-08</v>
+        <v>6.386954704629152e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>6.231316596592855e-08</v>
+        <v>6.231316596592854e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>4.559829344740937e-07</v>
+        <v>4.559829344740935e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>8.232956127042059e-08</v>
+        <v>8.232956127042036e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>8.232956127042059e-08</v>
+        <v>8.232956127042036e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>2.546249916949139e-07</v>
+        <v>2.546249916949143e-07</v>
       </c>
       <c r="H5" t="n">
         <v>1.206660395267891e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>8.232606224226791e-08</v>
+        <v>8.232606224226772e-08</v>
       </c>
       <c r="J5" t="n">
         <v>2.357099107935711e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>8.895095970368599e-08</v>
+        <v>8.895095970368608e-08</v>
       </c>
       <c r="L5" t="n">
         <v>1.195552185379983e-07</v>
@@ -2655,37 +2655,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.865013753942317e-08</v>
+        <v>4.865013753942319e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>4.812870264526617e-08</v>
+        <v>4.812870264526613e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>7.093891834459518e-08</v>
+        <v>7.093887004577743e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>4.867882866224534e-08</v>
+        <v>4.86788286622453e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>4.909151296884747e-08</v>
+        <v>4.909151296884745e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>5.87662842474168e-08</v>
+        <v>5.876628424741679e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>6.046720987022649e-08</v>
+        <v>6.046720987022653e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>4.910586197970529e-08</v>
+        <v>5.679107085106829e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>6.566904316480821e-08</v>
+        <v>5.779937269773975e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>4.965499001654031e-08</v>
+        <v>4.965499001654032e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>5.107882870546668e-08</v>
+        <v>5.10788287054667e-08</v>
       </c>
     </row>
     <row r="7">
@@ -2695,10 +2695,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.632147147332247e-08</v>
+        <v>5.632147147332248e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>5.618911891444103e-08</v>
+        <v>5.618911891444106e-08</v>
       </c>
       <c r="D7" t="n">
         <v>7.806604415273974e-08</v>
@@ -2710,22 +2710,22 @@
         <v>5.679746957546476e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>6.643761818131609e-08</v>
+        <v>6.64376181813161e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>5.886072140974296e-08</v>
+        <v>5.886072140974301e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>5.677719591360461e-08</v>
+        <v>5.67771959136046e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>6.524844169870839e-08</v>
+        <v>6.524844169870841e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>5.754169338036467e-08</v>
+        <v>5.754169338036472e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>5.873662475006739e-08</v>
+        <v>5.873662475006742e-08</v>
       </c>
     </row>
     <row r="8">
@@ -2735,37 +2735,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.629649888599557e-08</v>
+        <v>6.629649888599561e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>7.957462310591559e-08</v>
+        <v>7.957462310632914e-08</v>
       </c>
       <c r="D8" t="n">
         <v>1.04209051855108e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>7.650156781278704e-08</v>
+        <v>7.650156781278712e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>6.719090285892097e-08</v>
+        <v>6.7190902858921e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>8.980286278091613e-08</v>
+        <v>8.980286278091614e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>8.222596600939583e-08</v>
+        <v>8.222596600939588e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>8.014244051320464e-08</v>
+        <v>8.014244051320466e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>8.861631785878389e-08</v>
+        <v>8.861631785878397e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>6.726799063376025e-08</v>
+        <v>6.726799063376028e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>9.608907087352495e-08</v>
+        <v>9.608907087352501e-08</v>
       </c>
     </row>
     <row r="9">
@@ -2775,7 +2775,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7.354798188395591e-08</v>
+        <v>7.354798188395588e-08</v>
       </c>
       <c r="C9" t="n">
         <v>8.124918890282588e-08</v>
@@ -2784,28 +2784,28 @@
         <v>1.031273430034464e-07</v>
       </c>
       <c r="E9" t="n">
-        <v>9.088054331384027e-08</v>
+        <v>9.088054331384028e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>8.184076781102468e-08</v>
+        <v>8.184076781102461e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>9.149768816970098e-08</v>
+        <v>9.149768816970096e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>8.392079139812778e-08</v>
+        <v>8.392079139812784e-08</v>
       </c>
       <c r="I9" t="n">
         <v>8.18372659019894e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>9.030851168709325e-08</v>
+        <v>9.030851168709324e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>7.27379098109648e-08</v>
+        <v>7.806297429280543e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>8.379669473845222e-08</v>
+        <v>8.379669473845226e-08</v>
       </c>
     </row>
   </sheetData>
@@ -2891,37 +2891,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.146086932803497e-08</v>
+        <v>1.770462734751733e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>6.632685181473322e-08</v>
+        <v>1.333579079512873e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>7.210909038243106e-08</v>
+        <v>1.773874193413956e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>6.931703066584557e-08</v>
+        <v>1.485187875834278e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>6.931703066584557e-08</v>
+        <v>1.48524862727092e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>7.251570790155979e-08</v>
+        <v>1.776014140656382e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>7.224178615619889e-08</v>
+        <v>1.770877517173862e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>7.281291662751241e-08</v>
+        <v>1.777508009187236e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>8.175258253055466e-08</v>
+        <v>1.882673752509359e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>8.030642251904261e-08</v>
+        <v>2.491580089358341e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>7.250139217520644e-08</v>
+        <v>1.775082275427386e-08</v>
       </c>
     </row>
     <row r="3">
@@ -2931,37 +2931,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.745917223774207e-08</v>
+        <v>1.694654204031716e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>7.232846113682535e-08</v>
+        <v>9.788807799588047e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>7.820476072888442e-08</v>
+        <v>1.71951518557161e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>7.551641480821052e-08</v>
+        <v>1.264511435018674e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>7.551641480821052e-08</v>
+        <v>1.264572186455315e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>7.867245510644799e-08</v>
+        <v>1.734878398304845e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>7.837181899515792e-08</v>
+        <v>1.721411669989551e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>7.899441162425894e-08</v>
+        <v>1.745448511511247e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>8.91849527797338e-08</v>
+        <v>2.156432410245193e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>8.633392823280893e-08</v>
+        <v>2.891165998511317e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>7.86560275389766e-08</v>
+        <v>1.734192955059532e-08</v>
       </c>
     </row>
     <row r="4">
@@ -2971,13 +2971,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.880136289404707e-08</v>
+        <v>4.88013628940471e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>4.842036955958334e-08</v>
+        <v>4.842036955958333e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>4.918670284342945e-08</v>
+        <v>4.918670284342946e-08</v>
       </c>
       <c r="E4" t="n">
         <v>4.912837612167999e-08</v>
@@ -2989,19 +2989,19 @@
         <v>4.935684242641702e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>4.92667319493017e-08</v>
+        <v>4.926673194930173e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>4.911414365663899e-08</v>
+        <v>4.911414365663897e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>5.447680690766475e-08</v>
+        <v>5.447680690766478e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>4.891693548601436e-08</v>
+        <v>4.891693548601434e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>4.94217660504512e-08</v>
+        <v>4.942176605045123e-08</v>
       </c>
     </row>
     <row r="5">
@@ -3011,37 +3011,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.803216083260054e-08</v>
+        <v>5.80321608326006e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>5.943094845189805e-08</v>
+        <v>5.943094845189801e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>6.750722339420847e-08</v>
+        <v>6.750722339420851e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>7.427803625836074e-08</v>
+        <v>7.427803625836077e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>7.427803625836074e-08</v>
+        <v>7.427803625836077e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>7.217877834466754e-08</v>
+        <v>7.21787783446676e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>7.174709270546111e-08</v>
+        <v>7.174709270546102e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>7.42765567713914e-08</v>
+        <v>7.427655677139161e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>1.630184134311766e-07</v>
+        <v>1.630184134311767e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>6.298898308281724e-08</v>
+        <v>6.298898308281723e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>7.52831158941341e-08</v>
+        <v>7.528311589413418e-08</v>
       </c>
     </row>
     <row r="6">
@@ -3057,28 +3057,28 @@
         <v>4.708736458009973e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>4.75778208631281e-08</v>
+        <v>5.437424820139354e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>4.734180522601614e-08</v>
+        <v>4.734180522601611e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>4.74959322852485e-08</v>
+        <v>4.749593228524848e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>5.421494973169365e-08</v>
+        <v>4.772898037338379e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>5.563559422386973e-08</v>
+        <v>5.563559422386972e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>5.397225096191563e-08</v>
+        <v>5.397225096191562e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>5.30186025481456e-08</v>
+        <v>5.963347753731961e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>4.723227518635902e-08</v>
+        <v>4.723227518635901e-08</v>
       </c>
       <c r="L6" t="n">
         <v>4.779596004450794e-08</v>
@@ -3091,34 +3091,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.400470879561476e-08</v>
+        <v>5.400470879561477e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>5.405031578848998e-08</v>
+        <v>5.405031578849001e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>5.438890383301561e-08</v>
+        <v>5.43889038330156e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>5.434369235271714e-08</v>
+        <v>5.434369235271715e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>5.434369235271714e-08</v>
+        <v>5.434369235271715e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>5.456018832798472e-08</v>
+        <v>5.456018832798474e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>5.447007785086943e-08</v>
+        <v>5.447007785086942e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>5.431748955820664e-08</v>
+        <v>5.431748955820667e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>5.968015280923241e-08</v>
+        <v>5.968015280923243e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>5.412028138758201e-08</v>
+        <v>5.412028138758202e-08</v>
       </c>
       <c r="L7" t="n">
         <v>5.462511195201892e-08</v>
@@ -3131,37 +3131,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.289734010322086e-08</v>
+        <v>6.28973401032209e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>7.473064689173597e-08</v>
+        <v>7.473064689132737e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>7.748149248452527e-08</v>
+        <v>7.748149248452539e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>7.177970700410167e-08</v>
+        <v>7.177970700410162e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>6.359981371406219e-08</v>
+        <v>6.359981371406218e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>7.521306796527453e-08</v>
+        <v>7.521306796527456e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>7.512295748827081e-08</v>
+        <v>7.51229574882708e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>7.497036919549652e-08</v>
+        <v>7.497036919549655e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>8.033534367147667e-08</v>
+        <v>8.033534367147675e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>6.279446004425183e-08</v>
+        <v>6.279446004425179e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>8.756255434616619e-08</v>
+        <v>8.756255434616614e-08</v>
       </c>
     </row>
     <row r="9">
@@ -3171,37 +3171,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.582003364636498e-08</v>
+        <v>6.582003364636504e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>7.179260775574969e-08</v>
+        <v>7.179260775574972e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>7.213234925300045e-08</v>
+        <v>7.213234925300047e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>7.890086650952819e-08</v>
+        <v>7.890086650952829e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>7.206126372922919e-08</v>
+        <v>7.206126372922933e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>7.230248029524443e-08</v>
+        <v>7.230248029524449e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>7.221236981812915e-08</v>
+        <v>7.221236981812918e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>7.205978152546638e-08</v>
+        <v>7.205978152546643e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>7.742244477649211e-08</v>
+        <v>7.742244477649218e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>6.439946158169128e-08</v>
+        <v>6.842846892274358e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>7.236740391927863e-08</v>
+        <v>7.236740391927867e-08</v>
       </c>
     </row>
   </sheetData>
@@ -3287,37 +3287,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.089091609089575e-08</v>
+        <v>1.723225310661802e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>6.631798005387278e-08</v>
+        <v>1.327208848868151e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>7.152724983565955e-08</v>
+        <v>1.726574208774432e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>6.868265847326371e-08</v>
+        <v>1.473285524262698e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>6.868265847326371e-08</v>
+        <v>1.473347041051462e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>7.13139903952041e-08</v>
+        <v>1.725451866696051e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>7.148798810451325e-08</v>
+        <v>1.722720178746889e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>7.172053203320085e-08</v>
+        <v>1.727523642334395e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>7.846544182324219e-08</v>
+        <v>1.843727258913882e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>8.002915841358751e-08</v>
+        <v>2.480436415835546e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>7.147081972635541e-08</v>
+        <v>1.725441564234372e-08</v>
       </c>
     </row>
     <row r="3">
@@ -3327,37 +3327,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.742392217289249e-08</v>
+        <v>1.622266261012065e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>7.286590628971343e-08</v>
+        <v>9.760773660665015e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>7.815583779550898e-08</v>
+        <v>1.646685797329904e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>7.533834449328265e-08</v>
+        <v>1.235415522766082e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>7.533834449328265e-08</v>
+        <v>1.235477039554848e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>7.791054526242523e-08</v>
+        <v>1.638776943962396e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>7.812445436566666e-08</v>
+        <v>1.642121691093489e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>7.835877570702659e-08</v>
+        <v>1.653490060800967e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>8.598085570783461e-08</v>
+        <v>2.010852161221564e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>8.656876865228197e-08</v>
+        <v>2.874027809435663e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>7.809094861217916e-08</v>
+        <v>1.644414994260963e-08</v>
       </c>
     </row>
     <row r="4">
@@ -3367,37 +3367,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.889065410984155e-08</v>
+        <v>4.889065410984159e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>4.86635667181741e-08</v>
+        <v>4.866356671817414e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>4.926892755735557e-08</v>
+        <v>4.926892755735562e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>4.876751714644849e-08</v>
+        <v>4.876751714644847e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>4.876751714644849e-08</v>
+        <v>4.876751714644848e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>4.90780600330876e-08</v>
+        <v>4.907806003308953e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>4.924663599250997e-08</v>
+        <v>4.924663599250994e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>4.894319885940418e-08</v>
+        <v>4.894319885940394e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>5.277861691933251e-08</v>
+        <v>5.277861691933259e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>4.891679062419018e-08</v>
+        <v>4.891679062419017e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>4.923718129472722e-08</v>
+        <v>4.923718129472719e-08</v>
       </c>
     </row>
     <row r="5">
@@ -3407,37 +3407,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.760406330944447e-08</v>
+        <v>5.760406330944481e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>5.979771500941708e-08</v>
+        <v>5.979771500941709e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>6.698032662929881e-08</v>
+        <v>6.69803266292988e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>6.859118287640869e-08</v>
+        <v>6.859118287640888e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>6.859118287640869e-08</v>
+        <v>6.859118287640888e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>6.519929286700066e-08</v>
+        <v>6.519929286700051e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>6.918272773482986e-08</v>
+        <v>6.918272773482985e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>6.858978955527323e-08</v>
+        <v>6.85897895552735e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>1.306778789606231e-07</v>
+        <v>1.30677878960623e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>6.105394124868409e-08</v>
+        <v>6.105394124868414e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>6.945915983001089e-08</v>
+        <v>6.945915983001098e-08</v>
       </c>
     </row>
     <row r="6">
@@ -3447,37 +3447,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.38235972534264e-08</v>
+        <v>5.382359725342642e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>4.726414778646508e-08</v>
+        <v>4.72641477864651e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>4.766284378569653e-08</v>
+        <v>4.76628437856965e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>4.716884889803364e-08</v>
+        <v>4.71688488980337e-08</v>
       </c>
       <c r="F6" t="n">
         <v>4.73430478731493e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>5.401100317667227e-08</v>
+        <v>5.401100317667225e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>5.586166405101228e-08</v>
+        <v>4.764172123179334e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>4.733624355538384e-08</v>
+        <v>5.387614200298918e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>5.80311248737584e-08</v>
+        <v>5.133753811033734e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>4.72612819503028e-08</v>
+        <v>4.726128195030268e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>4.763029292682211e-08</v>
+        <v>4.763029292682212e-08</v>
       </c>
     </row>
     <row r="7">
@@ -3487,37 +3487,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.408336435539332e-08</v>
+        <v>5.408336435539335e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>5.417397510079316e-08</v>
+        <v>5.417397510079314e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>5.446049034492799e-08</v>
+        <v>5.446049034492801e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>5.415733728334849e-08</v>
+        <v>5.415733728334848e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>5.415733728334849e-08</v>
+        <v>5.415733728334848e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>5.427077027863921e-08</v>
+        <v>5.427077027863927e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>5.44393462380618e-08</v>
+        <v>5.443934623806179e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>5.413590910495611e-08</v>
+        <v>5.413590910495613e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>5.797132716488431e-08</v>
+        <v>5.797132716488435e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>5.410950086974195e-08</v>
+        <v>5.410950086974192e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>5.442989154027899e-08</v>
+        <v>5.442989154027897e-08</v>
       </c>
     </row>
     <row r="8">
@@ -3527,37 +3527,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.301467386517683e-08</v>
+        <v>6.301467386517679e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>7.491575162405079e-08</v>
+        <v>7.491575162453222e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>7.762464173014575e-08</v>
+        <v>7.762464173014567e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>7.165250423363309e-08</v>
+        <v>7.165250423363304e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>6.345489322576057e-08</v>
+        <v>6.345489322576054e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>7.498956281246086e-08</v>
+        <v>7.49895628124609e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>7.515813877208137e-08</v>
+        <v>7.515813877208141e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>7.485470163877786e-08</v>
+        <v>7.485470163877785e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>7.869243627548049e-08</v>
+        <v>7.869243627548047e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>6.282185183011515e-08</v>
+        <v>6.282185183011517e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>8.746169574633928e-08</v>
+        <v>8.746169574633927e-08</v>
       </c>
     </row>
     <row r="9">
@@ -3567,37 +3567,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.465930337698188e-08</v>
+        <v>6.465930337698194e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>7.033528032781366e-08</v>
+        <v>7.033528032781371e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>7.062295138310386e-08</v>
+        <v>7.062295138310382e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>7.674401269265862e-08</v>
+        <v>7.674401269265863e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>7.029861030613387e-08</v>
+        <v>7.029861030613388e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>7.043207550565976e-08</v>
+        <v>7.043207550565985e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>7.06006514650823e-08</v>
+        <v>7.060065146508246e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>7.029721433197666e-08</v>
+        <v>7.029721433197674e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>7.413263239190485e-08</v>
+        <v>7.413263239190489e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>6.690333026198241e-08</v>
+        <v>6.703462649522279e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>7.059119676729959e-08</v>
+        <v>7.059119676729961e-08</v>
       </c>
     </row>
   </sheetData>
@@ -3683,37 +3683,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.237540213287522e-08</v>
+        <v>1.846822944212187e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>6.671095885331424e-08</v>
+        <v>1.381522249751491e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>7.740047729572747e-08</v>
+        <v>1.873268916734105e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>6.994000079150143e-08</v>
+        <v>1.532850179400726e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>6.994000079150143e-08</v>
+        <v>1.532911297413306e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>7.827073573133937e-08</v>
+        <v>1.877848914033475e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>7.591285675312362e-08</v>
+        <v>1.861471072115454e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>7.378553576910682e-08</v>
+        <v>1.854167185534687e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>8.527742767103916e-08</v>
+        <v>1.952717308479804e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>8.129504063505104e-08</v>
+        <v>2.545150954574413e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>7.595577941039285e-08</v>
+        <v>1.864542341404571e-08</v>
       </c>
     </row>
     <row r="3">
@@ -3723,37 +3723,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.842284250160421e-08</v>
+        <v>1.785176857925796e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>7.272990746366264e-08</v>
+        <v>1.016918125129051e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>8.420271988006828e-08</v>
+        <v>1.974079555170793e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>7.619705529401066e-08</v>
+        <v>1.309293851395707e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>7.61970552940105e-08</v>
+        <v>1.309354969408259e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>8.520369735451383e-08</v>
+        <v>2.007105160066241e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>8.250603784151496e-08</v>
+        <v>1.915742142409294e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>8.002112524192214e-08</v>
+        <v>1.838095836533388e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>9.318965480467666e-08</v>
+        <v>2.319393692207006e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>8.74274637727671e-08</v>
+        <v>2.954757822858582e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>8.254122732480398e-08</v>
+        <v>1.920486966580983e-08</v>
       </c>
     </row>
     <row r="4">
@@ -3763,37 +3763,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.944535395849442e-08</v>
+        <v>4.944535395849458e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>4.865694678952564e-08</v>
+        <v>4.865694678952565e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>5.2432548212313e-08</v>
+        <v>5.243254821231315e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>4.936196628793353e-08</v>
+        <v>4.936196628793354e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>4.936196628793352e-08</v>
+        <v>4.936196628793354e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>5.28938596651611e-08</v>
+        <v>5.28938596651612e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>5.154986819850238e-08</v>
+        <v>5.15498681985025e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>4.989568113934518e-08</v>
+        <v>4.98956811393452e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>5.682540689622421e-08</v>
+        <v>5.682540689622434e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>4.978168052715147e-08</v>
+        <v>4.97816805271516e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>5.157633583660705e-08</v>
+        <v>5.157633583660713e-08</v>
       </c>
     </row>
     <row r="5">
@@ -3803,37 +3803,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.196130662036998e-08</v>
+        <v>6.196130662037005e-08</v>
       </c>
       <c r="C5" t="n">
         <v>6.120665193184127e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>1.184307566409931e-07</v>
+        <v>1.184307566409932e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>7.977901454972904e-08</v>
+        <v>7.977901454972845e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>7.977901454972904e-08</v>
+        <v>7.977901454972846e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>1.298549655342328e-07</v>
+        <v>1.298549655342317e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>1.097570518851915e-07</v>
+        <v>1.097570518851919e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>7.977704478923309e-08</v>
+        <v>7.977704478923268e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>2.046048384405513e-07</v>
+        <v>2.046048384405511e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>7.110546521367552e-08</v>
+        <v>7.110546521367567e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>1.115383698140692e-07</v>
+        <v>1.115383698140695e-07</v>
       </c>
     </row>
     <row r="6">
@@ -3843,37 +3843,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.778631785098481e-08</v>
+        <v>4.778631785098504e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>4.74805772949444e-08</v>
+        <v>4.748057729494438e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>5.082892576806615e-08</v>
+        <v>5.082892576806624e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>4.79756987162445e-08</v>
+        <v>4.797569871624449e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>4.823843447090362e-08</v>
+        <v>4.823843447090361e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>5.835649260328825e-08</v>
+        <v>5.123482355765161e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>5.85698227939332e-08</v>
+        <v>5.856982279393316e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>5.53583140774723e-08</v>
+        <v>4.823664503183569e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>6.264272909951888e-08</v>
+        <v>5.536197191224177e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>4.801794818079035e-08</v>
+        <v>4.801794818079044e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>4.992901554034415e-08</v>
+        <v>4.992901554034419e-08</v>
       </c>
     </row>
     <row r="7">
@@ -3883,37 +3883,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.51727785361229e-08</v>
+        <v>5.517277853612301e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>5.509382100908966e-08</v>
+        <v>5.509382100908967e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>5.815876039343171e-08</v>
+        <v>5.815876039343168e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>5.5647451440859e-08</v>
+        <v>5.564745144085901e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>5.5647451440859e-08</v>
+        <v>5.564745144085901e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>5.86212842427895e-08</v>
+        <v>5.862128424278963e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>5.727729277613072e-08</v>
+        <v>5.727729277613091e-08</v>
       </c>
       <c r="I7" t="n">
         <v>5.562310571697362e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>6.255283147385273e-08</v>
+        <v>6.255283147385285e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>5.550910510477989e-08</v>
+        <v>5.550910510477996e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>5.730376041423555e-08</v>
+        <v>5.73037604142356e-08</v>
       </c>
     </row>
     <row r="8">
@@ -3926,34 +3926,34 @@
         <v>6.473243187197054e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>7.740386865305587e-08</v>
+        <v>7.740386865264466e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>8.308313271419127e-08</v>
+        <v>8.308313271419143e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>7.445189395710601e-08</v>
+        <v>7.445189395710604e-08</v>
       </c>
       <c r="F8" t="n">
         <v>6.56021605077108e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>8.090585056415871e-08</v>
+        <v>8.090585056415879e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>7.956185909755183e-08</v>
+        <v>7.956185909755184e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>7.790767203834275e-08</v>
+        <v>7.79076720383428e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>8.483989860444808e-08</v>
+        <v>8.483989860444845e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>6.483238664844939e-08</v>
+        <v>6.483238664844933e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>9.288056238934654e-08</v>
+        <v>9.288056238934662e-08</v>
       </c>
     </row>
     <row r="9">
@@ -3963,37 +3963,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7.010336108290548e-08</v>
+        <v>7.010336108290567e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>7.704831448378761e-08</v>
+        <v>7.704831448378754e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>8.011447671994897e-08</v>
+        <v>8.011447671994916e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>8.568502590961902e-08</v>
+        <v>8.568502590961898e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>7.757957153314947e-08</v>
+        <v>7.757957153314945e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>8.05757777174874e-08</v>
+        <v>8.057577771748752e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>7.923178625082877e-08</v>
+        <v>7.923178625082887e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>7.757759919167161e-08</v>
+        <v>7.757759919167159e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>8.45073249485506e-08</v>
+        <v>8.450732494855071e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>7.339392140027934e-08</v>
+        <v>7.339392140027949e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>7.925825388893347e-08</v>
+        <v>7.925825388893353e-08</v>
       </c>
     </row>
   </sheetData>
@@ -4079,37 +4079,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.09528659489517e-08</v>
+        <v>1.722782011688058e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>6.641095985330027e-08</v>
+        <v>1.342032653194338e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>7.145924325592706e-08</v>
+        <v>1.725446974880033e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>6.92280732844471e-08</v>
+        <v>1.489425190351229e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>6.92280732844471e-08</v>
+        <v>1.489485974882899e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>7.132635383798674e-08</v>
+        <v>1.724747604267378e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>7.147000868285293e-08</v>
+        <v>1.721854283609731e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>7.208630498054025e-08</v>
+        <v>1.728677356298833e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>8.192065791253371e-08</v>
+        <v>1.883287919754042e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>8.063596394860993e-08</v>
+        <v>2.50297928939737e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>7.156968525989204e-08</v>
+        <v>1.725197673331739e-08</v>
       </c>
     </row>
     <row r="3">
@@ -4119,37 +4119,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.697349841469882e-08</v>
+        <v>1.613108791879681e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>7.242180512935373e-08</v>
+        <v>9.874277776127404e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>7.755593721346364e-08</v>
+        <v>1.632643653406694e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>7.541696650030832e-08</v>
+        <v>1.262362987472372e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>7.541696650030832e-08</v>
+        <v>1.262423772004042e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>7.740308685487225e-08</v>
+        <v>1.627754392786448e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>7.75824976095202e-08</v>
+        <v>1.62997665488208e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>7.825828648319453e-08</v>
+        <v>1.65570196968569e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>8.939072985531058e-08</v>
+        <v>2.157566229976299e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>8.670628569446757e-08</v>
+        <v>2.911062542372417e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>7.768298176451236e-08</v>
+        <v>1.636692894946418e-08</v>
       </c>
     </row>
     <row r="4">
@@ -4159,37 +4159,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.88394459227288e-08</v>
+        <v>4.883944592272878e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>4.839898513690899e-08</v>
+        <v>4.839898513690897e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>4.9140465774699e-08</v>
+        <v>4.914046577469898e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>4.9053268802135e-08</v>
+        <v>4.905326880213497e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>4.9053268802135e-08</v>
+        <v>4.905326880213496e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>4.898995626493388e-08</v>
+        <v>4.89899562649338e-08</v>
       </c>
       <c r="H4" t="n">
         <v>4.914791631587705e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>4.902278365740605e-08</v>
+        <v>4.902278365740604e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>5.457572648402944e-08</v>
+        <v>5.457572648402941e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>4.903609549390425e-08</v>
+        <v>4.903609549390421e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>4.920789565872381e-08</v>
+        <v>4.92078956587238e-08</v>
       </c>
     </row>
     <row r="5">
@@ -4199,37 +4199,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.932815322527738e-08</v>
+        <v>5.932815322527735e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>5.981970877090222e-08</v>
+        <v>5.981970877090218e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>6.732045427358967e-08</v>
+        <v>6.732045427358959e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>7.330807388738215e-08</v>
+        <v>7.33080738873821e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>7.330807388738215e-08</v>
+        <v>7.33080738873821e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>6.638128126092924e-08</v>
+        <v>6.63812812609278e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>7.015160943981745e-08</v>
+        <v>7.015160943981736e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>7.330665273947454e-08</v>
+        <v>7.330665273947452e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>1.654150462434194e-07</v>
+        <v>1.654150462434195e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>6.562413149733496e-08</v>
+        <v>6.56241314973349e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>7.180349085049424e-08</v>
+        <v>7.180349085049422e-08</v>
       </c>
     </row>
     <row r="6">
@@ -4239,37 +4239,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.723584292014714e-08</v>
+        <v>5.370299878005638e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>4.710331942690105e-08</v>
+        <v>4.710331942690103e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>4.756147684187261e-08</v>
+        <v>4.756152398560955e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>4.727878210800331e-08</v>
+        <v>4.727878210800329e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>4.742958034498151e-08</v>
+        <v>4.742958034498146e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>4.738635326235224e-08</v>
+        <v>4.738635326235218e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>5.551518673802908e-08</v>
+        <v>5.551518673802902e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>5.388633651473369e-08</v>
+        <v>5.388633651473366e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>5.973607769905432e-08</v>
+        <v>5.31424532299442e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>4.738975241038621e-08</v>
+        <v>4.738975241038616e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>4.760454959950024e-08</v>
+        <v>4.760454959950022e-08</v>
       </c>
     </row>
     <row r="7">
@@ -4279,37 +4279,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.396166993392822e-08</v>
+        <v>5.396166993392819e-08</v>
       </c>
       <c r="C7" t="n">
         <v>5.395578732971931e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>5.426154922338088e-08</v>
+        <v>5.426154922338082e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>5.417525363351876e-08</v>
+        <v>5.41752536335187e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>5.417525363351876e-08</v>
+        <v>5.41752536335187e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>5.411218027613332e-08</v>
+        <v>5.411218027613322e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>5.427014032707651e-08</v>
+        <v>5.427014032707646e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>5.414500766860549e-08</v>
+        <v>5.414500766860546e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>5.969795049522888e-08</v>
+        <v>5.969795049522882e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>5.415831950510368e-08</v>
+        <v>5.415831950510362e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>5.433011966992322e-08</v>
+        <v>5.433011966992317e-08</v>
       </c>
     </row>
     <row r="8">
@@ -4319,37 +4319,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.278652338458341e-08</v>
+        <v>6.278652338458335e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>7.446999921280185e-08</v>
+        <v>7.446999921280174e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>7.716292178640525e-08</v>
+        <v>7.71629217864051e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>7.146859856341696e-08</v>
+        <v>7.146859856341684e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>6.335869909730144e-08</v>
+        <v>6.335869909730143e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>7.459504723139435e-08</v>
+        <v>7.459504723139421e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>7.475300728244658e-08</v>
+        <v>7.475300728244644e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>7.462787462386652e-08</v>
+        <v>7.46278746238664e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>8.018310858314107e-08</v>
+        <v>8.01831085831409e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>6.276661936920566e-08</v>
+        <v>6.276661936920561e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>8.699075655829529e-08</v>
+        <v>8.699075655829511e-08</v>
       </c>
     </row>
     <row r="9">
@@ -4359,37 +4359,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.570791839272431e-08</v>
+        <v>6.570791839272422e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>7.158414589607488e-08</v>
+        <v>7.15841458960748e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>7.189105671418606e-08</v>
+        <v>7.189105671418595e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>7.856262872536846e-08</v>
+        <v>7.856262872536834e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>7.177479013506643e-08</v>
+        <v>7.177479013506628e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>7.17405388424888e-08</v>
+        <v>7.174053884248867e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>7.189849889343208e-08</v>
+        <v>7.189849889343194e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>7.177336623496104e-08</v>
+        <v>7.177336623496091e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>7.732630906158443e-08</v>
+        <v>7.732630906158428e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>6.837856389130631e-08</v>
+        <v>6.438004932586868e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>7.195847823627882e-08</v>
+        <v>7.195847823627869e-08</v>
       </c>
     </row>
   </sheetData>
@@ -4475,37 +4475,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.076548180108735e-08</v>
+        <v>1.728210093795388e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>6.642025172779733e-08</v>
+        <v>1.357424664944455e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>7.127457610449904e-08</v>
+        <v>1.730889355999974e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>6.869668297927515e-08</v>
+        <v>1.495405123861029e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>6.869668297927514e-08</v>
+        <v>1.495466737982937e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>7.111769315210347e-08</v>
+        <v>1.730063712180977e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>7.128684410605926e-08</v>
+        <v>1.727312457295175e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>7.152421278887792e-08</v>
+        <v>1.732135410305856e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>7.85149339571934e-08</v>
+        <v>1.86323553128251e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>8.039595999597186e-08</v>
+        <v>2.50871372235392e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>7.127499567165222e-08</v>
+        <v>1.7300515185299e-08</v>
       </c>
     </row>
     <row r="3">
@@ -4515,37 +4515,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.735485636183318e-08</v>
+        <v>1.597272824299962e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>7.301247950370892e-08</v>
+        <v>9.904016967142491e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>7.794042026932386e-08</v>
+        <v>1.616917791632092e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>7.539809114349835e-08</v>
+        <v>1.236660036687758e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>7.539809114349835e-08</v>
+        <v>1.236721650809667e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>7.775997237586325e-08</v>
+        <v>1.611122491293716e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>7.796815294687149e-08</v>
+        <v>1.614291967288034e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>7.820831783948619e-08</v>
+        <v>1.625834735976879e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>8.608678731168081e-08</v>
+        <v>2.0098483120765e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>8.702599635517838e-08</v>
+        <v>2.894008739233353e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>7.794091619130011e-08</v>
+        <v>1.616775802287709e-08</v>
       </c>
     </row>
     <row r="4">
@@ -4555,34 +4555,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.893527138193985e-08</v>
+        <v>4.893527138193984e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>4.864243055280412e-08</v>
+        <v>4.864243055280411e-08</v>
       </c>
       <c r="D4" t="n">
         <v>4.923790637316255e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>4.876975902017694e-08</v>
+        <v>4.87697590201769e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>4.876975902017694e-08</v>
+        <v>4.87697590201769e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>4.908023524042565e-08</v>
+        <v>4.908023524042564e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>4.924625254335853e-08</v>
+        <v>4.924625254335852e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>4.894358684979079e-08</v>
+        <v>4.894358684979077e-08</v>
       </c>
       <c r="J4" t="n">
         <v>5.282351514495596e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>4.909619392323538e-08</v>
+        <v>4.90961939232354e-08</v>
       </c>
       <c r="L4" t="n">
         <v>4.923995705656967e-08</v>
@@ -4595,37 +4595,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.841744849200283e-08</v>
+        <v>5.84174484920028e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>5.978278798149392e-08</v>
+        <v>5.978278798149389e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>6.648004878022669e-08</v>
+        <v>6.64800487802266e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>6.865903400573023e-08</v>
+        <v>6.865903400573032e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>6.865903400573023e-08</v>
+        <v>6.865903400573032e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>6.527072366578329e-08</v>
+        <v>6.527072366578335e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>6.920640344824545e-08</v>
+        <v>6.92064034482454e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>6.865763422277238e-08</v>
+        <v>6.865763422277225e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>1.315079630471374e-07</v>
+        <v>1.315079630471375e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>6.414263041938559e-08</v>
+        <v>6.414263041938558e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>6.954498098309083e-08</v>
+        <v>6.954498098309079e-08</v>
       </c>
     </row>
     <row r="6">
@@ -4635,37 +4635,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.736296906811927e-08</v>
+        <v>5.392012834299273e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>4.72914894052134e-08</v>
+        <v>4.729148940521339e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>4.766765625694569e-08</v>
+        <v>4.766760877678354e-08</v>
       </c>
       <c r="E6" t="n">
         <v>4.719988357789109e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>4.737802366227887e-08</v>
+        <v>4.737802366227886e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>5.406509220147848e-08</v>
+        <v>4.750793292660508e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>5.590552417945581e-08</v>
+        <v>5.590552417945579e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>5.392844381084361e-08</v>
+        <v>4.737128453597019e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>5.141545249662641e-08</v>
+        <v>5.812664321910741e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>4.748441417783804e-08</v>
+        <v>4.748441417783806e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>4.766785794743705e-08</v>
+        <v>4.766785794743717e-08</v>
       </c>
     </row>
     <row r="7">
@@ -4675,37 +4675,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.406580745805493e-08</v>
+        <v>5.406580745805495e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>5.410879790160043e-08</v>
+        <v>5.410879790160041e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>5.436730050533927e-08</v>
+        <v>5.436730050533929e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>5.409643802916596e-08</v>
+        <v>5.409643802916594e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>5.409643802916596e-08</v>
+        <v>5.409643802916594e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>5.421077131654074e-08</v>
+        <v>5.421077131654076e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>5.437678861947361e-08</v>
+        <v>5.437678861947362e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>5.407412292590587e-08</v>
+        <v>5.407412292590585e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>5.795405122107104e-08</v>
+        <v>5.795405122107106e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>5.422672999935047e-08</v>
+        <v>5.422672999935048e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>5.437049313268477e-08</v>
+        <v>5.437049313268478e-08</v>
       </c>
     </row>
     <row r="8">
@@ -4715,37 +4715,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.29502828407622e-08</v>
+        <v>6.295028284076219e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>7.473503159259401e-08</v>
+        <v>7.473503159211259e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>7.740066656792464e-08</v>
+        <v>7.740066656792458e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>7.149411296487101e-08</v>
+        <v>7.149411296487095e-08</v>
       </c>
       <c r="F8" t="n">
         <v>6.334459738524528e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>7.481320122818138e-08</v>
+        <v>7.481320122818136e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>7.497921853130971e-08</v>
+        <v>7.497921853130972e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>7.467655283754653e-08</v>
+        <v>7.46765528375465e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>7.855878404484769e-08</v>
+        <v>7.855878404484771e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>6.289353836016619e-08</v>
+        <v>6.289353836016623e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>8.721330638927218e-08</v>
+        <v>8.72133063892722e-08</v>
       </c>
     </row>
     <row r="9">
@@ -4755,37 +4755,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.466828473743771e-08</v>
+        <v>6.466828473743773e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>7.02866703647521e-08</v>
+        <v>7.028667036475207e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>7.054632326794038e-08</v>
+        <v>7.054632326794033e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>7.668729394700378e-08</v>
+        <v>7.668729394700374e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>7.025339788976551e-08</v>
+        <v>7.025339788976547e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>7.038864377969245e-08</v>
+        <v>7.03886437796924e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>7.055466108262528e-08</v>
+        <v>7.055466108262524e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>7.025199538905753e-08</v>
+        <v>7.025199538905746e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>7.41319236842227e-08</v>
+        <v>7.413192368422267e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>6.704313826805428e-08</v>
+        <v>6.704313826805427e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>7.054836559583641e-08</v>
+        <v>7.054836559583638e-08</v>
       </c>
     </row>
   </sheetData>
@@ -4871,37 +4871,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.477941465824342e-08</v>
+        <v>2.01527672469479e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>7.610639860815361e-08</v>
+        <v>2.183987671834847e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.94924175019075e-07</v>
+        <v>2.64757473580241e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>7.752914300018178e-08</v>
+        <v>2.307540536830478e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>7.260307376560527e-08</v>
+        <v>1.897574339696803e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.330963656393464e-07</v>
+        <v>2.322187255028937e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>8.038921043608393e-08</v>
+        <v>2.036275234765389e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>7.396131405944551e-08</v>
+        <v>2.010833112512714e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>9.527920743310768e-08</v>
+        <v>2.825251108860418e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>9.073601515791855e-08</v>
+        <v>3.064361398640971e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>8.477766149972917e-08</v>
+        <v>2.062293123176011e-08</v>
       </c>
     </row>
     <row r="3">
@@ -4911,37 +4911,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.209408734769323e-08</v>
+        <v>1.715240904701491e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>8.328083046761461e-08</v>
+        <v>1.976294295991322e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>2.202854496747808e-07</v>
+        <v>6.214496929943278e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>8.471698925821235e-08</v>
+        <v>2.174713789510561e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>7.979092002363586e-08</v>
+        <v>1.497947385347388e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.491706612959641e-07</v>
+        <v>3.901978815498249e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>8.856313557577534e-08</v>
+        <v>1.920214628253195e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>8.10889314704791e-08</v>
+        <v>1.683348298437359e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.043206133612353e-07</v>
+        <v>3.384876525827529e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>9.858832656923555e-08</v>
+        <v>3.550004780930798e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>9.359731333021046e-08</v>
+        <v>2.089847433283109e-08</v>
       </c>
     </row>
     <row r="4">
@@ -4951,37 +4951,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.385637423259198e-08</v>
+        <v>5.385637423259202e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>5.193866059774508e-08</v>
+        <v>5.193866059774505e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>1.252773433017556e-07</v>
+        <v>1.252773433017555e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>5.214793307232843e-08</v>
+        <v>5.214793307232839e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>5.214793307232843e-08</v>
+        <v>5.214793307232839e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>8.8441623888895e-08</v>
+        <v>8.844162388889508e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>5.720462646350092e-08</v>
+        <v>5.720462646350095e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>5.280170920539308e-08</v>
+        <v>5.280170920539306e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>6.069006854584255e-08</v>
+        <v>6.069006854584257e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>5.598412540683837e-08</v>
+        <v>5.598412540683839e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>5.981542105323281e-08</v>
+        <v>5.981542105323283e-08</v>
       </c>
     </row>
     <row r="5">
@@ -4991,37 +4991,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.02626539694201e-07</v>
+        <v>1.026265396942014e-07</v>
       </c>
       <c r="C5" t="n">
-        <v>9.160117860878702e-08</v>
+        <v>9.160117860878689e-08</v>
       </c>
       <c r="D5" t="n">
         <v>1.378042477972858e-06</v>
       </c>
       <c r="E5" t="n">
-        <v>9.160119521913613e-08</v>
+        <v>9.160119521913594e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>9.160119521913613e-08</v>
+        <v>9.160119521913594e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>7.374586873067062e-07</v>
+        <v>7.374586873067065e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>1.773803533566599e-07</v>
+        <v>1.773803533566598e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>9.159166800711932e-08</v>
+        <v>9.159166800711921e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>2.357432001681875e-07</v>
+        <v>2.357432001681874e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>1.41243026622962e-07</v>
+        <v>1.412430266229625e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>1.346723027846053e-07</v>
+        <v>1.346723027846051e-07</v>
       </c>
     </row>
     <row r="6">
@@ -5031,37 +5031,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.32253747617238e-08</v>
+        <v>5.332101161452594e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>5.13123262484685e-08</v>
+        <v>5.131232624846846e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.26505099422529e-07</v>
+        <v>1.26505129421823e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>5.120906529252704e-08</v>
+        <v>5.120906529252701e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>5.218467470406156e-08</v>
+        <v>5.218467470406153e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>9.781062441802671e-08</v>
+        <v>8.79062612708289e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>6.74836084003576e-08</v>
+        <v>6.748360840035763e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>6.217070973452487e-08</v>
+        <v>6.217070973452484e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>7.051952756817765e-08</v>
+        <v>6.043960291024637e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>5.475869598593029e-08</v>
+        <v>5.475869598593017e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>5.933148919646436e-08</v>
+        <v>5.933148919646439e-08</v>
       </c>
     </row>
     <row r="7">
@@ -5071,37 +5071,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.153990325231265e-08</v>
+        <v>6.15399032523126e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>6.049474882678138e-08</v>
+        <v>6.049474882678135e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.329595329286205e-07</v>
+        <v>1.329595329286204e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>6.04761366207193e-08</v>
+        <v>6.047613662071927e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>6.04761366207193e-08</v>
+        <v>6.047613662071927e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>9.612515290861562e-08</v>
+        <v>9.612515290861565e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>6.48881554832216e-08</v>
+        <v>6.488815548322155e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>6.048523822511369e-08</v>
+        <v>6.048523822511368e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>6.837359756556318e-08</v>
+        <v>6.837359756556319e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>6.366765442655899e-08</v>
+        <v>6.3667654426559e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>6.74989500729535e-08</v>
+        <v>6.749895007295343e-08</v>
       </c>
     </row>
     <row r="8">
@@ -5111,31 +5111,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7.255230637890621e-08</v>
+        <v>7.255230637890624e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>8.672116899058664e-08</v>
+        <v>8.672116899095249e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>1.623578108642307e-07</v>
+        <v>1.623578108642306e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>8.25576921806784e-08</v>
+        <v>8.255769218067835e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>7.197953006361223e-08</v>
+        <v>7.197953006361216e-08</v>
       </c>
       <c r="G8" t="n">
         <v>1.223646535800764e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>9.112765615467808e-08</v>
+        <v>9.112765615467807e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>8.672473889657446e-08</v>
+        <v>8.672473889657443e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>9.461609079647821e-08</v>
+        <v>9.461609079647822e-08</v>
       </c>
       <c r="K8" t="n">
         <v>7.439720639830304e-08</v>
@@ -5151,34 +5151,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8.845501879699705e-08</v>
+        <v>8.845501879699704e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>9.843545895211437e-08</v>
+        <v>9.843545895211429e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>1.709016120925487e-07</v>
+        <v>1.709016120925486e-07</v>
       </c>
       <c r="E9" t="n">
-        <v>1.11158808803207e-07</v>
+        <v>1.111588088032071e-07</v>
       </c>
       <c r="F9" t="n">
-        <v>9.843547882320068e-08</v>
+        <v>9.84354788232006e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>1.340658630339485e-07</v>
+        <v>1.340658630339486e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>1.028288656085545e-07</v>
+        <v>1.028288656085546e-07</v>
       </c>
       <c r="I9" t="n">
-        <v>9.842594835044669e-08</v>
+        <v>9.842594835044661e-08</v>
       </c>
       <c r="J9" t="n">
         <v>1.063143076908961e-07</v>
       </c>
       <c r="K9" t="n">
-        <v>9.522010421989545e-08</v>
+        <v>9.522010421989551e-08</v>
       </c>
       <c r="L9" t="n">
         <v>1.054396601982863e-07</v>
@@ -5267,37 +5267,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.314214778163716e-08</v>
+        <v>1.985373132356613e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>7.606840292786619e-08</v>
+        <v>2.158913363352745e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.855871651087698e-07</v>
+        <v>2.577148925170024e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>7.746708587262097e-08</v>
+        <v>2.280324894548135e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>7.260828542904617e-08</v>
+        <v>1.875957903813456e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.31381720408999e-07</v>
+        <v>2.291876435783603e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>7.917665847109863e-08</v>
+        <v>2.008694428816872e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>7.397025338599867e-08</v>
+        <v>1.989597504836775e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>9.168020866993602e-08</v>
+        <v>2.772027999134579e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>9.035824080858667e-08</v>
+        <v>3.037569230230962e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>8.392932186123218e-08</v>
+        <v>2.036633812373735e-08</v>
       </c>
     </row>
     <row r="3">
@@ -5307,37 +5307,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.034667298752558e-08</v>
+        <v>1.642988479213936e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>8.338144406570814e-08</v>
+        <v>1.959107314259713e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>2.096817358288948e-07</v>
+        <v>5.850288568753145e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>8.479218012564776e-08</v>
+        <v>2.154150733399992e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>7.993337968207293e-08</v>
+        <v>1.486626872038781e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.473342458001166e-07</v>
+        <v>3.825196760983243e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>8.730461043473848e-08</v>
+        <v>1.863650035549258e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>8.123735946929483e-08</v>
+        <v>1.672655051298399e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.003418347550277e-07</v>
+        <v>3.222057587609868e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>9.829636463364861e-08</v>
+        <v>3.519730861029482e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>9.275729888219308e-08</v>
+        <v>2.047029812039085e-08</v>
       </c>
     </row>
     <row r="4">
@@ -5347,28 +5347,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.24729099934337e-08</v>
+        <v>5.247290999343372e-08</v>
       </c>
       <c r="C4" t="n">
         <v>5.183997777512812e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>1.193167080948518e-07</v>
+        <v>1.193167080948519e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>5.202212845419867e-08</v>
+        <v>5.202212845419868e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>5.202212845419867e-08</v>
+        <v>5.202212845419868e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>8.701767153318416e-08</v>
+        <v>8.701767153318435e-08</v>
       </c>
       <c r="H4" t="n">
         <v>5.60735089178697e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>5.243412568872031e-08</v>
+        <v>5.243412568872033e-08</v>
       </c>
       <c r="J4" t="n">
         <v>5.82395112083779e-08</v>
@@ -5387,37 +5387,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.428400015375219e-08</v>
+        <v>8.42840001537523e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>8.971374220757357e-08</v>
+        <v>8.971374220757352e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>1.182402189211097e-06</v>
+        <v>1.1824021892111e-06</v>
       </c>
       <c r="E5" t="n">
-        <v>8.97137521831762e-08</v>
+        <v>8.971375218317615e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>8.97137521831762e-08</v>
+        <v>8.971375218317615e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>6.689614552142816e-07</v>
+        <v>6.689614552142829e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>1.568411456005973e-07</v>
+        <v>1.56841145600597e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>8.970450963296835e-08</v>
+        <v>8.970450963296833e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>1.886553080567127e-07</v>
+        <v>1.886553080567126e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>1.298481629538902e-07</v>
+        <v>1.298481629538904e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>1.463539870233441e-07</v>
+        <v>1.463539870233442e-07</v>
       </c>
     </row>
     <row r="6">
@@ -5427,37 +5427,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.115473377713201e-08</v>
+        <v>5.198868485974577e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>5.110108824750824e-08</v>
+        <v>5.110108824750827e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.203143641614795e-07</v>
+        <v>1.203143641614808e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>5.100109657467255e-08</v>
+        <v>5.100109657467256e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>5.187186501565833e-08</v>
+        <v>5.187186501565836e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>9.569949531688251e-08</v>
+        <v>8.653344639949642e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>6.552262371343387e-08</v>
+        <v>6.552262371343394e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>6.111594947241857e-08</v>
+        <v>6.111594947241856e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>6.732605647418746e-08</v>
+        <v>5.800256922790374e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>5.425533795131775e-08</v>
+        <v>5.425533795131785e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>5.847794224489899e-08</v>
+        <v>5.847794224489906e-08</v>
       </c>
     </row>
     <row r="7">
@@ -5467,37 +5467,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.942896436881953e-08</v>
+        <v>5.942896436881958e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>5.939941263871139e-08</v>
+        <v>5.939941263871143e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.262715133365446e-07</v>
+        <v>1.262715133365448e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>5.937842090609831e-08</v>
+        <v>5.937842090609832e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>5.937842090609831e-08</v>
+        <v>5.937842090609833e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>9.397372590857017e-08</v>
+        <v>9.397372590857022e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>6.302956329325552e-08</v>
+        <v>6.302956329325557e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>5.939018006410614e-08</v>
+        <v>5.939018006410616e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>6.519556558376371e-08</v>
+        <v>6.519556558376376e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>6.233224357823185e-08</v>
+        <v>6.233224357823189e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>6.585671895640773e-08</v>
+        <v>6.58567189564078e-08</v>
       </c>
     </row>
     <row r="8">
@@ -5507,37 +5507,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.950087224759639e-08</v>
+        <v>6.950087224759645e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>8.335923289843774e-08</v>
+        <v>8.335923289843786e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>1.531313218603923e-07</v>
+        <v>1.531313218603924e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>7.955801273929468e-08</v>
+        <v>7.955801273929476e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>6.990027107449991e-08</v>
+        <v>6.990027107449996e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>1.179492747676413e-07</v>
+        <v>1.179492747676414e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>8.700511215231884e-08</v>
+        <v>8.700511215231893e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>8.336572892317737e-08</v>
+        <v>8.336572892317741e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>8.917384690495421e-08</v>
+        <v>8.91738469049543e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>7.214588418737019e-08</v>
+        <v>7.214588418737027e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>1.043557834221039e-07</v>
+        <v>1.043557834221041e-07</v>
       </c>
     </row>
     <row r="9">
@@ -5547,37 +5547,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8.148841711118714e-08</v>
+        <v>8.148841711118726e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>9.082566387380952e-08</v>
+        <v>9.082566387380963e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>1.576990407979048e-07</v>
+        <v>1.576990407979049e-07</v>
       </c>
       <c r="E9" t="n">
-        <v>1.016347891376201e-07</v>
+        <v>1.016347891376202e-07</v>
       </c>
       <c r="F9" t="n">
-        <v>9.082567700516951e-08</v>
+        <v>9.082567700516956e-08</v>
       </c>
       <c r="G9" t="n">
         <v>1.253999771436683e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>9.445581452835366e-08</v>
+        <v>9.445581452835368e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>9.081643129920426e-08</v>
+        <v>9.081643129920433e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>9.662181681886189e-08</v>
+        <v>9.662181681886193e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>8.196401652155359e-08</v>
+        <v>8.833134637541461e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>9.728297019150595e-08</v>
+        <v>9.728297019150593e-08</v>
       </c>
     </row>
   </sheetData>
@@ -5663,37 +5663,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.228273434517538e-08</v>
+        <v>1.915812608260465e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>7.630860717897071e-08</v>
+        <v>2.093687515149422e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.678669485437351e-07</v>
+        <v>2.418853343033428e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>7.762813723627725e-08</v>
+        <v>2.208044382386741e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>7.300436776257855e-08</v>
+        <v>1.823240099557861e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.231727602926511e-07</v>
+        <v>2.183636707248759e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>7.85282370295685e-08</v>
+        <v>1.940921467554259e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>7.423343876668437e-08</v>
+        <v>1.92595347693557e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>8.575272583266635e-08</v>
+        <v>2.651909688887895e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>8.891880891616994e-08</v>
+        <v>2.968794487994015e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>8.177102847849522e-08</v>
+        <v>1.960842953360084e-08</v>
       </c>
     </row>
     <row r="3">
@@ -5703,37 +5703,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.940728983794723e-08</v>
+        <v>1.575652202997217e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>8.371131815631629e-08</v>
+        <v>1.930524638991125e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.893489363766117e-07</v>
+        <v>5.145911516916256e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>8.504212621983472e-08</v>
+        <v>2.114479921895813e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>8.04183567461361e-08</v>
+        <v>1.479248250799512e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.37941361514661e-07</v>
+        <v>3.480040540314351e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>8.660685463197803e-08</v>
+        <v>1.804197933237741e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>8.159518788957798e-08</v>
+        <v>1.647239677752133e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>9.361913437033989e-08</v>
+        <v>2.933697235628004e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>9.668244611135502e-08</v>
+        <v>3.435219810952043e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>9.0323480730455e-08</v>
+        <v>1.930651689629132e-08</v>
       </c>
     </row>
     <row r="4">
@@ -5743,37 +5743,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.191951935040643e-08</v>
+        <v>5.191951935040639e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>5.216661762423479e-08</v>
+        <v>5.216661762423486e-08</v>
       </c>
       <c r="D4" t="n">
         <v>1.087402844447217e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>5.233865424467053e-08</v>
+        <v>5.233865424467064e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>5.233865424467052e-08</v>
+        <v>5.233865424467064e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>8.210139823929859e-08</v>
+        <v>8.210139823929846e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>5.564376046958116e-08</v>
+        <v>5.564376046958121e-08</v>
       </c>
       <c r="I4" t="n">
         <v>5.259006779002646e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>5.485546615484415e-08</v>
+        <v>5.485546615484416e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>5.444873978681149e-08</v>
+        <v>5.444873978681143e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>5.757340027440159e-08</v>
+        <v>5.757340027440169e-08</v>
       </c>
     </row>
     <row r="5">
@@ -5783,37 +5783,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.977021054781959e-08</v>
+        <v>7.977021054781864e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>9.547692780139447e-08</v>
+        <v>9.547692780139473e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>9.812627539978979e-07</v>
+        <v>9.812627539978983e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>9.547693364739171e-08</v>
+        <v>9.547693364739214e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>9.547693364739171e-08</v>
+        <v>9.547693364739214e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>5.78036656054636e-07</v>
+        <v>5.780366560546354e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>1.512953895538872e-07</v>
+        <v>1.512953895538875e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>9.546887437470277e-08</v>
+        <v>9.5468874374704e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>1.336608311205698e-07</v>
+        <v>1.336608311205694e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>1.171468544266947e-07</v>
+        <v>1.171468544266931e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>1.941878058592438e-07</v>
+        <v>1.042992275833864e-07</v>
       </c>
     </row>
     <row r="6">
@@ -5823,37 +5823,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.132043344480967e-08</v>
+        <v>5.132043344480961e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>5.127313270455857e-08</v>
+        <v>5.127313270455862e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.174238791955305e-07</v>
+        <v>1.093587803173466e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>5.117502469071261e-08</v>
+        <v>5.117502469071258e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>5.192965994429356e-08</v>
+        <v>5.192965994429353e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>8.150231233370174e-08</v>
+        <v>9.028814246361929e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>6.456592340905938e-08</v>
+        <v>6.456592340905936e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>6.077681201434756e-08</v>
+        <v>5.19909818844298e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>5.448015292097285e-08</v>
+        <v>6.340472350766228e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>5.328468854267736e-08</v>
+        <v>5.32846885426773e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>5.700325199089085e-08</v>
+        <v>5.700325199089092e-08</v>
       </c>
     </row>
     <row r="7">
@@ -5863,37 +5863,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.860873642699554e-08</v>
+        <v>5.860873642699556e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>5.928733829330632e-08</v>
+        <v>5.92873382933063e-08</v>
       </c>
       <c r="D7" t="n">
         <v>1.154282531573875e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>5.926686890964251e-08</v>
+        <v>5.926686890964259e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>5.926686890964251e-08</v>
+        <v>5.926686890964258e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>8.879061531588738e-08</v>
+        <v>8.879061531588732e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>6.233297754617023e-08</v>
+        <v>6.23329775461703e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>5.927928486661558e-08</v>
+        <v>5.92792848666156e-08</v>
       </c>
       <c r="J7" t="n">
         <v>6.154468323143326e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>6.113795686340058e-08</v>
+        <v>6.113795686340048e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>6.426261735099077e-08</v>
+        <v>6.426261735099076e-08</v>
       </c>
     </row>
     <row r="8">
@@ -5903,37 +5903,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.836694706242371e-08</v>
+        <v>6.836694706242375e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>8.251079306361294e-08</v>
+        <v>8.251079306361302e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>1.414635441620977e-07</v>
+        <v>1.414635441620978e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>7.88252338390009e-08</v>
+        <v>7.882523383900091e-08</v>
       </c>
       <c r="F8" t="n">
         <v>6.946139769250664e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>1.120293777281127e-07</v>
+        <v>1.120293777281128e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>8.557173995838723e-08</v>
+        <v>8.557173995838726e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>8.251804727884079e-08</v>
+        <v>8.251804727884081e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>8.47860949565925e-08</v>
+        <v>8.478609495659253e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>7.06457593283599e-08</v>
+        <v>7.064575932835987e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>1.015829433186153e-07</v>
+        <v>1.015829433186154e-07</v>
       </c>
     </row>
     <row r="9">
@@ -5943,37 +5943,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7.746609277400745e-08</v>
+        <v>7.746609277400729e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>8.652854342868096e-08</v>
+        <v>8.6528543428681e-08</v>
       </c>
       <c r="D9" t="n">
         <v>1.426707309236685e-07</v>
       </c>
       <c r="E9" t="n">
-        <v>9.620335861069904e-08</v>
+        <v>9.620335861069896e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>8.652855220565379e-08</v>
+        <v>8.652855220565383e-08</v>
       </c>
       <c r="G9" t="n">
         <v>1.160318204512621e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>8.9574182681545e-08</v>
+        <v>8.957418268154505e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>8.652049000199029e-08</v>
+        <v>8.65204900019903e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>8.878588836680798e-08</v>
+        <v>8.878588836680795e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>8.352153729148155e-08</v>
+        <v>8.352153729148144e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>9.150382248636543e-08</v>
+        <v>9.150382248636551e-08</v>
       </c>
     </row>
   </sheetData>
@@ -6059,37 +6059,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.010198369925728e-08</v>
+        <v>1.601413325969012e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>7.259494428365472e-08</v>
+        <v>1.810274863135564e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>9.962623415853243e-08</v>
+        <v>1.75679359214772e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>7.386272452973236e-08</v>
+        <v>1.918158459295929e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>6.938708226252291e-08</v>
+        <v>1.545681294106264e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>8.375405908324879e-08</v>
+        <v>1.673261487194388e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>7.235590776077554e-08</v>
+        <v>1.608542439650256e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>7.004075342797718e-08</v>
+        <v>1.600997011122311e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>8.195290877166216e-08</v>
+        <v>2.344725129386684e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>8.576479163254537e-08</v>
+        <v>2.678548582328004e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.167799342743018e-07</v>
+        <v>1.848386471389719e-08</v>
       </c>
     </row>
     <row r="3">
@@ -6099,37 +6099,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.662899599598296e-08</v>
+        <v>1.322275320853113e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>7.909988780877079e-08</v>
+        <v>1.668393824567558e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.105879999542071e-07</v>
+        <v>2.422491267067319e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>8.037785466298594e-08</v>
+        <v>1.844055577777086e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>7.590221239577649e-08</v>
+        <v>1.229173723043077e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>9.233171070646926e-08</v>
+        <v>1.832656524011554e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>7.92352598792179e-08</v>
+        <v>1.402963178593348e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>7.652467602130585e-08</v>
+        <v>1.31892471996405e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>8.894826625630819e-08</v>
+        <v>2.639696856389365e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>9.272829857187708e-08</v>
+        <v>3.183472005195716e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.303167311170781e-07</v>
+        <v>3.083166641279962e-08</v>
       </c>
     </row>
     <row r="4">
@@ -6139,37 +6139,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.038288483321616e-08</v>
+        <v>5.038288483321618e-08</v>
       </c>
       <c r="C4" t="n">
         <v>4.937627805755003e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>6.793380068263977e-08</v>
+        <v>6.793380068263975e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>4.95536029947802e-08</v>
+        <v>4.955360299478019e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>4.95536029947802e-08</v>
+        <v>4.955360299478019e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>5.843321662536783e-08</v>
+        <v>5.843321662536785e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>5.172644639027768e-08</v>
+        <v>5.172644639027772e-08</v>
       </c>
       <c r="I4" t="n">
         <v>4.989417237455132e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>5.223640092686615e-08</v>
+        <v>5.223640092686616e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>5.211034967267504e-08</v>
+        <v>5.211034967267508e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>7.812570312765974e-08</v>
+        <v>7.812570312765975e-08</v>
       </c>
     </row>
     <row r="5">
@@ -6179,34 +6179,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.071432048563672e-08</v>
+        <v>8.071432048563745e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>7.727707045033685e-08</v>
+        <v>7.727707045033683e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>3.639534305145984e-07</v>
+        <v>3.639534305145985e-07</v>
       </c>
       <c r="E5" t="n">
         <v>7.727708438946591e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>7.727708438946591e-08</v>
+        <v>7.727708438946593e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>2.207349903033788e-07</v>
+        <v>2.207349903033787e-07</v>
       </c>
       <c r="H5" t="n">
         <v>1.092346612892197e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>7.727378091072851e-08</v>
+        <v>7.727378091072849e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>1.181040145949855e-07</v>
+        <v>1.181040145949858e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>1.093856120673313e-07</v>
+        <v>1.093856120673316e-07</v>
       </c>
       <c r="L5" t="n">
         <v>6.419524863487127e-07</v>
@@ -6219,37 +6219,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.901236002607687e-08</v>
+        <v>5.668356532883664e-08</v>
       </c>
       <c r="C6" t="n">
         <v>4.821123516705647e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>7.455466049710182e-08</v>
+        <v>7.455466049710179e-08</v>
       </c>
       <c r="E6" t="n">
         <v>4.813591350298838e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>4.849622027653215e-08</v>
+        <v>4.849622027653216e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>5.706269181822856e-08</v>
+        <v>6.473389712098833e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>5.882384582553446e-08</v>
+        <v>5.035765422597209e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>4.852364756741204e-08</v>
+        <v>5.619485287017175e-08</v>
       </c>
       <c r="J6" t="n">
         <v>5.878987410534709e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>5.058233807088085e-08</v>
+        <v>5.058233807088086e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>7.69222480345754e-08</v>
+        <v>7.692224803457539e-08</v>
       </c>
     </row>
     <row r="7">
@@ -6259,34 +6259,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.611181230888991e-08</v>
+        <v>5.611181230888994e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>5.562638938983344e-08</v>
+        <v>5.562638938983343e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>7.366139516955631e-08</v>
+        <v>7.366139516955629e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>5.562031217931865e-08</v>
+        <v>5.562031217931862e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>5.562031217931865e-08</v>
+        <v>5.562031217931863e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>6.416214410104162e-08</v>
+        <v>6.416214410104163e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>5.745537386595147e-08</v>
+        <v>5.745537386595145e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>5.562309985022509e-08</v>
+        <v>5.562309985022507e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>5.796532840253992e-08</v>
+        <v>5.796532840253991e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>5.783927714834879e-08</v>
+        <v>5.783927714834878e-08</v>
       </c>
       <c r="L7" t="n">
         <v>8.38546306033336e-08</v>
@@ -6299,10 +6299,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.541932169906671e-08</v>
+        <v>6.541932169906676e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>7.74343574832042e-08</v>
+        <v>7.743435748320416e-08</v>
       </c>
       <c r="D8" t="n">
         <v>9.806471741587081e-08</v>
@@ -6311,22 +6311,22 @@
         <v>7.401492589235704e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>6.532737119518335e-08</v>
+        <v>6.532737119518332e-08</v>
       </c>
       <c r="G8" t="n">
         <v>8.597174354278657e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>7.926497330769442e-08</v>
+        <v>7.926497330769439e-08</v>
       </c>
       <c r="I8" t="n">
         <v>7.743269929196999e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>7.977738486239404e-08</v>
+        <v>7.977738486239396e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>6.69145537968109e-08</v>
+        <v>6.691455379681097e-08</v>
       </c>
       <c r="L8" t="n">
         <v>1.187237085118193e-07</v>
@@ -6342,13 +6342,13 @@
         <v>7.361911510223613e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>8.084295326691364e-08</v>
+        <v>8.084295326691363e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>9.887930461391841e-08</v>
+        <v>9.887930461391844e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>8.973930482654859e-08</v>
+        <v>8.973930482654863e-08</v>
       </c>
       <c r="F9" t="n">
         <v>8.084296914355962e-08</v>
@@ -6357,19 +6357,19 @@
         <v>8.93787079781218e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>8.267193774303162e-08</v>
+        <v>8.267193774303166e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>8.083966372730534e-08</v>
+        <v>8.083966372730529e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>8.318189227962008e-08</v>
+        <v>8.318189227962016e-08</v>
       </c>
       <c r="K9" t="n">
         <v>7.858907016738739e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>1.090711944804137e-07</v>
+        <v>1.090711944804138e-07</v>
       </c>
     </row>
   </sheetData>
@@ -6455,37 +6455,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.066168539526616e-08</v>
+        <v>1.511060512875634e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>7.351568982881216e-08</v>
+        <v>1.731776829980244e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>7.207479117662667e-08</v>
+        <v>1.518497407937519e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>7.474272068678219e-08</v>
+        <v>1.835607753897256e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>7.03842399004554e-08</v>
+        <v>1.472882050850698e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>7.228840844812318e-08</v>
+        <v>1.519621633209598e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>6.920640476224364e-08</v>
+        <v>1.499479768281173e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>7.083946823641146e-08</v>
+        <v>1.511916862066261e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>8.429872081344552e-08</v>
+        <v>2.259881871262934e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>8.679751464386184e-08</v>
+        <v>2.601953097768249e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>6.806235728109338e-08</v>
+        <v>1.496152103137656e-08</v>
       </c>
     </row>
     <row r="3">
@@ -6495,37 +6495,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.735065155874761e-08</v>
+        <v>1.288277202434261e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>8.022056789677593e-08</v>
+        <v>1.659822419758541e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>7.897601593129287e-08</v>
+        <v>1.340495362427434e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>8.145612816229687e-08</v>
+        <v>1.829594458402169e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>7.709764737597e-08</v>
+        <v>1.230809633822364e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>7.922172004419847e-08</v>
+        <v>1.348898714132725e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>7.569022567096964e-08</v>
+        <v>1.230510560903863e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>7.753033680793419e-08</v>
+        <v>1.293684049640318e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>9.173181304176581e-08</v>
+        <v>2.667130244954871e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>9.397232045343072e-08</v>
+        <v>3.181282580729323e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>7.436110965057936e-08</v>
+        <v>1.190494878884178e-08</v>
       </c>
     </row>
     <row r="4">
@@ -6535,7 +6535,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.026599594819931e-08</v>
+        <v>5.026599594819934e-08</v>
       </c>
       <c r="C4" t="n">
         <v>4.980536710163577e-08</v>
@@ -6544,22 +6544,22 @@
         <v>5.110602745684682e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>4.994673873173852e-08</v>
+        <v>4.994673873173851e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>4.994673873173852e-08</v>
+        <v>4.994673873173853e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>5.117704066631075e-08</v>
+        <v>5.117704066631085e-08</v>
       </c>
       <c r="H4" t="n">
         <v>4.940261162136135e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>4.9983228695038e-08</v>
+        <v>4.998322869503799e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>5.321093842323103e-08</v>
+        <v>5.321093842323104e-08</v>
       </c>
       <c r="K4" t="n">
         <v>5.218874785466166e-08</v>
@@ -6578,31 +6578,31 @@
         <v>8.994814431890248e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>8.762774904805633e-08</v>
+        <v>8.762774904805641e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>1.003522234028512e-07</v>
+        <v>1.003522234028513e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>8.762775518524904e-08</v>
+        <v>8.76277551852491e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>8.762775518524904e-08</v>
+        <v>8.76277551852491e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>1.045099130611394e-07</v>
+        <v>1.045099130611403e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>7.842714524925685e-08</v>
+        <v>7.842714524925688e-08</v>
       </c>
       <c r="I5" t="n">
         <v>8.762617832261054e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>1.407192026429833e-07</v>
+        <v>1.407192026429832e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>1.182373114996304e-07</v>
+        <v>1.182373114996303e-07</v>
       </c>
       <c r="L5" t="n">
         <v>9.192364932345316e-08</v>
@@ -6621,7 +6621,7 @@
         <v>4.850203622193701e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>4.976213006242229e-08</v>
+        <v>4.976216191408965e-08</v>
       </c>
       <c r="E6" t="n">
         <v>4.842788145405034e-08</v>
@@ -6630,22 +6630,22 @@
         <v>4.859767150088785e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>4.979718340735536e-08</v>
+        <v>5.625100377731383e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>4.801422541513149e-08</v>
+        <v>5.510288829842838e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>4.860337143608259e-08</v>
+        <v>5.505719180604114e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>5.843690350157736e-08</v>
+        <v>5.198177798841888e-08</v>
       </c>
       <c r="K6" t="n">
         <v>5.080861028282545e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>4.736129347865982e-08</v>
+        <v>4.736129347865984e-08</v>
       </c>
     </row>
     <row r="7">
@@ -6664,22 +6664,22 @@
         <v>5.592966571523947e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>5.480716197442216e-08</v>
+        <v>5.480716197442217e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>5.480716197442216e-08</v>
+        <v>5.480716197442217e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>5.600192864487944e-08</v>
+        <v>5.600192864487952e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>5.422749959993002e-08</v>
+        <v>5.422749959993003e-08</v>
       </c>
       <c r="I7" t="n">
         <v>5.480811667360664e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>5.803582640179969e-08</v>
+        <v>5.80358264017997e-08</v>
       </c>
       <c r="K7" t="n">
         <v>5.701363583323032e-08</v>
@@ -6695,25 +6695,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.329081561658875e-08</v>
+        <v>6.329081561658876e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>7.392601004398115e-08</v>
+        <v>7.392601004398111e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>7.730919278939764e-08</v>
+        <v>7.730919278939765e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>7.094032513940137e-08</v>
+        <v>7.09403251394014e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>6.335485048579408e-08</v>
+        <v>6.335485048579407e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>7.51169011755544e-08</v>
+        <v>7.511690117555443e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>7.33424721306033e-08</v>
+        <v>7.334247213060328e-08</v>
       </c>
       <c r="I8" t="n">
         <v>7.392308920428155e-08</v>
@@ -6722,10 +6722,10 @@
         <v>7.71529440501412e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>6.501081503523767e-08</v>
+        <v>6.501081503523769e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>8.406520119363715e-08</v>
+        <v>8.406520119363719e-08</v>
       </c>
     </row>
     <row r="9">
@@ -6735,37 +6735,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.800618776483898e-08</v>
+        <v>6.8006187764839e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>7.377985306872947e-08</v>
+        <v>7.37798530687295e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>7.490108973372475e-08</v>
+        <v>7.490108973372478e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>8.076705219910379e-08</v>
+        <v>8.07670521991038e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>7.377986162449524e-08</v>
+        <v>7.377986162449523e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>7.497209431455646e-08</v>
+        <v>7.497209431455651e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>7.319766526960706e-08</v>
+        <v>7.31976652696071e-08</v>
       </c>
       <c r="I9" t="n">
         <v>7.377828234328368e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>7.700599207147671e-08</v>
+        <v>7.700599207147676e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>7.233326166410492e-08</v>
+        <v>7.247559440756654e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>7.2518721473267e-08</v>
+        <v>7.251872147326704e-08</v>
       </c>
     </row>
   </sheetData>
@@ -6851,37 +6851,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.298456393562656e-08</v>
+        <v>1.524126028166433e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>7.771450867619412e-08</v>
+        <v>1.75679663473399e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>7.024086202471419e-08</v>
+        <v>1.509686469952392e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>7.888840940847024e-08</v>
+        <v>1.856153453752298e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>7.469304925050069e-08</v>
+        <v>1.50700530914394e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>7.142228313212111e-08</v>
+        <v>1.515904054591543e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>6.893653115962936e-08</v>
+        <v>1.498966858286626e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>7.50112474556266e-08</v>
+        <v>1.534718075760714e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>8.598414254427412e-08</v>
+        <v>2.257752138688037e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>8.543491209774297e-08</v>
+        <v>2.595055381381861e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>6.892624499789767e-08</v>
+        <v>1.50168515595039e-08</v>
       </c>
     </row>
     <row r="3">
@@ -6891,37 +6891,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.014272483049681e-08</v>
+        <v>1.376036065617437e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>8.516704174234375e-08</v>
+        <v>1.820186298266549e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>7.698689927680899e-08</v>
+        <v>1.273368146341514e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>8.634888102326013e-08</v>
+        <v>1.982758843408075e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>8.215352086529059e-08</v>
+        <v>1.40638633279752e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>7.834577828097203e-08</v>
+        <v>1.317708194379005e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>7.549966234102658e-08</v>
+        <v>1.221539570077586e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>8.245276052861089e-08</v>
+        <v>1.450571590201653e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>9.381348801508423e-08</v>
+        <v>2.716365660674369e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>9.252641981615056e-08</v>
+        <v>3.130502900099243e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>7.547489466122447e-08</v>
+        <v>1.22415509488885e-08</v>
       </c>
     </row>
     <row r="4">
@@ -6931,37 +6931,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.182140932460063e-08</v>
+        <v>5.182140932460057e-08</v>
       </c>
       <c r="C4" t="n">
         <v>5.265047227199603e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>5.019039479907524e-08</v>
+        <v>5.019039479907523e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>5.278322271283739e-08</v>
+        <v>5.278322271283738e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>5.278322271283739e-08</v>
+        <v>5.278322271283738e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>5.084146302726175e-08</v>
+        <v>5.084146302726169e-08</v>
       </c>
       <c r="H4" t="n">
         <v>4.941660257649306e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>5.267011849840305e-08</v>
+        <v>5.267011849840301e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>5.44776796256541e-08</v>
+        <v>5.447767962565409e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>5.155762368432319e-08</v>
+        <v>5.155762368432317e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>4.94113241001607e-08</v>
+        <v>4.941132410016064e-08</v>
       </c>
     </row>
     <row r="5">
@@ -6971,37 +6971,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.117926248801898e-07</v>
+        <v>1.117926248801897e-07</v>
       </c>
       <c r="C5" t="n">
-        <v>1.271109527254194e-07</v>
+        <v>1.271109527254199e-07</v>
       </c>
       <c r="D5" t="n">
-        <v>8.49557778431424e-08</v>
+        <v>8.495577784314237e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>1.271109546736465e-07</v>
+        <v>1.271109546736468e-07</v>
       </c>
       <c r="F5" t="n">
-        <v>1.271109546736465e-07</v>
+        <v>1.271109546736468e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>9.71437344545594e-08</v>
+        <v>9.714373445455897e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>7.610356011768763e-08</v>
+        <v>7.610356011768757e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>1.271100858316802e-07</v>
+        <v>1.271100858316801e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>1.604653597216805e-07</v>
+        <v>1.604653597216804e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>1.046102708383964e-07</v>
+        <v>1.046102708383963e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>7.6963824860143e-08</v>
+        <v>9.755709133853499e-08</v>
       </c>
     </row>
     <row r="6">
@@ -7011,37 +7011,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.052700141131707e-08</v>
+        <v>5.052700141131705e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>5.136467355308936e-08</v>
+        <v>5.136467355308927e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>4.885924138248339e-08</v>
+        <v>4.885924138248337e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>5.128249486462815e-08</v>
+        <v>5.128249486462813e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>5.138238082158744e-08</v>
+        <v>5.138238082158745e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>5.59370070858617e-08</v>
+        <v>4.954705511397821e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>5.510521286908875e-08</v>
+        <v>5.510521286908874e-08</v>
       </c>
       <c r="I6" t="n">
         <v>5.13757105851195e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>5.969773115895344e-08</v>
+        <v>5.33357721961856e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>5.022687414552815e-08</v>
+        <v>5.022687414552814e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>4.809917017194249e-08</v>
+        <v>4.809917017194248e-08</v>
       </c>
     </row>
     <row r="7">
@@ -7051,37 +7051,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.664115783233788e-08</v>
+        <v>5.664115783233784e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>5.74907338998804e-08</v>
+        <v>5.749073389988032e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>5.500888668392026e-08</v>
+        <v>5.500888668392022e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>5.749007341902348e-08</v>
+        <v>5.749007341902345e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>5.749007341902348e-08</v>
+        <v>5.749007341902345e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>5.566121153499902e-08</v>
+        <v>5.566121153499898e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>5.423635108423039e-08</v>
+        <v>5.423635108423032e-08</v>
       </c>
       <c r="I7" t="n">
         <v>5.748986700614032e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>5.929742813339138e-08</v>
+        <v>5.929742813339134e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>5.637737219206051e-08</v>
+        <v>5.637737219206044e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>5.423107260789793e-08</v>
+        <v>5.423107260789789e-08</v>
       </c>
     </row>
     <row r="8">
@@ -7091,37 +7091,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.478053594972028e-08</v>
+        <v>6.478053594972026e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>7.65026077562245e-08</v>
+        <v>7.650260775622447e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>7.627271159082927e-08</v>
+        <v>7.627271159082931e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>7.352922042258814e-08</v>
+        <v>7.352922042258813e-08</v>
       </c>
       <c r="F8" t="n">
         <v>6.597501029533608e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>7.466994763413881e-08</v>
+        <v>7.466994763413875e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>7.324508718336932e-08</v>
+        <v>7.324508718336926e-08</v>
       </c>
       <c r="I8" t="n">
         <v>7.64986031052801e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>7.830830037219506e-08</v>
+        <v>7.830830037219499e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>6.431484640418796e-08</v>
+        <v>6.431484640418795e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>8.459376200013994e-08</v>
+        <v>8.459376200013985e-08</v>
       </c>
     </row>
     <row r="9">
@@ -7131,37 +7131,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.856127863586008e-08</v>
+        <v>6.856127863586001e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>7.518735698743201e-08</v>
+        <v>7.518735698743193e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>7.270677442104621e-08</v>
+        <v>7.270677442104613e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>8.185333067363361e-08</v>
+        <v>8.18533306736335e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>7.518736159796853e-08</v>
+        <v>7.518736159796849e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>7.335783462255062e-08</v>
+        <v>7.335783462255055e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>7.193297417178195e-08</v>
+        <v>7.193297417178192e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>7.518649009369192e-08</v>
+        <v>7.518649009369188e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>7.699405122094301e-08</v>
+        <v>7.699405122094291e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>7.059128125627387e-08</v>
+        <v>7.059128125627382e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>7.192769569544953e-08</v>
+        <v>7.192769569544947e-08</v>
       </c>
     </row>
   </sheetData>
@@ -7247,37 +7247,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.359981867394297e-08</v>
+        <v>1.91267605605282e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>7.510235281877167e-08</v>
+        <v>2.084032057933529e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.883421453113034e-07</v>
+        <v>2.516542131483575e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>7.645963819226998e-08</v>
+        <v>2.201458663151153e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>7.172133608196477e-08</v>
+        <v>1.80712085747409e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.217688078045667e-07</v>
+        <v>2.166179878715465e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>8.008908364305739e-08</v>
+        <v>1.939276382274537e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>7.294211728330266e-08</v>
+        <v>1.909085835409939e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>8.479373203136393e-08</v>
+        <v>2.650581885074056e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>8.961365637163067e-08</v>
+        <v>2.965700509577339e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>8.218196312070921e-08</v>
+        <v>1.953093230795515e-08</v>
       </c>
     </row>
     <row r="3">
@@ -7287,37 +7287,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.069579665166972e-08</v>
+        <v>1.618131923894645e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>8.208326429354268e-08</v>
+        <v>1.887478222470499e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>2.126732410859906e-07</v>
+        <v>5.905106207279409e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>8.345314663541832e-08</v>
+        <v>2.076525463142002e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>7.87148445251131e-08</v>
+        <v>1.425557081685705e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.361001123279249e-07</v>
+        <v>3.421527121312695e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>8.817553022100138e-08</v>
+        <v>1.855749030564199e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>7.988249120016346e-08</v>
+        <v>1.592314411138836e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>9.226312039720197e-08</v>
+        <v>2.90851304161495e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>9.724886130659257e-08</v>
+        <v>3.459463794012978e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>9.056962234499874e-08</v>
+        <v>1.939708648338125e-08</v>
       </c>
     </row>
     <row r="4">
@@ -7327,37 +7327,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.297225752257066e-08</v>
+        <v>5.297225752257065e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>5.12532729816905e-08</v>
+        <v>5.125327298169046e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>1.211817086636662e-07</v>
+        <v>1.211817086636661e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>5.145521935899711e-08</v>
+        <v>5.145521935899707e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>5.145521935899709e-08</v>
+        <v>5.145521935899706e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>8.152859202870292e-08</v>
+        <v>8.152859202870279e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>5.684072089640446e-08</v>
+        <v>5.684072089640424e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>5.203841083669049e-08</v>
+        <v>5.203841083669045e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>5.445006103534648e-08</v>
+        <v>5.445006103534644e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>5.51062942739749e-08</v>
+        <v>5.510629427397487e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>5.808702635402427e-08</v>
+        <v>5.808702635402425e-08</v>
       </c>
     </row>
     <row r="5">
@@ -7367,37 +7367,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.674692534539691e-08</v>
+        <v>9.674692534539671e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>8.748041006366656e-08</v>
+        <v>8.748041006366626e-08</v>
       </c>
       <c r="D5" t="n">
         <v>1.259375042652487e-06</v>
       </c>
       <c r="E5" t="n">
-        <v>8.748042607279114e-08</v>
+        <v>8.748042607279091e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>8.748042607279114e-08</v>
+        <v>8.748042607279091e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>6.05416150364282e-07</v>
+        <v>6.054161503642806e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>1.745376177809222e-07</v>
+        <v>1.745376177809207e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>8.747231098081648e-08</v>
+        <v>8.747231098081621e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>1.277669752127102e-07</v>
+        <v>1.277669752127101e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>1.34143973243635e-07</v>
+        <v>1.341439732436347e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>2.116087746332546e-07</v>
+        <v>1.6332523300582e-07</v>
       </c>
     </row>
     <row r="6">
@@ -7407,37 +7407,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.222745076023946e-08</v>
+        <v>5.222745076023943e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>5.048657613759799e-08</v>
+        <v>5.048657613759796e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2221272758663e-07</v>
+        <v>1.222127275866301e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>5.039360144937851e-08</v>
+        <v>5.039360144937847e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>5.122528489947494e-08</v>
+        <v>5.122528489947492e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>9.013885325570819e-08</v>
+        <v>9.013885325570811e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>6.635570369365473e-08</v>
+        <v>6.635570369365453e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>6.064867206369585e-08</v>
+        <v>6.064867206369574e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>6.348840890358992e-08</v>
+        <v>6.348840890358988e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>5.379719171698783e-08</v>
+        <v>5.379719171698772e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>5.738660973355552e-08</v>
+        <v>5.738660973355548e-08</v>
       </c>
     </row>
     <row r="7">
@@ -7447,37 +7447,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.011434640665222e-08</v>
+        <v>6.011434640665216e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>5.918859880362216e-08</v>
+        <v>5.918859880362212e-08</v>
       </c>
       <c r="D7" t="n">
         <v>1.283224611702661e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>5.917279889010372e-08</v>
+        <v>5.917279889010364e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>5.917279889010372e-08</v>
+        <v>5.917279889010364e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>8.867068091278443e-08</v>
+        <v>8.867068091278433e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>6.398280978048597e-08</v>
+        <v>6.398280978048584e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>5.918049972077206e-08</v>
+        <v>5.918049972077199e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>6.159214991942807e-08</v>
+        <v>6.159214991942798e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>6.224838315805648e-08</v>
+        <v>6.22483831580564e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>6.522911523810585e-08</v>
+        <v>6.522911523810578e-08</v>
       </c>
     </row>
     <row r="8">
@@ -7487,37 +7487,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7.066475872582657e-08</v>
+        <v>7.066475872582646e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>8.42091374414602e-08</v>
+        <v>8.420913744109634e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>1.563575369647805e-07</v>
+        <v>1.563575369647804e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>8.024953241783297e-08</v>
+        <v>8.024953241783283e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>7.018940415075965e-08</v>
+        <v>7.018940415075956e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>1.137017597868372e-07</v>
+        <v>1.137017597868371e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>8.901388865453536e-08</v>
+        <v>8.901388865453506e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>8.42115785948248e-08</v>
+        <v>8.421157859482464e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>8.662607465799305e-08</v>
+        <v>8.662607465799286e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>7.252980966122392e-08</v>
+        <v>7.25298096612238e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>1.053864611819257e-07</v>
+        <v>1.053864611819255e-07</v>
       </c>
     </row>
     <row r="9">
@@ -7527,37 +7527,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8.496795597644911e-08</v>
+        <v>8.496795597644897e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>9.430056626089829e-08</v>
+        <v>9.43005662608981e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>1.634357905604391e-07</v>
+        <v>1.634357905604389e-07</v>
       </c>
       <c r="E9" t="n">
-        <v>1.061385364340638e-07</v>
+        <v>1.061385364340636e-07</v>
       </c>
       <c r="F9" t="n">
-        <v>9.430058512814867e-08</v>
+        <v>9.430058512814854e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>1.237826483700606e-07</v>
+        <v>1.237826483700604e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>9.909477723776212e-08</v>
+        <v>9.909477723776195e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>9.429246717804813e-08</v>
+        <v>9.429246717804803e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>9.670411737670416e-08</v>
+        <v>9.670411737670397e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>9.141662851615491e-08</v>
+        <v>9.14166285161548e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>1.003410826953819e-07</v>
+        <v>1.003410826953818e-07</v>
       </c>
     </row>
   </sheetData>
@@ -7643,37 +7643,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.044821442145308e-08</v>
+        <v>1.703928182584676e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>7.425726287923821e-08</v>
+        <v>1.909686021511866e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.592524333916835e-07</v>
+        <v>2.171287149086456e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>7.555171712163268e-08</v>
+        <v>2.020398462993331e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>7.099867614912481e-08</v>
+        <v>1.64147953936445e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>9.514312942832905e-08</v>
+        <v>1.833892615460684e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>7.206665580789734e-08</v>
+        <v>1.706722560772405e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>7.182534700940732e-08</v>
+        <v>1.71107401909975e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>8.495843822158751e-08</v>
+        <v>2.460009950650874e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>8.401738704237199e-08</v>
+        <v>2.751417592636773e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>3.625306622359936e-07</v>
+        <v>3.259508421139279e-08</v>
       </c>
     </row>
     <row r="3">
@@ -7683,37 +7683,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.717813396254931e-08</v>
+        <v>1.399166182710736e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>8.118100421788154e-08</v>
+        <v>1.78202539645857e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.793213815168548e-07</v>
+        <v>4.710294061522834e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>8.248558806703203e-08</v>
+        <v>1.961703759548267e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>7.793254709452414e-08</v>
+        <v>1.33618816497687e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.055824017566892e-07</v>
+        <v>2.322334097581365e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>7.905438094682561e-08</v>
+        <v>1.455256718162633e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>7.872291807057618e-08</v>
+        <v>1.449508839138677e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>9.255850920013089e-08</v>
+        <v>2.814825823476006e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>9.09052056355734e-08</v>
+        <v>3.158325328673899e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>4.131201786266186e-07</v>
+        <v>1.242985200070334e-07</v>
       </c>
     </row>
     <row r="4">
@@ -7726,22 +7726,22 @@
         <v>5.050597871993366e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>5.053919601907513e-08</v>
+        <v>5.053919601907512e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>1.032963239437754e-07</v>
+        <v>1.032963239437753e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>5.069647941334014e-08</v>
+        <v>5.069647941334016e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>5.069647941334014e-08</v>
+        <v>5.069647941334016e-08</v>
       </c>
       <c r="G4" t="n">
         <v>6.512171223641323e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>5.147453155407904e-08</v>
+        <v>5.147453155407902e-08</v>
       </c>
       <c r="I4" t="n">
         <v>5.087719309427698e-08</v>
@@ -7753,7 +7753,7 @@
         <v>5.113087770853785e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>2.240778504191772e-07</v>
+        <v>2.240778504191773e-07</v>
       </c>
     </row>
     <row r="5">
@@ -7763,37 +7763,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.57658056404553e-08</v>
+        <v>7.576580564045526e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>8.620279540922947e-08</v>
+        <v>8.620279540922944e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>8.828149039298497e-07</v>
+        <v>8.828149039298488e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>8.620280299569357e-08</v>
+        <v>8.62028029956936e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>8.620280299569357e-08</v>
+        <v>8.62028029956936e-08</v>
       </c>
       <c r="G5" t="n">
         <v>3.125683757580924e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>9.638256692936275e-08</v>
+        <v>9.638256692936288e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>8.619822640620055e-08</v>
+        <v>8.619822640620053e-08</v>
       </c>
       <c r="J5" t="n">
         <v>1.384502327099093e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>8.543903187372842e-08</v>
+        <v>8.543903187372844e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>2.653063491519063e-07</v>
+        <v>3.376787883442586e-06</v>
       </c>
     </row>
     <row r="6">
@@ -7803,37 +7803,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.796333779972396e-08</v>
+        <v>5.796333779972395e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>4.942187370488376e-08</v>
+        <v>4.942187370488377e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.036494684028996e-07</v>
+        <v>1.036495086575308e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>4.933972735012246e-08</v>
+        <v>4.933972735012245e-08</v>
       </c>
       <c r="F6" t="n">
         <v>4.977831259471581e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>6.40546716394178e-08</v>
+        <v>7.257907131620352e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>5.957820354672424e-08</v>
+        <v>5.95782035467242e-08</v>
       </c>
       <c r="I6" t="n">
         <v>5.833455217406729e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>5.306509731980984e-08</v>
+        <v>5.306509731980982e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>4.97483671236239e-08</v>
+        <v>4.974836712362387e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>2.2399568601268e-07</v>
+        <v>2.239956860126802e-07</v>
       </c>
     </row>
     <row r="7">
@@ -7846,34 +7846,34 @@
         <v>5.615399955543819e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>5.652978293281045e-08</v>
+        <v>5.652978293281046e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.089430958742364e-07</v>
+        <v>1.089430958742363e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>5.652089370138839e-08</v>
+        <v>5.652089370138837e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>5.652089370138839e-08</v>
+        <v>5.652089370138837e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>7.076973307191781e-08</v>
+        <v>7.07697330719178e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>5.712255238958362e-08</v>
+        <v>5.712255238958361e-08</v>
       </c>
       <c r="I7" t="n">
         <v>5.652521392978156e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>5.95976982093791e-08</v>
+        <v>5.959769820937908e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>5.677889854404244e-08</v>
+        <v>5.677889854404242e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>2.297258712546817e-07</v>
+        <v>2.297258712546818e-07</v>
       </c>
     </row>
     <row r="8">
@@ -7883,16 +7883,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.523736667725783e-08</v>
+        <v>6.523736667725781e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>7.778241576891961e-08</v>
+        <v>7.778241576891959e-08</v>
       </c>
       <c r="D8" t="n">
         <v>1.327257766713895e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>7.445310601875057e-08</v>
+        <v>7.445310601875048e-08</v>
       </c>
       <c r="F8" t="n">
         <v>6.599448458796323e-08</v>
@@ -7901,19 +7901,19 @@
         <v>9.202685715366379e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>7.837967647132592e-08</v>
+        <v>7.837967647132584e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>7.778233801152759e-08</v>
+        <v>7.778233801152756e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>8.085721478220735e-08</v>
+        <v>8.085721478220732e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>6.563613187994812e-08</v>
+        <v>6.563613187994811e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>2.636995024340076e-07</v>
+        <v>2.636995024340078e-07</v>
       </c>
     </row>
     <row r="9">
@@ -7923,34 +7923,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7.284964852093437e-08</v>
+        <v>7.284964852093432e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>8.062930601267255e-08</v>
+        <v>8.062930601267254e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>1.330438799564726e-07</v>
+        <v>1.330438799564725e-07</v>
       </c>
       <c r="E9" t="n">
-        <v>8.917323704556046e-08</v>
+        <v>8.917323704556041e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>8.062931261529985e-08</v>
+        <v>8.062931261529983e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>9.486925615177981e-08</v>
+        <v>9.486925615177984e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>8.122207546944568e-08</v>
+        <v>8.122207546944564e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>8.062473700964361e-08</v>
+        <v>8.062473700964358e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>8.369722128924114e-08</v>
+        <v>8.36972212892411e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>7.155561939169505e-08</v>
+        <v>7.658859297287363e-08</v>
       </c>
       <c r="L9" t="n">
         <v>2.538253943345439e-07</v>

--- a/Results/Ammonia/ammonia particulate matter results.xlsx
+++ b/Results/Ammonia/ammonia particulate matter results.xlsx
@@ -515,34 +515,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.040823968884726e-08</v>
+        <v>2.040823968884728e-08</v>
       </c>
       <c r="C2" t="n">
         <v>2.223095900589507e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>2.69237707620027e-08</v>
+        <v>2.692377076200271e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>2.347221151046379e-08</v>
+        <v>2.347221151046377e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.932403850751237e-08</v>
+        <v>1.932403850751239e-08</v>
       </c>
       <c r="G2" t="n">
         <v>2.340696126417024e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>2.105684961868247e-08</v>
+        <v>2.105684961868249e-08</v>
       </c>
       <c r="I2" t="n">
         <v>2.038273241857663e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>2.829483828086047e-08</v>
+        <v>2.829483828086048e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>3.106137233322736e-08</v>
+        <v>3.106137233322737e-08</v>
       </c>
       <c r="L2" t="n">
         <v>2.096967577176797e-08</v>
@@ -555,13 +555,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.779182883768701e-08</v>
+        <v>1.779182883768703e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>2.072910740715594e-08</v>
+        <v>2.072910740715593e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>6.417867621039789e-08</v>
+        <v>6.417867621039791e-08</v>
       </c>
       <c r="E3" t="n">
         <v>2.272288015241924e-08</v>
@@ -570,13 +570,13 @@
         <v>1.587514411353929e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>3.916925853729064e-08</v>
+        <v>3.916925853729065e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>2.295310511006134e-08</v>
+        <v>2.295310511006135e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.760720128336733e-08</v>
+        <v>1.760720128336734e-08</v>
       </c>
       <c r="J3" t="n">
         <v>3.22733349347713e-08</v>
@@ -585,7 +585,7 @@
         <v>3.657550886819317e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>2.218314733769421e-08</v>
+        <v>2.218314733769423e-08</v>
       </c>
     </row>
     <row r="4">
@@ -595,25 +595,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.528753432793724e-08</v>
+        <v>5.528753432793722e-08</v>
       </c>
       <c r="C4" t="n">
         <v>5.372514843404891e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>1.288834550916042e-07</v>
+        <v>1.288834550916043e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>5.393919416748255e-08</v>
+        <v>5.393919416748254e-08</v>
       </c>
       <c r="F4" t="n">
         <v>5.393919416748254e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>8.908198472540882e-08</v>
+        <v>8.908198472540877e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>6.352621811358441e-08</v>
+        <v>6.352621811358444e-08</v>
       </c>
       <c r="I4" t="n">
         <v>5.44749276708968e-08</v>
@@ -622,7 +622,7 @@
         <v>5.828318870011919e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>5.776004580083404e-08</v>
+        <v>5.776004580083403e-08</v>
       </c>
       <c r="L4" t="n">
         <v>6.225175500096102e-08</v>
@@ -635,37 +635,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.215307368835029e-07</v>
+        <v>1.21530736883503e-07</v>
       </c>
       <c r="C5" t="n">
-        <v>1.136795035095826e-07</v>
+        <v>1.13679503509583e-07</v>
       </c>
       <c r="D5" t="n">
-        <v>1.535349436600189e-06</v>
+        <v>1.535349436600188e-06</v>
       </c>
       <c r="E5" t="n">
-        <v>1.136795159148537e-07</v>
+        <v>1.136795159148534e-07</v>
       </c>
       <c r="F5" t="n">
-        <v>1.136795159148537e-07</v>
+        <v>1.136795159148534e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>7.889428231501095e-07</v>
+        <v>7.88942823150107e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>3.090888761265892e-07</v>
+        <v>3.090888761265893e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>1.136702492369496e-07</v>
+        <v>1.1367024923695e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>1.86729886709912e-07</v>
+        <v>1.867298867099121e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>1.70014278890628e-07</v>
+        <v>1.700142788906283e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>2.891638214838586e-07</v>
+        <v>2.891638214838591e-07</v>
       </c>
     </row>
     <row r="6">
@@ -678,31 +678,31 @@
         <v>5.472347090684191e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>5.293118799385709e-08</v>
+        <v>5.293118799385712e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.302694507626698e-07</v>
+        <v>1.3026945076267e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>5.281907613573967e-08</v>
+        <v>5.281907613573963e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>5.383107891637284e-08</v>
+        <v>5.383107891637288e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>9.923762412470814e-08</v>
+        <v>9.923762412470819e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>7.467463444692327e-08</v>
+        <v>7.46746344469233e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>6.463056707019629e-08</v>
+        <v>6.463056707019628e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>6.888410536280107e-08</v>
+        <v>6.888410536280105e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>5.654718028530438e-08</v>
+        <v>5.654718028530445e-08</v>
       </c>
       <c r="L6" t="n">
         <v>6.174324117693617e-08</v>
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.367034168052623e-08</v>
+        <v>6.367034168052625e-08</v>
       </c>
       <c r="C7" t="n">
         <v>6.286698929611871e-08</v>
@@ -724,22 +724,22 @@
         <v>1.372648072040806e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>6.28501285160179e-08</v>
+        <v>6.285012851601791e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>6.28501285160179e-08</v>
+        <v>6.285012851601791e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>9.746479207799767e-08</v>
+        <v>9.746479207799772e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>7.190902546617347e-08</v>
+        <v>7.190902546617349e-08</v>
       </c>
       <c r="I7" t="n">
         <v>6.285773502348579e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>6.666599605270821e-08</v>
+        <v>6.666599605270823e-08</v>
       </c>
       <c r="K7" t="n">
         <v>6.614285315342306e-08</v>
@@ -755,37 +755,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7.560319441454774e-08</v>
+        <v>7.560319441454777e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>9.130236411189394e-08</v>
+        <v>9.130236411189399e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>1.691368246931395e-07</v>
+        <v>1.691368246931396e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>8.678680369408168e-08</v>
+        <v>8.678680369408169e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>7.531411006195234e-08</v>
+        <v>7.531411006195238e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>1.259111677666663e-07</v>
+        <v>1.259111677666665e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>1.003554011548402e-07</v>
+        <v>1.003554011548403e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>9.130411071215442e-08</v>
+        <v>9.130411071215446e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>9.51156171203812e-08</v>
+        <v>9.511561712038125e-08</v>
       </c>
       <c r="K8" t="n">
         <v>7.776895872010699e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>1.163306936062647e-07</v>
+        <v>1.163306936062648e-07</v>
       </c>
     </row>
     <row r="9">
@@ -795,25 +795,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.672722678916187e-08</v>
+        <v>9.672722678916186e-08</v>
       </c>
       <c r="C9" t="n">
         <v>1.089533725309587e-07</v>
       </c>
       <c r="D9" t="n">
-        <v>1.833526755561912e-07</v>
+        <v>1.833526755561913e-07</v>
       </c>
       <c r="E9" t="n">
-        <v>1.239891787835133e-07</v>
+        <v>1.239891787835134e-07</v>
       </c>
       <c r="F9" t="n">
         <v>1.089533867532789e-07</v>
       </c>
       <c r="G9" t="n">
-        <v>1.435511753128376e-07</v>
+        <v>1.435511753128377e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>1.179954087010133e-07</v>
+        <v>1.179954087010134e-07</v>
       </c>
       <c r="I9" t="n">
         <v>1.089441182583259e-07</v>
@@ -822,7 +822,7 @@
         <v>1.127523792875482e-07</v>
       </c>
       <c r="K9" t="n">
-        <v>9.582276474666547e-08</v>
+        <v>9.582276474666549e-08</v>
       </c>
       <c r="L9" t="n">
         <v>1.1672094558839e-07</v>
@@ -911,37 +911,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.506557507927707e-08</v>
+        <v>1.506557507927708e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.758248912433048e-08</v>
+        <v>1.758248912433051e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.533202652910149e-08</v>
+        <v>1.53320265291015e-08</v>
       </c>
       <c r="E2" t="n">
         <v>1.859239851511687e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.50568356618639e-08</v>
+        <v>1.505683566186391e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.524848114272573e-08</v>
+        <v>1.524848114272575e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.508015303377582e-08</v>
+        <v>1.508015303377583e-08</v>
       </c>
       <c r="I2" t="n">
         <v>1.535396683339122e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>2.280543308815512e-08</v>
+        <v>2.280543308815515e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>2.580470167556699e-08</v>
+        <v>2.580470167556701e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.504677257818111e-08</v>
+        <v>1.5046772578181e-08</v>
       </c>
     </row>
     <row r="3">
@@ -951,37 +951,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.220585658527314e-08</v>
+        <v>1.220585658527315e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.795744522915992e-08</v>
+        <v>1.795744522915994e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.409550115440599e-08</v>
+        <v>1.409550115440598e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.960915267665436e-08</v>
+        <v>1.960915267665438e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.377266293803804e-08</v>
+        <v>1.377266293803803e-08</v>
       </c>
       <c r="G3" t="n">
         <v>1.350684535265944e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.255548878913497e-08</v>
+        <v>1.255548878913498e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.424753575629844e-08</v>
+        <v>1.424753575629845e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>2.80197178318292e-08</v>
+        <v>2.801971783182924e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>3.032804259467328e-08</v>
+        <v>3.032804259467336e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.215286357953272e-08</v>
+        <v>1.215286357953267e-08</v>
       </c>
     </row>
     <row r="4">
@@ -991,37 +991,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.927726322238818e-08</v>
+        <v>4.927726322238817e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>5.215510816109326e-08</v>
+        <v>5.215510816109325e-08</v>
       </c>
       <c r="D4" t="n">
         <v>5.228695492187779e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>5.228850905368918e-08</v>
+        <v>5.228850905368916e-08</v>
       </c>
       <c r="F4" t="n">
         <v>5.228850905368916e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>5.129152422748503e-08</v>
+        <v>5.1291524227485e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>4.988242574091989e-08</v>
+        <v>4.988242574091988e-08</v>
       </c>
       <c r="I4" t="n">
         <v>5.218360842168723e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>5.552675894116472e-08</v>
+        <v>5.552675894116471e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>5.010118583611354e-08</v>
+        <v>5.010118583611351e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>4.920041431922054e-08</v>
+        <v>4.920041431922053e-08</v>
       </c>
     </row>
     <row r="5">
@@ -1034,34 +1034,34 @@
         <v>7.036265332621532e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>1.190312619872387e-07</v>
+        <v>1.190312619872389e-07</v>
       </c>
       <c r="D5" t="n">
         <v>1.173583694314798e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>1.190312639524472e-07</v>
+        <v>1.190312639524471e-07</v>
       </c>
       <c r="F5" t="n">
-        <v>1.190312639524472e-07</v>
+        <v>1.190312639524471e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>1.045606363411217e-07</v>
+        <v>1.045606363411218e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>8.430864991878477e-08</v>
+        <v>8.430864991878479e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>1.190301809742212e-07</v>
+        <v>1.190301809742214e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>1.821074507521309e-07</v>
+        <v>1.821074507521303e-07</v>
       </c>
       <c r="K5" t="n">
         <v>8.239605859788458e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>7.292281017589381e-08</v>
+        <v>7.292281017589373e-08</v>
       </c>
     </row>
     <row r="6">
@@ -1071,37 +1071,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.795549504131869e-08</v>
+        <v>4.795549504131865e-08</v>
       </c>
       <c r="C6" t="n">
         <v>5.084738259227437e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>5.754472036682009e-08</v>
+        <v>5.75447203668201e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>5.076526949081392e-08</v>
+        <v>5.076526949081397e-08</v>
       </c>
       <c r="F6" t="n">
         <v>5.088087562995739e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>5.63668048717002e-08</v>
+        <v>5.636680487170018e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>5.558424006999386e-08</v>
+        <v>5.558424006999387e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>5.086184024061773e-08</v>
+        <v>5.086184024061774e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>5.43807353017255e-08</v>
+        <v>5.438073530172548e-08</v>
       </c>
       <c r="K6" t="n">
         <v>4.871063784655699e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>4.78766549818397e-08</v>
+        <v>4.787665498183967e-08</v>
       </c>
     </row>
     <row r="7">
@@ -1111,13 +1111,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.417747193385743e-08</v>
+        <v>5.417747193385742e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>5.708489814617399e-08</v>
+        <v>5.7084898146174e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>5.718590658261583e-08</v>
+        <v>5.718590658261584e-08</v>
       </c>
       <c r="E7" t="n">
         <v>5.708452194835279e-08</v>
@@ -1126,22 +1126,22 @@
         <v>5.708452194835279e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>5.619173293895425e-08</v>
+        <v>5.619173293895426e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>5.478263445238914e-08</v>
+        <v>5.478263445238912e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>5.708381713315649e-08</v>
+        <v>5.708381713315647e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>6.0426967652634e-08</v>
+        <v>6.042696765263399e-08</v>
       </c>
       <c r="K7" t="n">
         <v>5.500139454758277e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>5.410062303068978e-08</v>
+        <v>5.410062303068976e-08</v>
       </c>
     </row>
     <row r="8">
@@ -1151,37 +1151,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.239427936935728e-08</v>
+        <v>6.239427936935731e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>7.628851252913154e-08</v>
+        <v>7.628851252913155e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>7.86648195983635e-08</v>
+        <v>7.866481959836361e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>7.328391130361371e-08</v>
+        <v>7.328391130361375e-08</v>
       </c>
       <c r="F8" t="n">
         <v>6.565038785215515e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>7.539191468961265e-08</v>
+        <v>7.539191468961268e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>7.398281620304604e-08</v>
+        <v>7.398281620304611e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>7.628399888381483e-08</v>
+        <v>7.628399888381488e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>7.962930795046086e-08</v>
+        <v>7.962930795046084e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>6.301418016589736e-08</v>
+        <v>6.301418016589737e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>8.477385766860338e-08</v>
+        <v>8.477385766860343e-08</v>
       </c>
     </row>
     <row r="9">
@@ -1191,37 +1191,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.616420056471865e-08</v>
+        <v>6.616420056471862e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>7.489476207750277e-08</v>
+        <v>7.489476207750278e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>7.499703585140951e-08</v>
+        <v>7.499703585140953e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>8.161454933770552e-08</v>
+        <v>8.161454933770556e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>7.489476655281966e-08</v>
+        <v>7.48947665528197e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>7.400159687028299e-08</v>
+        <v>7.400159687028304e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>7.259249838371785e-08</v>
+        <v>7.259249838371789e-08</v>
       </c>
       <c r="I9" t="n">
         <v>7.489368106448528e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>7.823683158396267e-08</v>
+        <v>7.823683158396275e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>6.943731450197146e-08</v>
+        <v>6.943731450197145e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>7.191048696201853e-08</v>
+        <v>7.191048696201856e-08</v>
       </c>
     </row>
   </sheetData>
@@ -1307,37 +1307,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.069823739391963e-08</v>
+        <v>2.069823739391966e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.569802751590717e-08</v>
+        <v>1.569802751590721e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>2.420552563186794e-08</v>
+        <v>2.420552563186796e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.710278982698044e-08</v>
+        <v>1.710278982698045e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.710341722575339e-08</v>
+        <v>1.710341722575342e-08</v>
       </c>
       <c r="G2" t="n">
         <v>2.220523779251569e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>2.090911772785777e-08</v>
+        <v>2.090911772785779e-08</v>
       </c>
       <c r="I2" t="n">
         <v>2.076833785651072e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>2.197934377297924e-08</v>
+        <v>2.19793437729793e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>2.748332804386626e-08</v>
+        <v>2.748332804386627e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>2.082711269395995e-08</v>
+        <v>2.082711269395997e-08</v>
       </c>
     </row>
     <row r="3">
@@ -1347,34 +1347,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.997248678596577e-08</v>
+        <v>1.99724867859658e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.250436882219181e-08</v>
+        <v>1.250436882219182e-08</v>
       </c>
       <c r="D3" t="n">
         <v>4.495711534802914e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.444328104155773e-08</v>
+        <v>1.444328104155774e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.444390844033071e-08</v>
+        <v>1.444390844033069e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>3.07279791788436e-08</v>
+        <v>3.072797917884363e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>2.186203045347334e-08</v>
+        <v>2.186203045347339e-08</v>
       </c>
       <c r="I3" t="n">
         <v>2.047802854843809e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>2.755066213970103e-08</v>
+        <v>2.755066213970104e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>3.209872200852945e-08</v>
+        <v>3.209872200852942e-08</v>
       </c>
       <c r="L3" t="n">
         <v>2.111824028692408e-08</v>
@@ -1390,25 +1390,25 @@
         <v>5.101076426153118e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>5.165305778889675e-08</v>
+        <v>5.16530577888968e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>9.062719834145895e-08</v>
+        <v>9.062719834145892e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>5.060164169600504e-08</v>
+        <v>5.060164169600506e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>5.060164169600505e-08</v>
+        <v>5.060164169600507e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>6.79685751925418e-08</v>
+        <v>6.796857519254178e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>5.406414043010113e-08</v>
+        <v>5.406414043010116e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>5.136658017075203e-08</v>
+        <v>5.1366580170752e-08</v>
       </c>
       <c r="J4" t="n">
         <v>6.223568759387127e-08</v>
@@ -1417,7 +1417,7 @@
         <v>5.291043356576542e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>5.284817285622934e-08</v>
+        <v>5.284817285622933e-08</v>
       </c>
     </row>
     <row r="5">
@@ -1427,37 +1427,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.829391061878999e-08</v>
+        <v>6.829391061879003e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>9.69397158750877e-08</v>
+        <v>9.693971587508868e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>7.80093954317264e-07</v>
+        <v>7.800939543172639e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>8.546661852566332e-08</v>
+        <v>8.546661852566343e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>8.546661852566332e-08</v>
+        <v>8.546661852566347e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>3.851128127605107e-07</v>
+        <v>3.851128127605108e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>1.359193197501878e-07</v>
+        <v>1.359193197501887e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>8.546152545078631e-08</v>
+        <v>8.546152545078676e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>2.834912054454857e-07</v>
+        <v>2.834912054454856e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>1.055778553813625e-07</v>
+        <v>1.055778553813626e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>1.126655147015984e-07</v>
+        <v>1.126655147015985e-07</v>
       </c>
     </row>
     <row r="6">
@@ -1467,37 +1467,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.808906713624483e-08</v>
+        <v>5.80890671362449e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>5.079574106551142e-08</v>
+        <v>5.079574106551155e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>9.040898133693587e-08</v>
+        <v>9.040898133693586e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>4.953323001931459e-08</v>
+        <v>4.953323001931449e-08</v>
       </c>
       <c r="F6" t="n">
         <v>5.011200434770896e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>6.674918190991181e-08</v>
+        <v>6.674918190991186e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>6.278011893059147e-08</v>
+        <v>6.278011893059153e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>5.014718688812201e-08</v>
+        <v>5.014718688812204e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>6.977421472553974e-08</v>
+        <v>6.977421472553976e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>5.135695863987047e-08</v>
+        <v>5.135695863987046e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>5.163909353376433e-08</v>
+        <v>5.163909353376431e-08</v>
       </c>
     </row>
     <row r="7">
@@ -1507,37 +1507,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.772524355454253e-08</v>
+        <v>5.772524355454255e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>5.922833726397547e-08</v>
+        <v>5.922833726397541e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>9.73404614324066e-08</v>
+        <v>9.734046143240655e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>5.808135013309283e-08</v>
+        <v>5.808135013309285e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>5.808135013309283e-08</v>
+        <v>5.808135013309286e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>7.468305448555313e-08</v>
+        <v>7.46830544855532e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>6.077861972311245e-08</v>
+        <v>6.077861972311253e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>5.808105946376337e-08</v>
+        <v>5.808105946376339e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>6.895016688688259e-08</v>
+        <v>6.895016688688263e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>5.962491285877677e-08</v>
+        <v>5.962491285877679e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>5.956265214924067e-08</v>
+        <v>5.95626521492407e-08</v>
       </c>
     </row>
     <row r="8">
@@ -1547,37 +1547,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.812292702181216e-08</v>
+        <v>6.812292702181211e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>8.372154533461988e-08</v>
+        <v>8.372154533461991e-08</v>
       </c>
       <c r="D8" t="n">
         <v>1.24757951030365e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>7.872393618794621e-08</v>
+        <v>7.87239361879462e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>6.892851002244766e-08</v>
+        <v>6.89285100224477e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>9.917648326541773e-08</v>
+        <v>9.917648326541769e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>8.527204850303213e-08</v>
+        <v>8.527204850303222e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>8.257448824362784e-08</v>
+        <v>8.257448824362782e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>9.344636588352126e-08</v>
+        <v>9.344636588352137e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>6.976076061963292e-08</v>
+        <v>6.97607606196329e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>9.878026557534601e-08</v>
+        <v>9.878026557534595e-08</v>
       </c>
     </row>
     <row r="9">
@@ -1587,37 +1587,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7.734387685453367e-08</v>
+        <v>7.734387685453368e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>8.753227583330282e-08</v>
+        <v>8.753227583330295e-08</v>
       </c>
       <c r="D9" t="n">
         <v>1.256456347128799e-07</v>
       </c>
       <c r="E9" t="n">
-        <v>9.641276963111391e-08</v>
+        <v>9.641276963111389e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>8.639009404295361e-08</v>
+        <v>8.639009404295368e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>1.029869930548805e-07</v>
+        <v>1.029869930548807e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>8.908255829243983e-08</v>
+        <v>8.90825582924399e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>8.638499803309078e-08</v>
+        <v>8.638499803309075e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>9.725410545620998e-08</v>
+        <v>9.725410545621003e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>8.289655923007262e-08</v>
+        <v>8.289655923007268e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>8.786659071856809e-08</v>
+        <v>8.786659071856808e-08</v>
       </c>
     </row>
   </sheetData>
@@ -1703,37 +1703,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.935025009730624e-08</v>
+        <v>1.935025009730627e-08</v>
       </c>
       <c r="C2" t="n">
         <v>1.476969625252255e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>2.181936182381049e-08</v>
+        <v>2.18193618238105e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.614685739775441e-08</v>
+        <v>1.614685739775444e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.614747688377916e-08</v>
+        <v>1.614747688377917e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>2.023083928113127e-08</v>
+        <v>2.023083928113131e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.94664960702024e-08</v>
+        <v>1.946649607020238e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.940964494061217e-08</v>
+        <v>1.940964494061216e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>2.077019389273735e-08</v>
+        <v>2.077019389273734e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>2.633850866026521e-08</v>
+        <v>2.63385086602651e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.937764367283886e-08</v>
+        <v>1.937764367283884e-08</v>
       </c>
     </row>
     <row r="3">
@@ -1743,37 +1743,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.855406013818204e-08</v>
+        <v>1.855406013818203e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.174597895752984e-08</v>
+        <v>1.174597895752982e-08</v>
       </c>
       <c r="D3" t="n">
         <v>3.614483229503034e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.361339258853412e-08</v>
+        <v>1.361339258853413e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.361401207455886e-08</v>
+        <v>1.36140120745589e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>2.484146794137974e-08</v>
+        <v>2.484146794137969e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.970513155463271e-08</v>
+        <v>1.970513155463269e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.89833134125333e-08</v>
+        <v>1.898331341253328e-08</v>
       </c>
       <c r="J3" t="n">
         <v>2.554222460597867e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>3.042841012203385e-08</v>
+        <v>3.042841012203374e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.890970079023211e-08</v>
+        <v>1.890970079023209e-08</v>
       </c>
     </row>
     <row r="4">
@@ -1783,37 +1783,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.995928482548929e-08</v>
+        <v>4.99592848254893e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>5.087209701391661e-08</v>
+        <v>5.087209701391659e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>7.784903762386593e-08</v>
+        <v>7.784903762386586e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>4.996997563962814e-08</v>
+        <v>4.996997563962813e-08</v>
       </c>
       <c r="F4" t="n">
         <v>4.996997563962815e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>5.9828446670008e-08</v>
+        <v>5.982844667000801e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>5.183539405079953e-08</v>
+        <v>5.183539405079951e-08</v>
       </c>
       <c r="I4" t="n">
         <v>5.010732836542532e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>5.949939943807603e-08</v>
+        <v>5.949939943807604e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>5.064683359410209e-08</v>
+        <v>5.06468335941021e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>5.053934024334718e-08</v>
+        <v>5.053934024334713e-08</v>
       </c>
     </row>
     <row r="5">
@@ -1826,31 +1826,31 @@
         <v>6.259207030747862e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>8.886881828610334e-08</v>
+        <v>8.886881828610326e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>5.395954286108487e-07</v>
+        <v>5.395954286108496e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>7.671086256194387e-08</v>
+        <v>7.671086256194389e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>7.671086256194386e-08</v>
+        <v>7.671086256194389e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>2.397844799162831e-07</v>
+        <v>2.397844799162825e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>1.038054453420633e-07</v>
+        <v>1.038054453420631e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>7.670720341094264e-08</v>
+        <v>7.670720341094258e-08</v>
       </c>
       <c r="J5" t="n">
         <v>2.367748670605628e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>7.734238269255427e-08</v>
+        <v>7.734238269255424e-08</v>
       </c>
       <c r="L5" t="n">
         <v>7.963556329146385e-08</v>
@@ -1863,37 +1863,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.591823177625851e-08</v>
+        <v>5.591823177625849e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>4.979519178237418e-08</v>
+        <v>4.979519178237421e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>8.429400797746331e-08</v>
+        <v>8.429400797746324e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>4.84049504890809e-08</v>
+        <v>4.840495048908093e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>4.877205234568128e-08</v>
+        <v>4.877205234568127e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>6.578739362077717e-08</v>
+        <v>6.57873936207772e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>5.93881232984001e-08</v>
+        <v>5.938812329840004e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>4.878712471646926e-08</v>
+        <v>4.878712471646923e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>5.84013004909426e-08</v>
+        <v>5.840130049094258e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>4.910534766501055e-08</v>
+        <v>4.910534766501053e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>4.922027677661059e-08</v>
+        <v>4.92202767766106e-08</v>
       </c>
     </row>
     <row r="7">
@@ -1903,34 +1903,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.584875554915284e-08</v>
+        <v>5.584875554915281e-08</v>
       </c>
       <c r="C7" t="n">
         <v>5.730697122941454e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>8.373736671096385e-08</v>
+        <v>8.373736671096382e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>5.60077857867434e-08</v>
+        <v>5.600778578674343e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>5.60077857867434e-08</v>
+        <v>5.600778578674343e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>6.57179173936716e-08</v>
+        <v>6.571791739367158e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>5.772486477446309e-08</v>
+        <v>5.772486477446303e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>5.599679908908886e-08</v>
+        <v>5.599679908908885e-08</v>
       </c>
       <c r="J7" t="n">
         <v>6.538887016173953e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>5.653630431776564e-08</v>
+        <v>5.653630431776562e-08</v>
       </c>
       <c r="L7" t="n">
         <v>5.642881096701072e-08</v>
@@ -1943,37 +1943,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.535585546041272e-08</v>
+        <v>6.53558554604128e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>7.957583602308709e-08</v>
+        <v>7.957583602308702e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>1.086403118143212e-07</v>
+        <v>1.086403118143211e-07</v>
       </c>
       <c r="E8" t="n">
         <v>7.478057665806382e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>6.591678958187195e-08</v>
+        <v>6.591678958187194e-08</v>
       </c>
       <c r="G8" t="n">
         <v>8.79757693585558e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>7.998271673946135e-08</v>
+        <v>7.99827167394613e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>7.825465105397308e-08</v>
+        <v>7.825465105397304e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>8.764922801339589e-08</v>
+        <v>8.76492280133958e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>6.580655246293972e-08</v>
+        <v>6.580655246293969e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>9.200588965246539e-08</v>
+        <v>9.200588965246538e-08</v>
       </c>
     </row>
     <row r="9">
@@ -1983,37 +1983,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7.039314945847723e-08</v>
+        <v>7.039314945847715e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>7.879425092723806e-08</v>
+        <v>7.879425092723812e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>1.052258016744364e-07</v>
+        <v>1.052258016744363e-07</v>
       </c>
       <c r="E9" t="n">
-        <v>8.549969665483871e-08</v>
+        <v>8.549969665483863e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>7.748774066555525e-08</v>
+        <v>7.748774066555518e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>8.720519709149517e-08</v>
+        <v>8.72051970914951e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>7.921214447228669e-08</v>
+        <v>7.921214447228661e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>7.748407878691248e-08</v>
+        <v>7.748407878691241e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>8.687614985956316e-08</v>
+        <v>8.687614985956315e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>7.400085445525553e-08</v>
+        <v>7.40008544552555e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>7.791609066483435e-08</v>
+        <v>7.79160906648343e-08</v>
       </c>
     </row>
   </sheetData>
@@ -2099,37 +2099,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.842258782021466e-08</v>
+        <v>1.842258782021473e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.412744209411019e-08</v>
+        <v>1.412744209411018e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>2.009354166921053e-08</v>
+        <v>2.009354166921061e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.550159541092735e-08</v>
+        <v>1.550159541092744e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.550221699200821e-08</v>
+        <v>1.550221699200824e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.889990808341525e-08</v>
+        <v>1.889990808341535e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.850019297054267e-08</v>
+        <v>1.850019297054269e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.845397970673609e-08</v>
+        <v>1.845397970673614e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.968967470664196e-08</v>
+        <v>1.968967470664195e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>2.5645618074128e-08</v>
+        <v>2.564561807412804e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.843809812600366e-08</v>
+        <v>1.843809812600367e-08</v>
       </c>
     </row>
     <row r="3">
@@ -2139,37 +2139,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.751899089764295e-08</v>
+        <v>1.751899089764299e-08</v>
       </c>
       <c r="C3" t="n">
         <v>1.096261479969329e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>2.942538551207649e-08</v>
+        <v>2.942538551207652e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.289123358097966e-08</v>
+        <v>1.289123358097964e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.289185516206049e-08</v>
+        <v>1.289185516206048e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>2.09299726767933e-08</v>
+        <v>2.092997267679332e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.835239841518518e-08</v>
+        <v>1.83523984151852e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.774876597972574e-08</v>
+        <v>1.774876597972575e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>2.291836462384335e-08</v>
+        <v>2.29183646238435e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>2.955870639215162e-08</v>
+        <v>2.955870639215174e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.774455117923195e-08</v>
+        <v>1.774455117923198e-08</v>
       </c>
     </row>
     <row r="4">
@@ -2179,37 +2179,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.950483340119207e-08</v>
+        <v>4.950483340119208e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>5.012112626965045e-08</v>
+        <v>5.012112626965048e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>6.837902580234794e-08</v>
+        <v>6.837902580234791e-08</v>
       </c>
       <c r="E4" t="n">
         <v>4.914584433553719e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>4.91458443355372e-08</v>
+        <v>4.914584433553719e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>5.482894961706776e-08</v>
+        <v>5.482894961706773e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>5.087142612703589e-08</v>
+        <v>5.087142612703593e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>4.940398680692984e-08</v>
+        <v>4.940398680692985e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>5.629564893540032e-08</v>
+        <v>5.629564893540036e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>4.9733637456015e-08</v>
+        <v>4.973363745601498e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>4.987041621967751e-08</v>
+        <v>4.987041621967753e-08</v>
       </c>
     </row>
     <row r="5">
@@ -2219,37 +2219,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.863463050428898e-08</v>
+        <v>5.8634630504289e-08</v>
       </c>
       <c r="C5" t="n">
         <v>7.718005088794263e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>3.824612281987348e-07</v>
+        <v>3.82461228198734e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>6.742247793005891e-08</v>
+        <v>6.742247793005896e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>6.742247793005891e-08</v>
+        <v>6.742247793005896e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>1.561661105753321e-07</v>
+        <v>1.56166110575332e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>8.970013261430342e-08</v>
+        <v>8.970013261430356e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>6.741986536427845e-08</v>
+        <v>6.741986536427846e-08</v>
       </c>
       <c r="J5" t="n">
         <v>1.836222802239302e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>6.560851297224234e-08</v>
+        <v>6.56085129722424e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>7.101947024693122e-08</v>
+        <v>7.101947024693125e-08</v>
       </c>
     </row>
     <row r="6">
@@ -2259,37 +2259,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.804898636957246e-08</v>
+        <v>4.804898636957248e-08</v>
       </c>
       <c r="C6" t="n">
         <v>4.886605321949798e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>6.742284947521767e-08</v>
+        <v>6.742284947521691e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>4.764664996423244e-08</v>
+        <v>4.764664996423247e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>4.794103478272359e-08</v>
+        <v>4.79410347827236e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>6.037327666165316e-08</v>
+        <v>6.037327666165315e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>5.815975413988989e-08</v>
+        <v>5.815975413988994e-08</v>
       </c>
       <c r="I6" t="n">
         <v>5.494831385151523e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>6.221415662434666e-08</v>
+        <v>6.22141566243467e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>4.813508532708116e-08</v>
+        <v>4.813508532708086e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>4.841333933898541e-08</v>
+        <v>4.841333933898547e-08</v>
       </c>
     </row>
     <row r="7">
@@ -2299,37 +2299,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.518229300980616e-08</v>
+        <v>5.518229300980618e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>5.62021763975563e-08</v>
+        <v>5.620217639755633e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>7.405534426290459e-08</v>
+        <v>7.40553442629046e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>5.509548027703031e-08</v>
+        <v>5.509548027703034e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>5.509548027703031e-08</v>
+        <v>5.509548027703034e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>6.050640922568184e-08</v>
+        <v>6.050640922568186e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>5.654888573565002e-08</v>
+        <v>5.654888573565003e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>5.508144641554392e-08</v>
+        <v>5.508144641554395e-08</v>
       </c>
       <c r="J7" t="n">
         <v>6.197310854401447e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>5.541109706462906e-08</v>
+        <v>5.541109706462911e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>5.554787582829163e-08</v>
+        <v>5.554787582829165e-08</v>
       </c>
     </row>
     <row r="8">
@@ -2342,34 +2342,34 @@
         <v>6.452154617973799e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>7.803023572127533e-08</v>
+        <v>7.80302357212754e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>9.845621988582497e-08</v>
+        <v>9.845621988582493e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>7.349866745991743e-08</v>
+        <v>7.34986674599175e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>6.482621059613428e-08</v>
+        <v>6.482621059613432e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>8.231959294165397e-08</v>
+        <v>8.231959294165405e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>7.836206945182083e-08</v>
+        <v>7.836206945182087e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>7.689463013151617e-08</v>
+        <v>7.689463013151618e-08</v>
       </c>
       <c r="J8" t="n">
         <v>8.378874374298287e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>6.451864057003965e-08</v>
+        <v>6.451864057003966e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>9.039112305267034e-08</v>
+        <v>9.039112305267038e-08</v>
       </c>
     </row>
     <row r="9">
@@ -2379,37 +2379,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.707684219892759e-08</v>
+        <v>6.707684219892763e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>7.423271721680352e-08</v>
+        <v>7.423271721680359e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>9.20870373303037e-08</v>
+        <v>9.208703733030371e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>8.019541730685672e-08</v>
+        <v>8.019541730685676e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>7.311460238849779e-08</v>
+        <v>7.311460238849782e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>7.853695004492906e-08</v>
+        <v>7.85369500449291e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>7.457942655489728e-08</v>
+        <v>7.45794265548973e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>7.311198723479113e-08</v>
+        <v>7.31119872347912e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>8.000364936326166e-08</v>
+        <v>8.000364936326169e-08</v>
       </c>
       <c r="K9" t="n">
         <v>6.974218497230005e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>7.357841664753882e-08</v>
+        <v>7.357841664753891e-08</v>
       </c>
     </row>
   </sheetData>
@@ -2495,37 +2495,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.955231787715327e-08</v>
+        <v>1.955231787715326e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.459352659456333e-08</v>
+        <v>1.459352659456337e-08</v>
       </c>
       <c r="D2" t="n">
         <v>2.147749728333419e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.61843237884856e-08</v>
+        <v>1.61843237884857e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.618494254754477e-08</v>
+        <v>1.618494254754486e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>2.045323598005937e-08</v>
+        <v>2.045323598005936e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.972760331229568e-08</v>
+        <v>1.972760331229577e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.96286949027809e-08</v>
+        <v>1.962869490278101e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>2.067461997814725e-08</v>
+        <v>2.067461997814727e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>2.644966072449833e-08</v>
+        <v>2.644966072449843e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.974422332152109e-08</v>
+        <v>1.974422332152117e-08</v>
       </c>
     </row>
     <row r="3">
@@ -2535,37 +2535,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.885115666479901e-08</v>
+        <v>1.885115666479902e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.06481761079438e-08</v>
+        <v>1.064817610794384e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>3.256798480518647e-08</v>
+        <v>3.256798480518649e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.373172217028537e-08</v>
+        <v>1.373172217028535e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.373234092934451e-08</v>
+        <v>1.373234092934449e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>2.528354187492439e-08</v>
+        <v>2.528354187492442e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>2.042347233731743e-08</v>
+        <v>2.042347233731758e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.94013848836081e-08</v>
+        <v>1.940138488360816e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>2.504999612883459e-08</v>
+        <v>2.504999612883462e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>3.083348418683232e-08</v>
+        <v>3.083348418683248e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>2.037486054273029e-08</v>
+        <v>2.037486054273036e-08</v>
       </c>
     </row>
     <row r="4">
@@ -2578,34 +2578,34 @@
         <v>5.011701351876177e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>4.919273974628156e-08</v>
+        <v>4.919273974628159e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>7.186280053785675e-08</v>
+        <v>7.186280053785673e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>4.995367255261856e-08</v>
+        <v>4.995367255261861e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>4.995367255261856e-08</v>
+        <v>4.995367255261859e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>6.02331602267554e-08</v>
+        <v>6.023316022675545e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>5.265626345518228e-08</v>
+        <v>5.265626345518234e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>5.057273795904385e-08</v>
+        <v>5.057273795904391e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>5.90439837441477e-08</v>
+        <v>5.904398374414771e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>5.133723542580396e-08</v>
+        <v>5.133723542580398e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>5.253216679550671e-08</v>
+        <v>5.253216679550672e-08</v>
       </c>
     </row>
     <row r="5">
@@ -2615,37 +2615,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.386954704629152e-08</v>
+        <v>6.386954704629163e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>6.231316596592854e-08</v>
+        <v>6.231316596592867e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>4.559829344740935e-07</v>
+        <v>4.559829344740932e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>8.232956127042036e-08</v>
+        <v>8.232956127042126e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>8.232956127042036e-08</v>
+        <v>8.232956127042126e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>2.546249916949143e-07</v>
+        <v>2.546249916949151e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>1.206660395267891e-07</v>
+        <v>1.20666039526791e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>8.232606224226772e-08</v>
+        <v>8.232606224226873e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>2.357099107935711e-07</v>
+        <v>2.357099107935714e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>8.895095970368608e-08</v>
+        <v>8.895095970368612e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>1.195552185379983e-07</v>
+        <v>1.195552185379985e-07</v>
       </c>
     </row>
     <row r="6">
@@ -2655,37 +2655,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.865013753942319e-08</v>
+        <v>4.865013753942325e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>4.812870264526613e-08</v>
+        <v>4.812870264526561e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>7.093887004577743e-08</v>
+        <v>7.09388700457775e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>4.86788286622453e-08</v>
+        <v>4.867882866224538e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>4.909151296884745e-08</v>
+        <v>4.909151296884751e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>5.876628424741679e-08</v>
+        <v>5.876628424741686e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>6.046720987022653e-08</v>
+        <v>6.046720987022663e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>5.679107085106829e-08</v>
+        <v>5.679107085106839e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>5.779937269773975e-08</v>
+        <v>5.779937269773978e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>4.965499001654032e-08</v>
+        <v>4.965499001654037e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>5.10788287054667e-08</v>
+        <v>5.107882870546673e-08</v>
       </c>
     </row>
     <row r="7">
@@ -2695,37 +2695,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.632147147332248e-08</v>
+        <v>5.632147147332257e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>5.618911891444106e-08</v>
+        <v>5.618911891444115e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>7.806604415273974e-08</v>
+        <v>7.806604415273978e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>5.679746957546476e-08</v>
+        <v>5.679746957546488e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>5.679746957546476e-08</v>
+        <v>5.679746957546488e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>6.64376181813161e-08</v>
+        <v>6.643761818131621e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>5.886072140974301e-08</v>
+        <v>5.886072140974324e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>5.67771959136046e-08</v>
+        <v>5.677719591360473e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>6.524844169870841e-08</v>
+        <v>6.524844169870852e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>5.754169338036472e-08</v>
+        <v>5.754169338036478e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>5.873662475006742e-08</v>
+        <v>5.873662475006751e-08</v>
       </c>
     </row>
     <row r="8">
@@ -2735,37 +2735,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.629649888599561e-08</v>
+        <v>6.629649888599568e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>7.957462310632914e-08</v>
+        <v>7.957462310632937e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>1.04209051855108e-07</v>
+        <v>1.042090518551082e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>7.650156781278712e-08</v>
+        <v>7.650156781278724e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>6.7190902858921e-08</v>
+        <v>6.719090285892115e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>8.980286278091614e-08</v>
+        <v>8.980286278091634e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>8.222596600939588e-08</v>
+        <v>8.222596600939601e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>8.014244051320466e-08</v>
+        <v>8.014244051320481e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>8.861631785878397e-08</v>
+        <v>8.861631785878416e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>6.726799063376028e-08</v>
+        <v>6.726799063376038e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>9.608907087352501e-08</v>
+        <v>9.608907087352528e-08</v>
       </c>
     </row>
     <row r="9">
@@ -2775,37 +2775,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7.354798188395588e-08</v>
+        <v>7.354798188395607e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>8.124918890282588e-08</v>
+        <v>8.12491889028261e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>1.031273430034464e-07</v>
+        <v>1.031273430034467e-07</v>
       </c>
       <c r="E9" t="n">
-        <v>9.088054331384028e-08</v>
+        <v>9.088054331384057e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>8.184076781102461e-08</v>
+        <v>8.184076781102486e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>9.149768816970096e-08</v>
+        <v>9.149768816970123e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>8.392079139812784e-08</v>
+        <v>8.392079139812811e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>8.18372659019894e-08</v>
+        <v>8.183726590198962e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>9.030851168709324e-08</v>
+        <v>9.030851168709346e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>7.806297429280543e-08</v>
+        <v>7.806297429280557e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>8.379669473845226e-08</v>
+        <v>8.379669473845246e-08</v>
       </c>
     </row>
   </sheetData>
@@ -2891,37 +2891,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.770462734751733e-08</v>
+        <v>1.770462734751736e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.333579079512873e-08</v>
+        <v>1.333579079512872e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.773874193413956e-08</v>
+        <v>1.773874193413949e-08</v>
       </c>
       <c r="E2" t="n">
         <v>1.485187875834278e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.48524862727092e-08</v>
+        <v>1.485248627270922e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.776014140656382e-08</v>
+        <v>1.77601414065638e-08</v>
       </c>
       <c r="H2" t="n">
         <v>1.770877517173862e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.777508009187236e-08</v>
+        <v>1.777508009187239e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.882673752509359e-08</v>
+        <v>1.882673752509355e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>2.491580089358341e-08</v>
+        <v>2.491580089358348e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.775082275427386e-08</v>
+        <v>1.775082275427387e-08</v>
       </c>
     </row>
     <row r="3">
@@ -2931,37 +2931,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.694654204031716e-08</v>
+        <v>1.69465420403171e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>9.788807799588047e-09</v>
+        <v>9.788807799588043e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>1.71951518557161e-08</v>
+        <v>1.719515185571607e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.264511435018674e-08</v>
+        <v>1.26451143501867e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.264572186455315e-08</v>
+        <v>1.264572186455306e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.734878398304845e-08</v>
+        <v>1.734878398304842e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.721411669989551e-08</v>
+        <v>1.721411669989552e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.745448511511247e-08</v>
+        <v>1.74544851151124e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>2.156432410245193e-08</v>
+        <v>2.156432410245192e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>2.891165998511317e-08</v>
+        <v>2.891165998511322e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.734192955059532e-08</v>
+        <v>1.734192955059531e-08</v>
       </c>
     </row>
     <row r="4">
@@ -2971,37 +2971,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.88013628940471e-08</v>
+        <v>4.880136289404708e-08</v>
       </c>
       <c r="C4" t="n">
         <v>4.842036955958333e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>4.918670284342946e-08</v>
+        <v>4.918670284342944e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>4.912837612167999e-08</v>
+        <v>4.912837612167998e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>4.912837612167999e-08</v>
+        <v>4.912837612167998e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>4.935684242641702e-08</v>
+        <v>4.9356842426417e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>4.926673194930173e-08</v>
+        <v>4.926673194930172e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>4.911414365663897e-08</v>
+        <v>4.911414365663898e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>5.447680690766478e-08</v>
+        <v>5.447680690766476e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>4.891693548601434e-08</v>
+        <v>4.891693548601433e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>4.942176605045123e-08</v>
+        <v>4.942176605045121e-08</v>
       </c>
     </row>
     <row r="5">
@@ -3011,28 +3011,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.80321608326006e-08</v>
+        <v>5.803216083260055e-08</v>
       </c>
       <c r="C5" t="n">
         <v>5.943094845189801e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>6.750722339420851e-08</v>
+        <v>6.750722339420847e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>7.427803625836077e-08</v>
+        <v>7.42780362583608e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>7.427803625836077e-08</v>
+        <v>7.42780362583608e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>7.21787783446676e-08</v>
+        <v>7.217877834466773e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>7.174709270546102e-08</v>
+        <v>7.174709270546104e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>7.427655677139161e-08</v>
+        <v>7.427655677139157e-08</v>
       </c>
       <c r="J5" t="n">
         <v>1.630184134311767e-07</v>
@@ -3041,7 +3041,7 @@
         <v>6.298898308281723e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>7.528311589413418e-08</v>
+        <v>7.528311589413414e-08</v>
       </c>
     </row>
     <row r="6">
@@ -3051,34 +3051,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.717350084101389e-08</v>
+        <v>4.717350084101387e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>4.708736458009973e-08</v>
+        <v>4.708736458009972e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>5.437424820139354e-08</v>
+        <v>5.437424820139357e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>4.734180522601611e-08</v>
+        <v>4.734180522601616e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>4.749593228524848e-08</v>
+        <v>4.74959322852485e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>4.772898037338379e-08</v>
+        <v>4.772898037338382e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>5.563559422386972e-08</v>
+        <v>5.563559422386973e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>5.397225096191562e-08</v>
+        <v>5.397225096191561e-08</v>
       </c>
       <c r="J6" t="n">
         <v>5.963347753731961e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>4.723227518635901e-08</v>
+        <v>4.72322751863589e-08</v>
       </c>
       <c r="L6" t="n">
         <v>4.779596004450794e-08</v>
@@ -3091,34 +3091,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.400470879561477e-08</v>
+        <v>5.400470879561474e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>5.405031578849001e-08</v>
+        <v>5.405031578848997e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>5.43889038330156e-08</v>
+        <v>5.438890383301559e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>5.434369235271715e-08</v>
+        <v>5.434369235271714e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>5.434369235271715e-08</v>
+        <v>5.434369235271714e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>5.456018832798474e-08</v>
+        <v>5.45601883279847e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>5.447007785086942e-08</v>
+        <v>5.44700778508694e-08</v>
       </c>
       <c r="I7" t="n">
         <v>5.431748955820667e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>5.968015280923243e-08</v>
+        <v>5.968015280923239e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>5.412028138758202e-08</v>
+        <v>5.412028138758199e-08</v>
       </c>
       <c r="L7" t="n">
         <v>5.462511195201892e-08</v>
@@ -3131,37 +3131,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.28973401032209e-08</v>
+        <v>6.289734010322089e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>7.473064689132737e-08</v>
+        <v>7.473064689132735e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>7.748149248452539e-08</v>
+        <v>7.748149248452537e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>7.177970700410162e-08</v>
+        <v>7.177970700410167e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>6.359981371406218e-08</v>
+        <v>6.359981371406222e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>7.521306796527456e-08</v>
+        <v>7.521306796527452e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>7.51229574882708e-08</v>
+        <v>7.512295748827081e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>7.497036919549655e-08</v>
+        <v>7.497036919549653e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>8.033534367147675e-08</v>
+        <v>8.033534367147668e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>6.279446004425179e-08</v>
+        <v>6.279446004425177e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>8.756255434616614e-08</v>
+        <v>8.756255434616608e-08</v>
       </c>
     </row>
     <row r="9">
@@ -3171,34 +3171,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.582003364636504e-08</v>
+        <v>6.582003364636505e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>7.179260775574972e-08</v>
+        <v>7.179260775574973e-08</v>
       </c>
       <c r="D9" t="n">
         <v>7.213234925300047e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>7.890086650952829e-08</v>
+        <v>7.890086650952828e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>7.206126372922933e-08</v>
+        <v>7.20612637292293e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>7.230248029524449e-08</v>
+        <v>7.230248029524445e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>7.221236981812918e-08</v>
+        <v>7.221236981812921e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>7.205978152546643e-08</v>
+        <v>7.20597815254664e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>7.742244477649218e-08</v>
+        <v>7.74224447764922e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>6.842846892274358e-08</v>
+        <v>6.842846892274356e-08</v>
       </c>
       <c r="L9" t="n">
         <v>7.236740391927867e-08</v>
@@ -3287,19 +3287,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.723225310661802e-08</v>
+        <v>1.7232253106618e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.327208848868151e-08</v>
+        <v>1.32720884886815e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.726574208774432e-08</v>
+        <v>1.726574208774431e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.473285524262698e-08</v>
+        <v>1.4732855242627e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.473347041051462e-08</v>
+        <v>1.473347041051463e-08</v>
       </c>
       <c r="G2" t="n">
         <v>1.725451866696051e-08</v>
@@ -3308,16 +3308,16 @@
         <v>1.722720178746889e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.727523642334395e-08</v>
+        <v>1.727523642334393e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.843727258913882e-08</v>
+        <v>1.84372725891388e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>2.480436415835546e-08</v>
+        <v>2.480436415835545e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.725441564234372e-08</v>
+        <v>1.725441564234373e-08</v>
       </c>
     </row>
     <row r="3">
@@ -3327,34 +3327,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.622266261012065e-08</v>
+        <v>1.622266261012063e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>9.760773660665015e-09</v>
+        <v>9.760773660665007e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>1.646685797329904e-08</v>
+        <v>1.646685797329901e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.235415522766082e-08</v>
+        <v>1.235415522766078e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.235477039554848e-08</v>
+        <v>1.235477039554852e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.638776943962396e-08</v>
+        <v>1.6387769439624e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.642121691093489e-08</v>
+        <v>1.642121691093488e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.653490060800967e-08</v>
+        <v>1.653490060800966e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>2.010852161221564e-08</v>
+        <v>2.010852161221563e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>2.874027809435663e-08</v>
+        <v>2.874027809435667e-08</v>
       </c>
       <c r="L3" t="n">
         <v>1.644414994260963e-08</v>
@@ -3367,37 +3367,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.889065410984159e-08</v>
+        <v>4.889065410984153e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>4.866356671817414e-08</v>
+        <v>4.8663566718174e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>4.926892755735562e-08</v>
+        <v>4.926892755735557e-08</v>
       </c>
       <c r="E4" t="n">
+        <v>4.876751714644846e-08</v>
+      </c>
+      <c r="F4" t="n">
         <v>4.876751714644847e-08</v>
       </c>
-      <c r="F4" t="n">
-        <v>4.876751714644848e-08</v>
-      </c>
       <c r="G4" t="n">
-        <v>4.907806003308953e-08</v>
+        <v>4.907806003308747e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>4.924663599250994e-08</v>
+        <v>4.924663599250997e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>4.894319885940394e-08</v>
+        <v>4.894319885940431e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>5.277861691933259e-08</v>
+        <v>5.277861691933251e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>4.891679062419017e-08</v>
+        <v>4.891679062419015e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>4.923718129472719e-08</v>
+        <v>4.923718129472721e-08</v>
       </c>
     </row>
     <row r="5">
@@ -3407,37 +3407,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.760406330944481e-08</v>
+        <v>5.760406330944449e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>5.979771500941709e-08</v>
+        <v>5.979771500941708e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>6.69803266292988e-08</v>
+        <v>6.698032662929877e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>6.859118287640888e-08</v>
+        <v>6.859118287640876e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>6.859118287640888e-08</v>
+        <v>6.859118287640873e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>6.519929286700051e-08</v>
+        <v>6.5199292867e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>6.918272773482985e-08</v>
+        <v>6.918272773482984e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>6.85897895552735e-08</v>
+        <v>6.858978955527336e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>1.30677878960623e-07</v>
+        <v>1.306778789606231e-07</v>
       </c>
       <c r="K5" t="n">
         <v>6.105394124868414e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>6.945915983001098e-08</v>
+        <v>6.945915983001091e-08</v>
       </c>
     </row>
     <row r="6">
@@ -3447,37 +3447,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.382359725342642e-08</v>
+        <v>5.382359725342639e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>4.72641477864651e-08</v>
+        <v>4.726414778646508e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>4.76628437856965e-08</v>
+        <v>4.766284378569654e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>4.71688488980337e-08</v>
+        <v>4.716884889803371e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>4.73430478731493e-08</v>
+        <v>4.734304787314926e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>5.401100317667225e-08</v>
+        <v>5.401100317667238e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>4.764172123179334e-08</v>
+        <v>4.764172123179328e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>5.387614200298918e-08</v>
+        <v>5.387614200298919e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>5.133753811033734e-08</v>
+        <v>5.133753811033731e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>4.726128195030268e-08</v>
+        <v>4.726128195030267e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>4.763029292682212e-08</v>
+        <v>4.763029292682213e-08</v>
       </c>
     </row>
     <row r="7">
@@ -3487,37 +3487,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.408336435539335e-08</v>
+        <v>5.408336435539334e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>5.417397510079314e-08</v>
+        <v>5.417397510079307e-08</v>
       </c>
       <c r="D7" t="n">
         <v>5.446049034492801e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>5.415733728334848e-08</v>
+        <v>5.415733728334847e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>5.415733728334848e-08</v>
+        <v>5.415733728334846e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>5.427077027863927e-08</v>
+        <v>5.427077027863921e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>5.443934623806179e-08</v>
+        <v>5.44393462380618e-08</v>
       </c>
       <c r="I7" t="n">
         <v>5.413590910495613e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>5.797132716488435e-08</v>
+        <v>5.797132716488432e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>5.410950086974192e-08</v>
+        <v>5.410950086974197e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>5.442989154027897e-08</v>
+        <v>5.442989154027904e-08</v>
       </c>
     </row>
     <row r="8">
@@ -3527,37 +3527,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.301467386517679e-08</v>
+        <v>6.301467386517683e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>7.491575162453222e-08</v>
+        <v>7.491575162453218e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>7.762464173014567e-08</v>
+        <v>7.762464173014577e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>7.165250423363304e-08</v>
+        <v>7.165250423363306e-08</v>
       </c>
       <c r="F8" t="n">
         <v>6.345489322576054e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>7.49895628124609e-08</v>
+        <v>7.4989562812461e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>7.515813877208141e-08</v>
+        <v>7.515813877208139e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>7.485470163877785e-08</v>
+        <v>7.485470163877782e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>7.869243627548047e-08</v>
+        <v>7.869243627548045e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>6.282185183011517e-08</v>
+        <v>6.282185183011519e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>8.746169574633927e-08</v>
+        <v>8.746169574633934e-08</v>
       </c>
     </row>
     <row r="9">
@@ -3567,37 +3567,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.465930337698194e-08</v>
+        <v>6.465930337698196e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>7.033528032781371e-08</v>
+        <v>7.033528032781373e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>7.062295138310382e-08</v>
+        <v>7.062295138310391e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>7.674401269265863e-08</v>
+        <v>7.674401269265868e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>7.029861030613388e-08</v>
+        <v>7.029861030613395e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>7.043207550565985e-08</v>
+        <v>7.043207550565993e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>7.060065146508246e-08</v>
+        <v>7.060065146508238e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>7.029721433197674e-08</v>
+        <v>7.029721433197676e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>7.413263239190489e-08</v>
+        <v>7.413263239190493e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>6.703462649522279e-08</v>
+        <v>6.703462649522276e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>7.059119676729961e-08</v>
+        <v>7.059119676729959e-08</v>
       </c>
     </row>
   </sheetData>
@@ -3683,37 +3683,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.846822944212187e-08</v>
+        <v>1.846822944212298e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.381522249751491e-08</v>
+        <v>1.3815222497516e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.873268916734105e-08</v>
+        <v>1.873268916734073e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.532850179400726e-08</v>
+        <v>1.532850179400888e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.532911297413306e-08</v>
+        <v>1.532911297413437e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.877848914033475e-08</v>
+        <v>1.877848914033456e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.861471072115454e-08</v>
+        <v>1.861471072115537e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.854167185534687e-08</v>
+        <v>1.854167185534676e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.952717308479804e-08</v>
+        <v>1.952717308479862e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>2.545150954574413e-08</v>
+        <v>2.545150954574491e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.864542341404571e-08</v>
+        <v>1.86454234140458e-08</v>
       </c>
     </row>
     <row r="3">
@@ -3723,34 +3723,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.785176857925796e-08</v>
+        <v>1.785176857925801e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.016918125129051e-08</v>
+        <v>1.016918125129052e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.974079555170793e-08</v>
+        <v>1.97407955517078e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.309293851395707e-08</v>
+        <v>1.309293851395694e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.309354969408259e-08</v>
+        <v>1.309354969408249e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>2.007105160066241e-08</v>
+        <v>2.007105160066238e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.915742142409294e-08</v>
+        <v>1.915742142409295e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.838095836533388e-08</v>
+        <v>1.838095836533394e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>2.319393692207006e-08</v>
+        <v>2.319393692206998e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>2.954757822858582e-08</v>
+        <v>2.954757822858587e-08</v>
       </c>
       <c r="L3" t="n">
         <v>1.920486966580983e-08</v>
@@ -3763,37 +3763,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.944535395849458e-08</v>
+        <v>4.944535395849453e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>4.865694678952565e-08</v>
+        <v>4.865694678952564e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>5.243254821231315e-08</v>
+        <v>5.24325482123131e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>4.936196628793354e-08</v>
+        <v>4.936196628793353e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>4.936196628793354e-08</v>
+        <v>4.936196628793352e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>5.28938596651612e-08</v>
+        <v>5.289385966516117e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>5.15498681985025e-08</v>
+        <v>5.154986819850242e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>4.98956811393452e-08</v>
+        <v>4.989568113934518e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>5.682540689622434e-08</v>
+        <v>5.682540689622436e-08</v>
       </c>
       <c r="K4" t="n">
         <v>4.97816805271516e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>5.157633583660713e-08</v>
+        <v>5.157633583660718e-08</v>
       </c>
     </row>
     <row r="5">
@@ -3803,34 +3803,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.196130662037005e-08</v>
+        <v>6.196130662037002e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>6.120665193184127e-08</v>
+        <v>6.120665193184128e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>1.184307566409932e-07</v>
+        <v>1.18430756640993e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>7.977901454972845e-08</v>
+        <v>7.977901454972838e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>7.977901454972846e-08</v>
+        <v>7.977901454972838e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>1.298549655342317e-07</v>
+        <v>1.298549655342334e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>1.097570518851919e-07</v>
+        <v>1.097570518851918e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>7.977704478923268e-08</v>
+        <v>7.977704478923265e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>2.046048384405511e-07</v>
+        <v>2.046048384405517e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>7.110546521367567e-08</v>
+        <v>7.110546521367565e-08</v>
       </c>
       <c r="L5" t="n">
         <v>1.115383698140695e-07</v>
@@ -3843,22 +3843,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.778631785098504e-08</v>
+        <v>4.778631785098502e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>4.748057729494438e-08</v>
+        <v>4.748057729494435e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>5.082892576806624e-08</v>
+        <v>5.082892576806619e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>4.797569871624449e-08</v>
+        <v>4.797569871624446e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>4.823843447090361e-08</v>
+        <v>4.823843447090362e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>5.123482355765161e-08</v>
+        <v>5.123482355765163e-08</v>
       </c>
       <c r="H6" t="n">
         <v>5.856982279393316e-08</v>
@@ -3867,13 +3867,13 @@
         <v>4.823664503183569e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>5.536197191224177e-08</v>
+        <v>5.536197191224172e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>4.801794818079044e-08</v>
+        <v>4.80179481807905e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>4.992901554034419e-08</v>
+        <v>4.992901554034423e-08</v>
       </c>
     </row>
     <row r="7">
@@ -3883,13 +3883,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.517277853612301e-08</v>
+        <v>5.517277853612296e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>5.509382100908967e-08</v>
+        <v>5.509382100908969e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>5.815876039343168e-08</v>
+        <v>5.815876039343167e-08</v>
       </c>
       <c r="E7" t="n">
         <v>5.564745144085901e-08</v>
@@ -3898,22 +3898,22 @@
         <v>5.564745144085901e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>5.862128424278963e-08</v>
+        <v>5.862128424278957e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>5.727729277613091e-08</v>
+        <v>5.727729277613082e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>5.562310571697362e-08</v>
+        <v>5.562310571697364e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>6.255283147385285e-08</v>
+        <v>6.255283147385277e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>5.550910510477996e-08</v>
+        <v>5.550910510478e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>5.73037604142356e-08</v>
+        <v>5.730376041423563e-08</v>
       </c>
     </row>
     <row r="8">
@@ -3923,31 +3923,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.473243187197054e-08</v>
+        <v>6.473243187197049e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>7.740386865264466e-08</v>
+        <v>7.740386865264468e-08</v>
       </c>
       <c r="D8" t="n">
         <v>8.308313271419143e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>7.445189395710604e-08</v>
+        <v>7.445189395710605e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>6.56021605077108e-08</v>
+        <v>6.560216050771084e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>8.090585056415879e-08</v>
+        <v>8.090585056415873e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>7.956185909755184e-08</v>
+        <v>7.956185909755186e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>7.79076720383428e-08</v>
+        <v>7.790767203834276e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>8.483989860444845e-08</v>
+        <v>8.483989860444825e-08</v>
       </c>
       <c r="K8" t="n">
         <v>6.483238664844933e-08</v>
@@ -3963,25 +3963,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7.010336108290567e-08</v>
+        <v>7.010336108290565e-08</v>
       </c>
       <c r="C9" t="n">
         <v>7.704831448378754e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>8.011447671994916e-08</v>
+        <v>8.011447671994912e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>8.568502590961898e-08</v>
+        <v>8.568502590961902e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>7.757957153314945e-08</v>
+        <v>7.757957153314943e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>8.057577771748752e-08</v>
+        <v>8.057577771748747e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>7.923178625082887e-08</v>
+        <v>7.923178625082874e-08</v>
       </c>
       <c r="I9" t="n">
         <v>7.757759919167159e-08</v>
@@ -3990,10 +3990,10 @@
         <v>8.450732494855071e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>7.339392140027949e-08</v>
+        <v>7.339392140027944e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>7.925825388893353e-08</v>
+        <v>7.925825388893356e-08</v>
       </c>
     </row>
   </sheetData>
@@ -4079,37 +4079,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.722782011688058e-08</v>
+        <v>1.722782011688044e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.342032653194338e-08</v>
+        <v>1.342032653194337e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.725446974880033e-08</v>
+        <v>1.725446974880019e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.489425190351229e-08</v>
+        <v>1.489425190351223e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.489485974882899e-08</v>
+        <v>1.489485974882895e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.724747604267378e-08</v>
+        <v>1.724747604267364e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.721854283609731e-08</v>
+        <v>1.721854283609733e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.728677356298833e-08</v>
+        <v>1.728677356298821e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.883287919754042e-08</v>
+        <v>1.883287919754037e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>2.50297928939737e-08</v>
+        <v>2.502979289397368e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.725197673331739e-08</v>
+        <v>1.72519767333174e-08</v>
       </c>
     </row>
     <row r="3">
@@ -4119,37 +4119,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.613108791879681e-08</v>
+        <v>1.613108791879675e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>9.874277776127404e-09</v>
+        <v>9.874277776127409e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>1.632643653406694e-08</v>
+        <v>1.63264365340669e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.262362987472372e-08</v>
+        <v>1.262362987472377e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.262423772004042e-08</v>
+        <v>1.262423772004048e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.627754392786448e-08</v>
+        <v>1.627754392786446e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.62997665488208e-08</v>
+        <v>1.629976654882082e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.65570196968569e-08</v>
+        <v>1.655701969685687e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>2.157566229976299e-08</v>
+        <v>2.1575662299763e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>2.911062542372417e-08</v>
+        <v>2.911062542372415e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.636692894946418e-08</v>
+        <v>1.636692894946419e-08</v>
       </c>
     </row>
     <row r="4">
@@ -4159,37 +4159,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.883944592272878e-08</v>
+        <v>4.883944592272882e-08</v>
       </c>
       <c r="C4" t="n">
         <v>4.839898513690897e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>4.914046577469898e-08</v>
+        <v>4.914046577469904e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>4.905326880213497e-08</v>
+        <v>4.905326880213499e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>4.905326880213496e-08</v>
+        <v>4.905326880213499e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>4.89899562649338e-08</v>
+        <v>4.898995626493389e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>4.914791631587705e-08</v>
+        <v>4.91479163158771e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>4.902278365740604e-08</v>
+        <v>4.902278365740607e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>5.457572648402941e-08</v>
+        <v>5.457572648402944e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>4.903609549390421e-08</v>
+        <v>4.903609549390415e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>4.92078956587238e-08</v>
+        <v>4.920789565872379e-08</v>
       </c>
     </row>
     <row r="5">
@@ -4199,37 +4199,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.932815322527735e-08</v>
+        <v>5.932815322527737e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>5.981970877090218e-08</v>
+        <v>5.981970877090216e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>6.732045427358959e-08</v>
+        <v>6.732045427358965e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>7.33080738873821e-08</v>
+        <v>7.330807388738214e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>7.33080738873821e-08</v>
+        <v>7.330807388738214e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>6.63812812609278e-08</v>
+        <v>6.63812812609289e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>7.015160943981736e-08</v>
+        <v>7.015160943981741e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>7.330665273947452e-08</v>
+        <v>7.330665273947455e-08</v>
       </c>
       <c r="J5" t="n">
         <v>1.654150462434195e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>6.56241314973349e-08</v>
+        <v>6.562413149733499e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>7.180349085049422e-08</v>
+        <v>7.180349085049419e-08</v>
       </c>
     </row>
     <row r="6">
@@ -4239,37 +4239,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.370299878005638e-08</v>
+        <v>5.370299878005646e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>4.710331942690103e-08</v>
+        <v>4.710331942690095e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>4.756152398560955e-08</v>
+        <v>4.75615239856095e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>4.727878210800329e-08</v>
+        <v>4.727878210800332e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>4.742958034498146e-08</v>
+        <v>4.742958034498151e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>4.738635326235218e-08</v>
+        <v>4.738635326235222e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>5.551518673802902e-08</v>
+        <v>5.551518673802914e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>5.388633651473366e-08</v>
+        <v>5.388633651473369e-08</v>
       </c>
       <c r="J6" t="n">
         <v>5.31424532299442e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>4.738975241038616e-08</v>
+        <v>4.73897524103861e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>4.760454959950022e-08</v>
+        <v>4.760454959950021e-08</v>
       </c>
     </row>
     <row r="7">
@@ -4279,37 +4279,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.396166993392819e-08</v>
+        <v>5.396166993392811e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>5.395578732971931e-08</v>
+        <v>5.39557873297193e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>5.426154922338082e-08</v>
+        <v>5.426154922338084e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>5.41752536335187e-08</v>
+        <v>5.417525363351874e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>5.41752536335187e-08</v>
+        <v>5.417525363351874e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>5.411218027613322e-08</v>
+        <v>5.411218027613324e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>5.427014032707646e-08</v>
+        <v>5.427014032707639e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>5.414500766860546e-08</v>
+        <v>5.414500766860548e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>5.969795049522882e-08</v>
+        <v>5.969795049522888e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>5.415831950510362e-08</v>
+        <v>5.415831950510363e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>5.433011966992317e-08</v>
+        <v>5.43301196699232e-08</v>
       </c>
     </row>
     <row r="8">
@@ -4319,37 +4319,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.278652338458335e-08</v>
+        <v>6.278652338458346e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>7.446999921280174e-08</v>
+        <v>7.446999921280178e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>7.71629217864051e-08</v>
+        <v>7.716292178640519e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>7.146859856341684e-08</v>
+        <v>7.146859856341694e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>6.335869909730143e-08</v>
+        <v>6.335869909730144e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>7.459504723139421e-08</v>
+        <v>7.459504723139425e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>7.475300728244644e-08</v>
+        <v>7.475300728244643e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>7.46278746238664e-08</v>
+        <v>7.46278746238665e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>8.01831085831409e-08</v>
+        <v>8.018310858314098e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>6.276661936920561e-08</v>
+        <v>6.27666193692056e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>8.699075655829511e-08</v>
+        <v>8.699075655829526e-08</v>
       </c>
     </row>
     <row r="9">
@@ -4359,37 +4359,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.570791839272422e-08</v>
+        <v>6.570791839272427e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>7.15841458960748e-08</v>
+        <v>7.158414589607482e-08</v>
       </c>
       <c r="D9" t="n">
         <v>7.189105671418595e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>7.856262872536834e-08</v>
+        <v>7.856262872536844e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>7.177479013506628e-08</v>
+        <v>7.177479013506638e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>7.174053884248867e-08</v>
+        <v>7.174053884248875e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>7.189849889343194e-08</v>
+        <v>7.189849889343196e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>7.177336623496091e-08</v>
+        <v>7.177336623496098e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>7.732630906158428e-08</v>
+        <v>7.73263090615844e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>6.438004932586868e-08</v>
+        <v>6.438004932586861e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>7.195847823627869e-08</v>
+        <v>7.195847823627878e-08</v>
       </c>
     </row>
   </sheetData>
@@ -4475,37 +4475,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.728210093795388e-08</v>
+        <v>1.728210093795386e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.357424664944455e-08</v>
+        <v>1.357424664944457e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.730889355999974e-08</v>
+        <v>1.73088935599997e-08</v>
       </c>
       <c r="E2" t="n">
         <v>1.495405123861029e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.495466737982937e-08</v>
+        <v>1.495466737982938e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.730063712180977e-08</v>
+        <v>1.730063712180976e-08</v>
       </c>
       <c r="H2" t="n">
         <v>1.727312457295175e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.732135410305856e-08</v>
+        <v>1.732135410305855e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.86323553128251e-08</v>
+        <v>1.863235531282509e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>2.50871372235392e-08</v>
+        <v>2.508713722353918e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.7300515185299e-08</v>
+        <v>1.730051518529901e-08</v>
       </c>
     </row>
     <row r="3">
@@ -4515,37 +4515,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.597272824299962e-08</v>
+        <v>1.597272824299963e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>9.904016967142491e-09</v>
+        <v>9.90401696714249e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>1.616917791632092e-08</v>
+        <v>1.616917791632088e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.236660036687758e-08</v>
+        <v>1.236660036687757e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.236721650809667e-08</v>
+        <v>1.236721650809666e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.611122491293716e-08</v>
+        <v>1.611122491293712e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.614291967288034e-08</v>
+        <v>1.614291967288035e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.625834735976879e-08</v>
+        <v>1.625834735976878e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>2.0098483120765e-08</v>
+        <v>2.009848312076494e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>2.894008739233353e-08</v>
+        <v>2.894008739233354e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.616775802287709e-08</v>
+        <v>1.61677580228771e-08</v>
       </c>
     </row>
     <row r="4">
@@ -4555,7 +4555,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.893527138193984e-08</v>
+        <v>4.893527138193983e-08</v>
       </c>
       <c r="C4" t="n">
         <v>4.864243055280411e-08</v>
@@ -4564,10 +4564,10 @@
         <v>4.923790637316255e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>4.87697590201769e-08</v>
+        <v>4.876975902017691e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>4.87697590201769e-08</v>
+        <v>4.876975902017691e-08</v>
       </c>
       <c r="G4" t="n">
         <v>4.908023524042564e-08</v>
@@ -4576,16 +4576,16 @@
         <v>4.924625254335852e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>4.894358684979077e-08</v>
+        <v>4.894358684979078e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>5.282351514495596e-08</v>
+        <v>5.282351514495594e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>4.90961939232354e-08</v>
+        <v>4.909619392323538e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>4.923995705656967e-08</v>
+        <v>4.923995705656966e-08</v>
       </c>
     </row>
     <row r="5">
@@ -4595,37 +4595,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.84174484920028e-08</v>
+        <v>5.841744849200282e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>5.978278798149389e-08</v>
+        <v>5.97827879814939e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>6.64800487802266e-08</v>
+        <v>6.648004878022665e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>6.865903400573032e-08</v>
+        <v>6.865903400573035e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>6.865903400573032e-08</v>
+        <v>6.865903400573035e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>6.527072366578335e-08</v>
+        <v>6.527072366578403e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>6.92064034482454e-08</v>
+        <v>6.920640344824541e-08</v>
       </c>
       <c r="I5" t="n">
         <v>6.865763422277225e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>1.315079630471375e-07</v>
+        <v>1.315079630471376e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>6.414263041938558e-08</v>
+        <v>6.41426304193856e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>6.954498098309079e-08</v>
+        <v>6.954498098309074e-08</v>
       </c>
     </row>
     <row r="6">
@@ -4635,34 +4635,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.392012834299273e-08</v>
+        <v>5.392012834299271e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>4.729148940521339e-08</v>
+        <v>4.729148940521338e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>4.766760877678354e-08</v>
+        <v>4.766760877678353e-08</v>
       </c>
       <c r="E6" t="n">
         <v>4.719988357789109e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>4.737802366227886e-08</v>
+        <v>4.737802366227888e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>4.750793292660508e-08</v>
+        <v>4.750793292660506e-08</v>
       </c>
       <c r="H6" t="n">
         <v>5.590552417945579e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>4.737128453597019e-08</v>
+        <v>4.737128453597022e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>5.812664321910741e-08</v>
+        <v>5.81266432191074e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>4.748441417783806e-08</v>
+        <v>4.748441417783804e-08</v>
       </c>
       <c r="L6" t="n">
         <v>4.766785794743717e-08</v>
@@ -4675,37 +4675,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.406580745805495e-08</v>
+        <v>5.406580745805493e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>5.410879790160041e-08</v>
+        <v>5.410879790160045e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>5.436730050533929e-08</v>
+        <v>5.436730050533927e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>5.409643802916594e-08</v>
+        <v>5.409643802916596e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>5.409643802916594e-08</v>
+        <v>5.409643802916596e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>5.421077131654076e-08</v>
+        <v>5.421077131654074e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>5.437678861947362e-08</v>
+        <v>5.437678861947361e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>5.407412292590585e-08</v>
+        <v>5.407412292590586e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>5.795405122107106e-08</v>
+        <v>5.795405122107104e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>5.422672999935048e-08</v>
+        <v>5.422672999935046e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>5.437049313268478e-08</v>
+        <v>5.437049313268475e-08</v>
       </c>
     </row>
     <row r="8">
@@ -4715,25 +4715,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.295028284076219e-08</v>
+        <v>6.295028284076217e-08</v>
       </c>
       <c r="C8" t="n">
         <v>7.473503159211259e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>7.740066656792458e-08</v>
+        <v>7.74006665679246e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>7.149411296487095e-08</v>
+        <v>7.149411296487097e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>6.334459738524528e-08</v>
+        <v>6.334459738524527e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>7.481320122818136e-08</v>
+        <v>7.481320122818137e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>7.497921853130972e-08</v>
+        <v>7.497921853130968e-08</v>
       </c>
       <c r="I8" t="n">
         <v>7.46765528375465e-08</v>
@@ -4742,10 +4742,10 @@
         <v>7.855878404484771e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>6.289353836016623e-08</v>
+        <v>6.289353836016616e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>8.72133063892722e-08</v>
+        <v>8.721330638927222e-08</v>
       </c>
     </row>
     <row r="9">
@@ -4755,37 +4755,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.466828473743773e-08</v>
+        <v>6.466828473743779e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>7.028667036475207e-08</v>
+        <v>7.028667036475215e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>7.054632326794033e-08</v>
+        <v>7.054632326794041e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>7.668729394700374e-08</v>
+        <v>7.668729394700386e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>7.025339788976547e-08</v>
+        <v>7.025339788976555e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>7.03886437796924e-08</v>
+        <v>7.038864377969245e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>7.055466108262524e-08</v>
+        <v>7.055466108262535e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>7.025199538905746e-08</v>
+        <v>7.025199538905758e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>7.413192368422267e-08</v>
+        <v>7.413192368422276e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>6.704313826805427e-08</v>
+        <v>6.704313826805433e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>7.054836559583638e-08</v>
+        <v>7.054836559583648e-08</v>
       </c>
     </row>
   </sheetData>
@@ -4871,19 +4871,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.01527672469479e-08</v>
+        <v>2.015276724694788e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>2.183987671834847e-08</v>
+        <v>2.183987671834845e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>2.64757473580241e-08</v>
+        <v>2.647574735802413e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>2.307540536830478e-08</v>
+        <v>2.307540536830476e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.897574339696803e-08</v>
+        <v>1.897574339696804e-08</v>
       </c>
       <c r="G2" t="n">
         <v>2.322187255028937e-08</v>
@@ -4892,16 +4892,16 @@
         <v>2.036275234765389e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>2.010833112512714e-08</v>
+        <v>2.010833112512715e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>2.825251108860418e-08</v>
+        <v>2.825251108860406e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>3.064361398640971e-08</v>
+        <v>3.064361398640969e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>2.062293123176011e-08</v>
+        <v>2.06229312317601e-08</v>
       </c>
     </row>
     <row r="3">
@@ -4911,34 +4911,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.715240904701491e-08</v>
+        <v>1.715240904701487e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.976294295991322e-08</v>
+        <v>1.976294295991318e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>6.214496929943278e-08</v>
+        <v>6.21449692994328e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>2.174713789510561e-08</v>
+        <v>2.174713789510557e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.497947385347388e-08</v>
+        <v>1.497947385347386e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>3.901978815498249e-08</v>
+        <v>3.901978815498248e-08</v>
       </c>
       <c r="H3" t="n">
         <v>1.920214628253195e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.683348298437359e-08</v>
+        <v>1.68334829843736e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>3.384876525827529e-08</v>
+        <v>3.384876525827522e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>3.550004780930798e-08</v>
+        <v>3.550004780930796e-08</v>
       </c>
       <c r="L3" t="n">
         <v>2.089847433283109e-08</v>
@@ -4951,37 +4951,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.385637423259202e-08</v>
+        <v>5.385637423259196e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>5.193866059774505e-08</v>
+        <v>5.193866059774508e-08</v>
       </c>
       <c r="D4" t="n">
         <v>1.252773433017555e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>5.214793307232839e-08</v>
+        <v>5.214793307232842e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>5.214793307232839e-08</v>
+        <v>5.214793307232841e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>8.844162388889508e-08</v>
+        <v>8.8441623888895e-08</v>
       </c>
       <c r="H4" t="n">
         <v>5.720462646350095e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>5.280170920539306e-08</v>
+        <v>5.280170920539307e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>6.069006854584257e-08</v>
+        <v>6.069006854584259e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>5.598412540683839e-08</v>
+        <v>5.59841254068384e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>5.981542105323283e-08</v>
+        <v>5.981542105323282e-08</v>
       </c>
     </row>
     <row r="5">
@@ -4994,34 +4994,34 @@
         <v>1.026265396942014e-07</v>
       </c>
       <c r="C5" t="n">
-        <v>9.160117860878689e-08</v>
+        <v>9.160117860878698e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>1.378042477972858e-06</v>
+        <v>1.378042477972859e-06</v>
       </c>
       <c r="E5" t="n">
-        <v>9.160119521913594e-08</v>
+        <v>9.160119521913602e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>9.160119521913594e-08</v>
+        <v>9.160119521913602e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>7.374586873067065e-07</v>
+        <v>7.374586873067078e-07</v>
       </c>
       <c r="H5" t="n">
         <v>1.773803533566598e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>9.159166800711921e-08</v>
+        <v>9.159166800711926e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>2.357432001681874e-07</v>
+        <v>2.357432001681872e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>1.412430266229625e-07</v>
+        <v>1.412430266229626e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>1.346723027846051e-07</v>
+        <v>1.34672302784605e-07</v>
       </c>
     </row>
     <row r="6">
@@ -5031,37 +5031,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.332101161452594e-08</v>
+        <v>5.332101161452588e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>5.131232624846846e-08</v>
+        <v>5.131232624846851e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.26505129421823e-07</v>
+        <v>1.265051294218231e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>5.120906529252701e-08</v>
+        <v>5.120906529252702e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>5.218467470406153e-08</v>
+        <v>5.218467470406155e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>8.79062612708289e-08</v>
+        <v>8.790626127082896e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>6.748360840035763e-08</v>
+        <v>6.748360840035764e-08</v>
       </c>
       <c r="I6" t="n">
         <v>6.217070973452484e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>6.043960291024637e-08</v>
+        <v>6.043960291024634e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>5.475869598593017e-08</v>
+        <v>5.47586959859303e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>5.933148919646439e-08</v>
+        <v>5.933148919646438e-08</v>
       </c>
     </row>
     <row r="7">
@@ -5071,25 +5071,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.15399032523126e-08</v>
+        <v>6.153990325231257e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>6.049474882678135e-08</v>
+        <v>6.049474882678137e-08</v>
       </c>
       <c r="D7" t="n">
         <v>1.329595329286204e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>6.047613662071927e-08</v>
+        <v>6.047613662071929e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>6.047613662071927e-08</v>
+        <v>6.047613662071929e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>9.612515290861565e-08</v>
+        <v>9.61251529086156e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>6.488815548322155e-08</v>
+        <v>6.48881554832216e-08</v>
       </c>
       <c r="I7" t="n">
         <v>6.048523822511368e-08</v>
@@ -5098,10 +5098,10 @@
         <v>6.837359756556319e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>6.3667654426559e-08</v>
+        <v>6.366765442655899e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>6.749895007295343e-08</v>
+        <v>6.749895007295347e-08</v>
       </c>
     </row>
     <row r="8">
@@ -5111,34 +5111,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7.255230637890624e-08</v>
+        <v>7.255230637890618e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>8.672116899095249e-08</v>
+        <v>8.672116899095255e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>1.623578108642306e-07</v>
+        <v>1.623578108642304e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>8.255769218067835e-08</v>
+        <v>8.255769218067836e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>7.197953006361216e-08</v>
+        <v>7.19795300636121e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>1.223646535800764e-07</v>
+        <v>1.223646535800763e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>9.112765615467807e-08</v>
+        <v>9.112765615467801e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>8.672473889657443e-08</v>
+        <v>8.67247388965744e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>9.461609079647822e-08</v>
+        <v>9.461609079647816e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>7.439720639830304e-08</v>
+        <v>7.439720639830298e-08</v>
       </c>
       <c r="L8" t="n">
         <v>1.096444273986369e-07</v>
@@ -5151,34 +5151,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8.845501879699704e-08</v>
+        <v>8.845501879699708e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>9.843545895211429e-08</v>
+        <v>9.843545895211437e-08</v>
       </c>
       <c r="D9" t="n">
         <v>1.709016120925486e-07</v>
       </c>
       <c r="E9" t="n">
-        <v>1.111588088032071e-07</v>
+        <v>1.11158808803207e-07</v>
       </c>
       <c r="F9" t="n">
-        <v>9.84354788232006e-08</v>
+        <v>9.843547882320068e-08</v>
       </c>
       <c r="G9" t="n">
         <v>1.340658630339486e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>1.028288656085546e-07</v>
+        <v>1.028288656085545e-07</v>
       </c>
       <c r="I9" t="n">
-        <v>9.842594835044661e-08</v>
+        <v>9.842594835044663e-08</v>
       </c>
       <c r="J9" t="n">
         <v>1.063143076908961e-07</v>
       </c>
       <c r="K9" t="n">
-        <v>9.522010421989551e-08</v>
+        <v>9.522010421989541e-08</v>
       </c>
       <c r="L9" t="n">
         <v>1.054396601982863e-07</v>
@@ -5267,37 +5267,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.985373132356613e-08</v>
+        <v>1.985373132356615e-08</v>
       </c>
       <c r="C2" t="n">
         <v>2.158913363352745e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>2.577148925170024e-08</v>
+        <v>2.577148925170029e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>2.280324894548135e-08</v>
+        <v>2.280324894548146e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.875957903813456e-08</v>
+        <v>1.875957903813461e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>2.291876435783603e-08</v>
+        <v>2.291876435783605e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>2.008694428816872e-08</v>
+        <v>2.008694428816874e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.989597504836775e-08</v>
+        <v>1.98959750483678e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>2.772027999134579e-08</v>
+        <v>2.772027999134578e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>3.037569230230962e-08</v>
+        <v>3.037569230230965e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>2.036633812373735e-08</v>
+        <v>2.03663381237374e-08</v>
       </c>
     </row>
     <row r="3">
@@ -5307,37 +5307,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.642988479213936e-08</v>
+        <v>1.642988479213939e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.959107314259713e-08</v>
+        <v>1.959107314259717e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>5.850288568753145e-08</v>
+        <v>5.850288568753147e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>2.154150733399992e-08</v>
+        <v>2.154150733400021e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.486626872038781e-08</v>
+        <v>1.486626872038784e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>3.825196760983243e-08</v>
+        <v>3.825196760983246e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.863650035549258e-08</v>
+        <v>1.863650035549263e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.672655051298399e-08</v>
+        <v>1.672655051298401e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>3.222057587609868e-08</v>
+        <v>3.222057587609908e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>3.519730861029482e-08</v>
+        <v>3.519730861029485e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>2.047029812039085e-08</v>
+        <v>2.04702981203909e-08</v>
       </c>
     </row>
     <row r="4">
@@ -5347,37 +5347,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.247290999343372e-08</v>
+        <v>5.247290999343382e-08</v>
       </c>
       <c r="C4" t="n">
         <v>5.183997777512812e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>1.193167080948519e-07</v>
+        <v>1.19316708094852e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>5.202212845419868e-08</v>
+        <v>5.202212845419866e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>5.202212845419868e-08</v>
+        <v>5.202212845419866e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>8.701767153318435e-08</v>
+        <v>8.701767153318427e-08</v>
       </c>
       <c r="H4" t="n">
         <v>5.60735089178697e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>5.243412568872033e-08</v>
+        <v>5.243412568872037e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>5.82395112083779e-08</v>
+        <v>5.823951120837801e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>5.537618920284602e-08</v>
+        <v>5.537618920284599e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>5.890066458102193e-08</v>
+        <v>5.890066458102197e-08</v>
       </c>
     </row>
     <row r="5">
@@ -5387,37 +5387,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.42840001537523e-08</v>
+        <v>8.428400015375266e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>8.971374220757352e-08</v>
+        <v>8.97137422075736e-08</v>
       </c>
       <c r="D5" t="n">
         <v>1.1824021892111e-06</v>
       </c>
       <c r="E5" t="n">
-        <v>8.971375218317615e-08</v>
+        <v>8.971375218317616e-08</v>
       </c>
       <c r="F5" t="n">
         <v>8.971375218317615e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>6.689614552142829e-07</v>
+        <v>6.689614552142831e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>1.56841145600597e-07</v>
+        <v>1.568411456005969e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>8.970450963296833e-08</v>
+        <v>8.970450963296841e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>1.886553080567126e-07</v>
+        <v>1.886553080567128e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>1.298481629538904e-07</v>
+        <v>1.298481629538901e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>1.463539870233442e-07</v>
+        <v>1.463539870233437e-07</v>
       </c>
     </row>
     <row r="6">
@@ -5427,37 +5427,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.198868485974577e-08</v>
+        <v>5.198868485974578e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>5.110108824750827e-08</v>
+        <v>5.110108824750828e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.203143641614808e-07</v>
+        <v>1.203143641614809e-07</v>
       </c>
       <c r="E6" t="n">
         <v>5.100109657467256e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>5.187186501565836e-08</v>
+        <v>5.187186501565835e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>8.653344639949642e-08</v>
+        <v>8.653344639949638e-08</v>
       </c>
       <c r="H6" t="n">
         <v>6.552262371343394e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>6.111594947241856e-08</v>
+        <v>6.111594947241855e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>5.800256922790374e-08</v>
+        <v>5.800256922790376e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>5.425533795131785e-08</v>
+        <v>5.425533795131781e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>5.847794224489906e-08</v>
+        <v>5.847794224489897e-08</v>
       </c>
     </row>
     <row r="7">
@@ -5467,10 +5467,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.942896436881958e-08</v>
+        <v>5.942896436881957e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>5.939941263871143e-08</v>
+        <v>5.939941263871139e-08</v>
       </c>
       <c r="D7" t="n">
         <v>1.262715133365448e-07</v>
@@ -5479,25 +5479,25 @@
         <v>5.937842090609832e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>5.937842090609833e-08</v>
+        <v>5.937842090609831e-08</v>
       </c>
       <c r="G7" t="n">
         <v>9.397372590857022e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>6.302956329325557e-08</v>
+        <v>6.302956329325553e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>5.939018006410616e-08</v>
+        <v>5.939018006410617e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>6.519556558376376e-08</v>
+        <v>6.519556558376379e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>6.233224357823189e-08</v>
+        <v>6.23322435782319e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>6.58567189564078e-08</v>
+        <v>6.585671895640777e-08</v>
       </c>
     </row>
     <row r="8">
@@ -5507,34 +5507,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.950087224759645e-08</v>
+        <v>6.950087224759646e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>8.335923289843786e-08</v>
+        <v>8.335923289843799e-08</v>
       </c>
       <c r="D8" t="n">
         <v>1.531313218603924e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>7.955801273929476e-08</v>
+        <v>7.955801273929478e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>6.990027107449996e-08</v>
+        <v>6.99002710745e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>1.179492747676414e-07</v>
+        <v>1.179492747676415e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>8.700511215231893e-08</v>
+        <v>8.700511215231896e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>8.336572892317741e-08</v>
+        <v>8.336572892317744e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>8.91738469049543e-08</v>
+        <v>8.917384690495446e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>7.214588418737027e-08</v>
+        <v>7.214588418737036e-08</v>
       </c>
       <c r="L8" t="n">
         <v>1.043557834221041e-07</v>
@@ -5547,37 +5547,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8.148841711118726e-08</v>
+        <v>8.148841711118723e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>9.082566387380963e-08</v>
+        <v>9.082566387380966e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>1.576990407979049e-07</v>
+        <v>1.57699040797905e-07</v>
       </c>
       <c r="E9" t="n">
         <v>1.016347891376202e-07</v>
       </c>
       <c r="F9" t="n">
-        <v>9.082567700516956e-08</v>
+        <v>9.082567700516962e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>1.253999771436683e-07</v>
+        <v>1.253999771436684e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>9.445581452835368e-08</v>
+        <v>9.445581452835374e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>9.081643129920433e-08</v>
+        <v>9.081643129920442e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>9.662181681886193e-08</v>
+        <v>9.662181681886195e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>8.833134637541461e-08</v>
+        <v>8.833134637541467e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>9.728297019150593e-08</v>
+        <v>9.728297019150601e-08</v>
       </c>
     </row>
   </sheetData>
@@ -5666,34 +5666,34 @@
         <v>1.915812608260465e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>2.093687515149422e-08</v>
+        <v>2.093687515149419e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>2.418853343033428e-08</v>
+        <v>2.418853343033431e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>2.208044382386741e-08</v>
+        <v>2.208044382386736e-08</v>
       </c>
       <c r="F2" t="n">
         <v>1.823240099557861e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>2.183636707248759e-08</v>
+        <v>2.183636707248763e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.940921467554259e-08</v>
+        <v>1.940921467554262e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.92595347693557e-08</v>
+        <v>1.925953476935571e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>2.651909688887895e-08</v>
+        <v>2.651909688887886e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>2.968794487994015e-08</v>
+        <v>2.968794487994014e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.960842953360084e-08</v>
+        <v>1.960842953360085e-08</v>
       </c>
     </row>
     <row r="3">
@@ -5703,34 +5703,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.575652202997217e-08</v>
+        <v>1.575652202997215e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.930524638991125e-08</v>
+        <v>1.930524638991127e-08</v>
       </c>
       <c r="D3" t="n">
         <v>5.145911516916256e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>2.114479921895813e-08</v>
+        <v>2.114479921895811e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.479248250799512e-08</v>
+        <v>1.479248250799508e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>3.480040540314351e-08</v>
+        <v>3.480040540314362e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.804197933237741e-08</v>
+        <v>1.804197933237739e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.647239677752133e-08</v>
+        <v>1.647239677752125e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>2.933697235628004e-08</v>
+        <v>2.933697235627998e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>3.435219810952043e-08</v>
+        <v>3.435219810952052e-08</v>
       </c>
       <c r="L3" t="n">
         <v>1.930651689629132e-08</v>
@@ -5743,16 +5743,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.191951935040639e-08</v>
+        <v>5.191951935040651e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>5.216661762423486e-08</v>
+        <v>5.216661762423487e-08</v>
       </c>
       <c r="D4" t="n">
         <v>1.087402844447217e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>5.233865424467064e-08</v>
+        <v>5.233865424467065e-08</v>
       </c>
       <c r="F4" t="n">
         <v>5.233865424467064e-08</v>
@@ -5761,19 +5761,19 @@
         <v>8.210139823929846e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>5.564376046958121e-08</v>
+        <v>5.564376046958128e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>5.259006779002646e-08</v>
+        <v>5.259006779002643e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>5.485546615484416e-08</v>
+        <v>5.485546615484424e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>5.444873978681143e-08</v>
+        <v>5.444873978681158e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>5.757340027440169e-08</v>
+        <v>5.757340027440176e-08</v>
       </c>
     </row>
     <row r="5">
@@ -5783,37 +5783,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.977021054781864e-08</v>
+        <v>7.977021054781972e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>9.547692780139473e-08</v>
+        <v>9.547692780139472e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>9.812627539978983e-07</v>
+        <v>9.812627539978977e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>9.547693364739214e-08</v>
+        <v>9.547693364739207e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>9.547693364739214e-08</v>
+        <v>9.547693364739207e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>5.780366560546354e-07</v>
+        <v>5.780366560546364e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>1.512953895538875e-07</v>
+        <v>1.512953895538873e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>9.5468874374704e-08</v>
+        <v>9.546887437470384e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>1.336608311205694e-07</v>
+        <v>1.336608311205699e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>1.171468544266931e-07</v>
+        <v>1.171468544266948e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>1.042992275833864e-07</v>
+        <v>1.042992275834043e-07</v>
       </c>
     </row>
     <row r="6">
@@ -5826,34 +5826,34 @@
         <v>5.132043344480961e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>5.127313270455862e-08</v>
+        <v>5.12731327045586e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.093587803173466e-07</v>
+        <v>1.093587803173465e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>5.117502469071258e-08</v>
+        <v>5.117502469071256e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>5.192965994429353e-08</v>
+        <v>5.192965994429351e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>9.028814246361929e-08</v>
+        <v>9.028814246361956e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>6.456592340905936e-08</v>
+        <v>6.456592340905939e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>5.19909818844298e-08</v>
+        <v>5.199098188442971e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>6.340472350766228e-08</v>
+        <v>6.340472350766236e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>5.32846885426773e-08</v>
+        <v>5.328468854267737e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>5.700325199089092e-08</v>
+        <v>5.700325199089087e-08</v>
       </c>
     </row>
     <row r="7">
@@ -5863,37 +5863,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.860873642699556e-08</v>
+        <v>5.860873642699555e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>5.92873382933063e-08</v>
+        <v>5.928733829330631e-08</v>
       </c>
       <c r="D7" t="n">
         <v>1.154282531573875e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>5.926686890964259e-08</v>
+        <v>5.926686890964258e-08</v>
       </c>
       <c r="F7" t="n">
         <v>5.926686890964258e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>8.879061531588732e-08</v>
+        <v>8.879061531588761e-08</v>
       </c>
       <c r="H7" t="n">
         <v>6.23329775461703e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>5.92792848666156e-08</v>
+        <v>5.927928486661559e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>6.154468323143326e-08</v>
+        <v>6.154468323143329e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>6.113795686340048e-08</v>
+        <v>6.113795686340063e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>6.426261735099076e-08</v>
+        <v>6.42626173509908e-08</v>
       </c>
     </row>
     <row r="8">
@@ -5903,37 +5903,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.836694706242375e-08</v>
+        <v>6.836694706242377e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>8.251079306361302e-08</v>
+        <v>8.251079306361307e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>1.414635441620978e-07</v>
+        <v>1.414635441620979e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>7.882523383900091e-08</v>
+        <v>7.882523383900076e-08</v>
       </c>
       <c r="F8" t="n">
         <v>6.946139769250664e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>1.120293777281128e-07</v>
+        <v>1.120293777281127e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>8.557173995838726e-08</v>
+        <v>8.557173995838733e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>8.251804727884081e-08</v>
+        <v>8.251804727884082e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>8.478609495659253e-08</v>
+        <v>8.478609495659261e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>7.064575932835987e-08</v>
+        <v>7.064575932836002e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>1.015829433186154e-07</v>
+        <v>1.015829433186155e-07</v>
       </c>
     </row>
     <row r="9">
@@ -5943,37 +5943,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7.746609277400729e-08</v>
+        <v>7.74660927740075e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>8.6528543428681e-08</v>
+        <v>8.652854342868108e-08</v>
       </c>
       <c r="D9" t="n">
         <v>1.426707309236685e-07</v>
       </c>
       <c r="E9" t="n">
-        <v>9.620335861069896e-08</v>
+        <v>9.620335861069907e-08</v>
       </c>
       <c r="F9" t="n">
         <v>8.652855220565383e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>1.160318204512621e-07</v>
+        <v>1.160318204512623e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>8.957418268154505e-08</v>
+        <v>8.957418268154519e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>8.65204900019903e-08</v>
+        <v>8.652049000199036e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>8.878588836680795e-08</v>
+        <v>8.878588836680808e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>8.352153729148144e-08</v>
+        <v>8.352153729148167e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>9.150382248636551e-08</v>
+        <v>9.150382248636562e-08</v>
       </c>
     </row>
   </sheetData>
@@ -6062,19 +6062,19 @@
         <v>1.601413325969012e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.810274863135564e-08</v>
+        <v>1.810274863135565e-08</v>
       </c>
       <c r="D2" t="n">
         <v>1.75679359214772e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.918158459295929e-08</v>
+        <v>1.918158459295928e-08</v>
       </c>
       <c r="F2" t="n">
         <v>1.545681294106264e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.673261487194388e-08</v>
+        <v>1.673261487194387e-08</v>
       </c>
       <c r="H2" t="n">
         <v>1.608542439650256e-08</v>
@@ -6083,10 +6083,10 @@
         <v>1.600997011122311e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>2.344725129386684e-08</v>
+        <v>2.34472512938669e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>2.678548582328004e-08</v>
+        <v>2.678548582328006e-08</v>
       </c>
       <c r="L2" t="n">
         <v>1.848386471389719e-08</v>
@@ -6099,37 +6099,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.322275320853113e-08</v>
+        <v>1.322275320853111e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.668393824567558e-08</v>
+        <v>1.66839382456756e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>2.422491267067319e-08</v>
+        <v>2.42249126706732e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.844055577777086e-08</v>
+        <v>1.84405557777709e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.229173723043077e-08</v>
+        <v>1.229173723043074e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.832656524011554e-08</v>
+        <v>1.83265652401155e-08</v>
       </c>
       <c r="H3" t="n">
         <v>1.402963178593348e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.31892471996405e-08</v>
+        <v>1.318924719964047e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>2.639696856389365e-08</v>
+        <v>2.639696856389375e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>3.183472005195716e-08</v>
+        <v>3.183472005195714e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>3.083166641279962e-08</v>
+        <v>3.083166641279963e-08</v>
       </c>
     </row>
     <row r="4">
@@ -6139,37 +6139,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.038288483321618e-08</v>
+        <v>5.038288483321616e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>4.937627805755003e-08</v>
+        <v>4.937627805755005e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>6.793380068263975e-08</v>
+        <v>6.793380068263979e-08</v>
       </c>
       <c r="E4" t="n">
         <v>4.955360299478019e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>4.955360299478019e-08</v>
+        <v>4.95536029947802e-08</v>
       </c>
       <c r="G4" t="n">
         <v>5.843321662536785e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>5.172644639027772e-08</v>
+        <v>5.172644639027771e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>4.989417237455132e-08</v>
+        <v>4.989417237455134e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>5.223640092686616e-08</v>
+        <v>5.223640092686617e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>5.211034967267508e-08</v>
+        <v>5.211034967267506e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>7.812570312765975e-08</v>
+        <v>7.812570312765974e-08</v>
       </c>
     </row>
     <row r="5">
@@ -6179,37 +6179,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.071432048563745e-08</v>
+        <v>8.071432048563675e-08</v>
       </c>
       <c r="C5" t="n">
         <v>7.727707045033683e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>3.639534305145985e-07</v>
+        <v>3.639534305145983e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>7.727708438946591e-08</v>
+        <v>7.727708438946588e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>7.727708438946593e-08</v>
+        <v>7.727708438946588e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>2.207349903033787e-07</v>
+        <v>2.20734990303379e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>1.092346612892197e-07</v>
+        <v>1.092346612892196e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>7.727378091072849e-08</v>
+        <v>7.727378091072851e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>1.181040145949858e-07</v>
+        <v>1.181040145949857e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>1.093856120673316e-07</v>
+        <v>1.093856120673313e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>6.419524863487127e-07</v>
+        <v>6.419524863487121e-07</v>
       </c>
     </row>
     <row r="6">
@@ -6219,37 +6219,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.668356532883664e-08</v>
+        <v>5.668356532883659e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>4.821123516705647e-08</v>
+        <v>4.82112351670565e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>7.455466049710179e-08</v>
+        <v>7.45546604971018e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>4.813591350298838e-08</v>
+        <v>4.81359135029884e-08</v>
       </c>
       <c r="F6" t="n">
         <v>4.849622027653216e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>6.473389712098833e-08</v>
+        <v>6.473389712098829e-08</v>
       </c>
       <c r="H6" t="n">
         <v>5.035765422597209e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>5.619485287017175e-08</v>
+        <v>5.619485287017174e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>5.878987410534709e-08</v>
+        <v>5.878987410534711e-08</v>
       </c>
       <c r="K6" t="n">
         <v>5.058233807088086e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>7.692224803457539e-08</v>
+        <v>7.692224803457537e-08</v>
       </c>
     </row>
     <row r="7">
@@ -6262,31 +6262,31 @@
         <v>5.611181230888994e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>5.562638938983343e-08</v>
+        <v>5.56263893898334e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>7.366139516955629e-08</v>
+        <v>7.366139516955632e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>5.562031217931862e-08</v>
+        <v>5.562031217931863e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>5.562031217931863e-08</v>
+        <v>5.562031217931864e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>6.416214410104163e-08</v>
+        <v>6.416214410104164e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>5.745537386595145e-08</v>
+        <v>5.745537386595146e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>5.562309985022507e-08</v>
+        <v>5.562309985022506e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>5.796532840253991e-08</v>
+        <v>5.796532840253995e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>5.783927714834878e-08</v>
+        <v>5.783927714834882e-08</v>
       </c>
       <c r="L7" t="n">
         <v>8.38546306033336e-08</v>
@@ -6299,37 +6299,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.541932169906676e-08</v>
+        <v>6.541932169906672e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>7.743435748320416e-08</v>
+        <v>7.743435748320421e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>9.806471741587081e-08</v>
+        <v>9.806471741587085e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>7.401492589235704e-08</v>
+        <v>7.401492589235703e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>6.532737119518332e-08</v>
+        <v>6.532737119518336e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>8.597174354278657e-08</v>
+        <v>8.597174354278654e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>7.926497330769439e-08</v>
+        <v>7.926497330769447e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>7.743269929196999e-08</v>
+        <v>7.743269929196995e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>7.977738486239396e-08</v>
+        <v>7.977738486239409e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>6.691455379681097e-08</v>
+        <v>6.691455379681092e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>1.187237085118193e-07</v>
+        <v>1.187237085118194e-07</v>
       </c>
     </row>
     <row r="9">
@@ -6345,31 +6345,31 @@
         <v>8.084295326691363e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>9.887930461391844e-08</v>
+        <v>9.887930461391847e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>8.973930482654863e-08</v>
+        <v>8.973930482654855e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>8.084296914355962e-08</v>
+        <v>8.084296914355963e-08</v>
       </c>
       <c r="G9" t="n">
         <v>8.93787079781218e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>8.267193774303166e-08</v>
+        <v>8.267193774303165e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>8.083966372730529e-08</v>
+        <v>8.083966372730527e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>8.318189227962016e-08</v>
+        <v>8.318189227962011e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>7.858907016738739e-08</v>
+        <v>7.858907016738736e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>1.090711944804138e-07</v>
+        <v>1.090711944804137e-07</v>
       </c>
     </row>
   </sheetData>
@@ -6455,37 +6455,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.511060512875634e-08</v>
+        <v>1.511060512875632e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.731776829980244e-08</v>
+        <v>1.731776829980243e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.518497407937519e-08</v>
+        <v>1.518497407937517e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.835607753897256e-08</v>
+        <v>1.835607753897255e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.472882050850698e-08</v>
+        <v>1.472882050850696e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.519621633209598e-08</v>
+        <v>1.519621633209597e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.499479768281173e-08</v>
+        <v>1.499479768281171e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.511916862066261e-08</v>
+        <v>1.511916862066259e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>2.259881871262934e-08</v>
+        <v>2.259881871262932e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>2.601953097768249e-08</v>
+        <v>2.601953097768248e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.496152103137656e-08</v>
+        <v>1.496152103137655e-08</v>
       </c>
     </row>
     <row r="3">
@@ -6498,31 +6498,31 @@
         <v>1.288277202434261e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.659822419758541e-08</v>
+        <v>1.659822419758539e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.340495362427434e-08</v>
+        <v>1.340495362427433e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.829594458402169e-08</v>
+        <v>1.829594458402171e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.230809633822364e-08</v>
+        <v>1.230809633822363e-08</v>
       </c>
       <c r="G3" t="n">
         <v>1.348898714132725e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.230510560903863e-08</v>
+        <v>1.230510560903862e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.293684049640318e-08</v>
+        <v>1.293684049640317e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>2.667130244954871e-08</v>
+        <v>2.667130244954866e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>3.181282580729323e-08</v>
+        <v>3.181282580729322e-08</v>
       </c>
       <c r="L3" t="n">
         <v>1.190494878884178e-08</v>
@@ -6538,31 +6538,31 @@
         <v>5.026599594819934e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>4.980536710163577e-08</v>
+        <v>4.980536710163576e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>5.110602745684682e-08</v>
+        <v>5.110602745684683e-08</v>
       </c>
       <c r="E4" t="n">
         <v>4.994673873173851e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>4.994673873173853e-08</v>
+        <v>4.994673873173851e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>5.117704066631085e-08</v>
+        <v>5.117704066631079e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>4.940261162136135e-08</v>
+        <v>4.940261162136136e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>4.998322869503799e-08</v>
+        <v>4.998322869503797e-08</v>
       </c>
       <c r="J4" t="n">
         <v>5.321093842323104e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>5.218874785466166e-08</v>
+        <v>5.218874785466167e-08</v>
       </c>
       <c r="L4" t="n">
         <v>4.872366782502136e-08</v>
@@ -6575,37 +6575,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.994814431890248e-08</v>
+        <v>8.994814431890253e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>8.762774904805641e-08</v>
+        <v>8.762774904805636e-08</v>
       </c>
       <c r="D5" t="n">
         <v>1.003522234028513e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>8.76277551852491e-08</v>
+        <v>8.7627755185249e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>8.76277551852491e-08</v>
+        <v>8.7627755185249e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>1.045099130611403e-07</v>
+        <v>1.045099130611396e-07</v>
       </c>
       <c r="H5" t="n">
         <v>7.842714524925688e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>8.762617832261054e-08</v>
+        <v>8.762617832261053e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>1.407192026429832e-07</v>
+        <v>1.407192026429831e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>1.182373114996303e-07</v>
+        <v>1.182373114996304e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>9.192364932345316e-08</v>
+        <v>9.192364932345321e-08</v>
       </c>
     </row>
     <row r="6">
@@ -6618,28 +6618,28 @@
         <v>5.533995905920246e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>4.850203622193701e-08</v>
+        <v>4.850203622193695e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>4.976216191408965e-08</v>
+        <v>4.976216191408964e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>4.842788145405034e-08</v>
+        <v>4.842788145405032e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>4.859767150088785e-08</v>
+        <v>4.859767150088783e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>5.625100377731383e-08</v>
+        <v>5.625100377731388e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>5.510288829842838e-08</v>
+        <v>5.510288829842839e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>5.505719180604114e-08</v>
+        <v>5.50571918060411e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>5.198177798841888e-08</v>
+        <v>5.198177798841887e-08</v>
       </c>
       <c r="K6" t="n">
         <v>5.080861028282545e-08</v>
@@ -6658,34 +6658,34 @@
         <v>5.5090883926768e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>5.48096873990525e-08</v>
+        <v>5.480968739905248e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>5.592966571523947e-08</v>
+        <v>5.592966571523945e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>5.480716197442217e-08</v>
+        <v>5.480716197442214e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>5.480716197442217e-08</v>
+        <v>5.480716197442214e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>5.600192864487952e-08</v>
+        <v>5.600192864487943e-08</v>
       </c>
       <c r="H7" t="n">
         <v>5.422749959993003e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>5.480811667360664e-08</v>
+        <v>5.480811667360662e-08</v>
       </c>
       <c r="J7" t="n">
         <v>5.80358264017997e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>5.701363583323032e-08</v>
+        <v>5.701363583323033e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>5.354855580359002e-08</v>
+        <v>5.354855580359001e-08</v>
       </c>
     </row>
     <row r="8">
@@ -6698,25 +6698,25 @@
         <v>6.329081561658876e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>7.392601004398111e-08</v>
+        <v>7.392601004398113e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>7.730919278939765e-08</v>
+        <v>7.730919278939764e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>7.09403251394014e-08</v>
+        <v>7.094032513940136e-08</v>
       </c>
       <c r="F8" t="n">
         <v>6.335485048579407e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>7.511690117555443e-08</v>
+        <v>7.511690117555439e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>7.334247213060328e-08</v>
+        <v>7.334247213060327e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>7.392308920428155e-08</v>
+        <v>7.392308920428153e-08</v>
       </c>
       <c r="J8" t="n">
         <v>7.71529440501412e-08</v>
@@ -6735,37 +6735,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.8006187764839e-08</v>
+        <v>6.800618776483896e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>7.37798530687295e-08</v>
+        <v>7.377985306872942e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>7.490108973372478e-08</v>
+        <v>7.490108973372472e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>8.07670521991038e-08</v>
+        <v>8.076705219910375e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>7.377986162449523e-08</v>
+        <v>7.37798616244952e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>7.497209431455651e-08</v>
+        <v>7.497209431455645e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>7.31976652696071e-08</v>
+        <v>7.319766526960702e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>7.377828234328368e-08</v>
+        <v>7.377828234328362e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>7.700599207147676e-08</v>
+        <v>7.700599207147668e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>7.247559440756654e-08</v>
+        <v>7.247559440756649e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>7.251872147326704e-08</v>
+        <v>7.251872147326698e-08</v>
       </c>
     </row>
   </sheetData>
@@ -6851,34 +6851,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.524126028166433e-08</v>
+        <v>1.524126028166437e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.75679663473399e-08</v>
+        <v>1.756796634733989e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.509686469952392e-08</v>
+        <v>1.509686469952398e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.856153453752298e-08</v>
+        <v>1.856153453752302e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.50700530914394e-08</v>
+        <v>1.507005309143939e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.515904054591543e-08</v>
+        <v>1.515904054591545e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.498966858286626e-08</v>
+        <v>1.498966858286625e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.534718075760714e-08</v>
+        <v>1.534718075760718e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>2.257752138688037e-08</v>
+        <v>2.257752138688035e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>2.595055381381861e-08</v>
+        <v>2.595055381381866e-08</v>
       </c>
       <c r="L2" t="n">
         <v>1.50168515595039e-08</v>
@@ -6891,34 +6891,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.376036065617437e-08</v>
+        <v>1.376036065617439e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.820186298266549e-08</v>
+        <v>1.82018629826655e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.273368146341514e-08</v>
+        <v>1.273368146341515e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.982758843408075e-08</v>
+        <v>1.982758843408076e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.40638633279752e-08</v>
+        <v>1.406386332797524e-08</v>
       </c>
       <c r="G3" t="n">
         <v>1.317708194379005e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.221539570077586e-08</v>
+        <v>1.221539570077587e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.450571590201653e-08</v>
+        <v>1.450571590201658e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>2.716365660674369e-08</v>
+        <v>2.71636566067437e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>3.130502900099243e-08</v>
+        <v>3.130502900099245e-08</v>
       </c>
       <c r="L3" t="n">
         <v>1.22415509488885e-08</v>
@@ -6931,7 +6931,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.182140932460057e-08</v>
+        <v>5.182140932460056e-08</v>
       </c>
       <c r="C4" t="n">
         <v>5.265047227199603e-08</v>
@@ -6940,28 +6940,28 @@
         <v>5.019039479907523e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>5.278322271283738e-08</v>
+        <v>5.27832227128374e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>5.278322271283738e-08</v>
+        <v>5.27832227128374e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>5.084146302726169e-08</v>
+        <v>5.08414630272617e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>4.941660257649306e-08</v>
+        <v>4.941660257649305e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>5.267011849840301e-08</v>
+        <v>5.267011849840303e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>5.447767962565409e-08</v>
+        <v>5.447767962565406e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>5.155762368432317e-08</v>
+        <v>5.155762368432315e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>4.941132410016064e-08</v>
+        <v>4.941132410016063e-08</v>
       </c>
     </row>
     <row r="5">
@@ -6974,10 +6974,10 @@
         <v>1.117926248801897e-07</v>
       </c>
       <c r="C5" t="n">
-        <v>1.271109527254199e-07</v>
+        <v>1.271109527254201e-07</v>
       </c>
       <c r="D5" t="n">
-        <v>8.495577784314237e-08</v>
+        <v>8.495577784314224e-08</v>
       </c>
       <c r="E5" t="n">
         <v>1.271109546736468e-07</v>
@@ -6986,16 +6986,16 @@
         <v>1.271109546736468e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>9.714373445455897e-08</v>
+        <v>9.714373445455956e-08</v>
       </c>
       <c r="H5" t="n">
         <v>7.610356011768757e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>1.271100858316801e-07</v>
+        <v>1.271100858316802e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>1.604653597216804e-07</v>
+        <v>1.604653597216807e-07</v>
       </c>
       <c r="K5" t="n">
         <v>1.046102708383963e-07</v>
@@ -7011,37 +7011,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.052700141131705e-08</v>
+        <v>5.052700141131704e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>5.136467355308927e-08</v>
+        <v>5.136467355308928e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>4.885924138248337e-08</v>
+        <v>4.885924138248336e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>5.128249486462813e-08</v>
+        <v>5.128249486462818e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>5.138238082158745e-08</v>
+        <v>5.138238082158744e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>4.954705511397821e-08</v>
+        <v>4.954705511397818e-08</v>
       </c>
       <c r="H6" t="n">
         <v>5.510521286908874e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>5.13757105851195e-08</v>
+        <v>5.137571058511949e-08</v>
       </c>
       <c r="J6" t="n">
         <v>5.33357721961856e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>5.022687414552814e-08</v>
+        <v>5.022687414552811e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>4.809917017194248e-08</v>
+        <v>4.809917017194247e-08</v>
       </c>
     </row>
     <row r="7">
@@ -7051,13 +7051,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.664115783233784e-08</v>
+        <v>5.664115783233782e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>5.749073389988032e-08</v>
+        <v>5.749073389988034e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>5.500888668392022e-08</v>
+        <v>5.500888668392021e-08</v>
       </c>
       <c r="E7" t="n">
         <v>5.749007341902345e-08</v>
@@ -7066,19 +7066,19 @@
         <v>5.749007341902345e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>5.566121153499898e-08</v>
+        <v>5.566121153499897e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>5.423635108423032e-08</v>
+        <v>5.423635108423031e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>5.748986700614032e-08</v>
+        <v>5.74898670061403e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>5.929742813339134e-08</v>
+        <v>5.929742813339133e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>5.637737219206044e-08</v>
+        <v>5.637737219206047e-08</v>
       </c>
       <c r="L7" t="n">
         <v>5.423107260789789e-08</v>
@@ -7091,37 +7091,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.478053594972026e-08</v>
+        <v>6.478053594972027e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>7.650260775622447e-08</v>
+        <v>7.650260775622446e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>7.627271159082931e-08</v>
+        <v>7.627271159082928e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>7.352922042258813e-08</v>
+        <v>7.352922042258815e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>6.597501029533608e-08</v>
+        <v>6.597501029533605e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>7.466994763413875e-08</v>
+        <v>7.466994763413872e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>7.324508718336926e-08</v>
+        <v>7.324508718336924e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>7.64986031052801e-08</v>
+        <v>7.649860310527994e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>7.830830037219499e-08</v>
+        <v>7.830830037219502e-08</v>
       </c>
       <c r="K8" t="n">
         <v>6.431484640418795e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>8.459376200013985e-08</v>
+        <v>8.459376200013983e-08</v>
       </c>
     </row>
     <row r="9">
@@ -7134,34 +7134,34 @@
         <v>6.856127863586001e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>7.518735698743193e-08</v>
+        <v>7.518735698743195e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>7.270677442104613e-08</v>
+        <v>7.270677442104617e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>8.18533306736335e-08</v>
+        <v>8.185333067363355e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>7.518736159796849e-08</v>
+        <v>7.518736159796848e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>7.335783462255055e-08</v>
+        <v>7.335783462255062e-08</v>
       </c>
       <c r="H9" t="n">
         <v>7.193297417178192e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>7.518649009369188e-08</v>
+        <v>7.518649009369193e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>7.699405122094291e-08</v>
+        <v>7.699405122094299e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>7.059128125627382e-08</v>
+        <v>7.059128125627383e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>7.192769569544947e-08</v>
+        <v>7.192769569544951e-08</v>
       </c>
     </row>
   </sheetData>
@@ -7247,37 +7247,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.91267605605282e-08</v>
+        <v>1.912676056052818e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>2.084032057933529e-08</v>
+        <v>2.08403205793353e-08</v>
       </c>
       <c r="D2" t="n">
         <v>2.516542131483575e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>2.201458663151153e-08</v>
+        <v>2.201458663151147e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.80712085747409e-08</v>
+        <v>1.807120857474087e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>2.166179878715465e-08</v>
+        <v>2.166179878715463e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.939276382274537e-08</v>
+        <v>1.939276382274536e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.909085835409939e-08</v>
+        <v>1.909085835409937e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>2.650581885074056e-08</v>
+        <v>2.650581885074053e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>2.965700509577339e-08</v>
+        <v>2.965700509577346e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.953093230795515e-08</v>
+        <v>1.953093230795512e-08</v>
       </c>
     </row>
     <row r="3">
@@ -7287,37 +7287,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.618131923894645e-08</v>
+        <v>1.618131923894644e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.887478222470499e-08</v>
+        <v>1.887478222470501e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>5.905106207279409e-08</v>
+        <v>5.905106207279416e-08</v>
       </c>
       <c r="E3" t="n">
         <v>2.076525463142002e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.425557081685705e-08</v>
+        <v>1.425557081685709e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>3.421527121312695e-08</v>
+        <v>3.421527121312698e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.855749030564199e-08</v>
+        <v>1.855749030564203e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.592314411138836e-08</v>
+        <v>1.592314411138833e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>2.90851304161495e-08</v>
+        <v>2.908513041614941e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>3.459463794012978e-08</v>
+        <v>3.459463794012968e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.939708648338125e-08</v>
+        <v>1.939708648338127e-08</v>
       </c>
     </row>
     <row r="4">
@@ -7327,37 +7327,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.297225752257065e-08</v>
+        <v>5.297225752257061e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>5.125327298169046e-08</v>
+        <v>5.125327298169047e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>1.211817086636661e-07</v>
+        <v>1.21181708663666e-07</v>
       </c>
       <c r="E4" t="n">
         <v>5.145521935899707e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>5.145521935899706e-08</v>
+        <v>5.145521935899707e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>8.152859202870279e-08</v>
+        <v>8.152859202870288e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>5.684072089640424e-08</v>
+        <v>5.684072089640436e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>5.203841083669045e-08</v>
+        <v>5.203841083669044e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>5.445006103534644e-08</v>
+        <v>5.445006103534642e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>5.510629427397487e-08</v>
+        <v>5.510629427397486e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>5.808702635402425e-08</v>
+        <v>5.808702635402421e-08</v>
       </c>
     </row>
     <row r="5">
@@ -7367,37 +7367,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.674692534539671e-08</v>
+        <v>9.674692534539667e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>8.748041006366626e-08</v>
+        <v>8.748041006366563e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>1.259375042652487e-06</v>
+        <v>1.259375042652489e-06</v>
       </c>
       <c r="E5" t="n">
-        <v>8.748042607279091e-08</v>
+        <v>8.748042607279043e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>8.748042607279091e-08</v>
+        <v>8.748042607279042e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>6.054161503642806e-07</v>
+        <v>6.054161503642808e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>1.745376177809207e-07</v>
+        <v>1.745376177809219e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>8.747231098081621e-08</v>
+        <v>8.747231098081574e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>1.277669752127101e-07</v>
+        <v>1.2776697521271e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>1.341439732436347e-07</v>
+        <v>1.341439732436348e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>1.6332523300582e-07</v>
+        <v>1.633252330058221e-07</v>
       </c>
     </row>
     <row r="6">
@@ -7413,31 +7413,31 @@
         <v>5.048657613759796e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.222127275866301e-07</v>
+        <v>1.222127275866302e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>5.039360144937847e-08</v>
+        <v>5.039360144937849e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>5.122528489947492e-08</v>
+        <v>5.122528489947493e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>9.013885325570811e-08</v>
+        <v>9.013885325570814e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>6.635570369365453e-08</v>
+        <v>6.635570369365464e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>6.064867206369574e-08</v>
+        <v>6.064867206369578e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>6.348840890358988e-08</v>
+        <v>6.348840890358986e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>5.379719171698772e-08</v>
+        <v>5.37971917169878e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>5.738660973355548e-08</v>
+        <v>5.738660973355549e-08</v>
       </c>
     </row>
     <row r="7">
@@ -7447,37 +7447,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.011434640665216e-08</v>
+        <v>6.01143464066522e-08</v>
       </c>
       <c r="C7" t="n">
         <v>5.918859880362212e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.283224611702661e-07</v>
+        <v>1.283224611702662e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>5.917279889010364e-08</v>
+        <v>5.917279889010368e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>5.917279889010364e-08</v>
+        <v>5.917279889010368e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>8.867068091278433e-08</v>
+        <v>8.86706809127844e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>6.398280978048584e-08</v>
+        <v>6.398280978048593e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>5.918049972077199e-08</v>
+        <v>5.9180499720772e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>6.159214991942798e-08</v>
+        <v>6.159214991942803e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>6.22483831580564e-08</v>
+        <v>6.224838315805644e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>6.522911523810578e-08</v>
+        <v>6.522911523810582e-08</v>
       </c>
     </row>
     <row r="8">
@@ -7487,34 +7487,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7.066475872582646e-08</v>
+        <v>7.066475872582649e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>8.420913744109634e-08</v>
+        <v>8.420913744109629e-08</v>
       </c>
       <c r="D8" t="n">
         <v>1.563575369647804e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>8.024953241783283e-08</v>
+        <v>8.024953241783289e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>7.018940415075956e-08</v>
+        <v>7.018940415075957e-08</v>
       </c>
       <c r="G8" t="n">
         <v>1.137017597868371e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>8.901388865453506e-08</v>
+        <v>8.901388865453522e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>8.421157859482464e-08</v>
+        <v>8.421157859482466e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>8.662607465799286e-08</v>
+        <v>8.66260746579929e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>7.25298096612238e-08</v>
+        <v>7.252980966122385e-08</v>
       </c>
       <c r="L8" t="n">
         <v>1.053864611819255e-07</v>
@@ -7527,37 +7527,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8.496795597644897e-08</v>
+        <v>8.496795597644901e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>9.43005662608981e-08</v>
+        <v>9.430056626089822e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>1.634357905604389e-07</v>
+        <v>1.63435790560439e-07</v>
       </c>
       <c r="E9" t="n">
-        <v>1.061385364340636e-07</v>
+        <v>1.061385364340637e-07</v>
       </c>
       <c r="F9" t="n">
-        <v>9.430058512814854e-08</v>
+        <v>9.430058512814856e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>1.237826483700604e-07</v>
+        <v>1.237826483700606e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>9.909477723776195e-08</v>
+        <v>9.909477723776199e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>9.429246717804803e-08</v>
+        <v>9.429246717804804e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>9.670411737670397e-08</v>
+        <v>9.670411737670405e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>9.14166285161548e-08</v>
+        <v>9.141662851615482e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>1.003410826953818e-07</v>
+        <v>1.003410826953819e-07</v>
       </c>
     </row>
   </sheetData>
@@ -7643,37 +7643,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.703928182584676e-08</v>
+        <v>1.703928182584675e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.909686021511866e-08</v>
+        <v>1.909686021511867e-08</v>
       </c>
       <c r="D2" t="n">
         <v>2.171287149086456e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>2.020398462993331e-08</v>
+        <v>2.020398462993333e-08</v>
       </c>
       <c r="F2" t="n">
         <v>1.64147953936445e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.833892615460684e-08</v>
+        <v>1.833892615460683e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.706722560772405e-08</v>
+        <v>1.706722560772403e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.71107401909975e-08</v>
+        <v>1.711074019099749e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>2.460009950650874e-08</v>
+        <v>2.460009950650877e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>2.751417592636773e-08</v>
+        <v>2.751417592636774e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>3.259508421139279e-08</v>
+        <v>3.259508421139278e-08</v>
       </c>
     </row>
     <row r="3">
@@ -7686,34 +7686,34 @@
         <v>1.399166182710736e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.78202539645857e-08</v>
+        <v>1.782025396458573e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>4.710294061522834e-08</v>
+        <v>4.710294061522835e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.961703759548267e-08</v>
+        <v>1.961703759548269e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.33618816497687e-08</v>
+        <v>1.336188164976871e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>2.322334097581365e-08</v>
+        <v>2.322334097581367e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.455256718162633e-08</v>
+        <v>1.455256718162635e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.449508839138677e-08</v>
+        <v>1.449508839138678e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>2.814825823476006e-08</v>
+        <v>2.814825823476012e-08</v>
       </c>
       <c r="K3" t="n">
         <v>3.158325328673899e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.242985200070334e-07</v>
+        <v>1.242985200070333e-07</v>
       </c>
     </row>
     <row r="4">
@@ -7723,37 +7723,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.050597871993366e-08</v>
+        <v>5.050597871993368e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>5.053919601907512e-08</v>
+        <v>5.053919601907513e-08</v>
       </c>
       <c r="D4" t="n">
         <v>1.032963239437753e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>5.069647941334016e-08</v>
+        <v>5.069647941334018e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>5.069647941334016e-08</v>
+        <v>5.069647941334017e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>6.512171223641323e-08</v>
+        <v>6.512171223641324e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>5.147453155407902e-08</v>
+        <v>5.147453155407905e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>5.087719309427698e-08</v>
+        <v>5.0877193094277e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>5.394967737387454e-08</v>
+        <v>5.394967737387457e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>5.113087770853785e-08</v>
+        <v>5.113087770853788e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>2.240778504191773e-07</v>
+        <v>2.240778504191771e-07</v>
       </c>
     </row>
     <row r="5">
@@ -7763,37 +7763,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.576580564045526e-08</v>
+        <v>7.576580564045522e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>8.620279540922944e-08</v>
+        <v>8.620279540922952e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>8.828149039298488e-07</v>
+        <v>8.828149039298487e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>8.62028029956936e-08</v>
+        <v>8.620280299569363e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>8.62028029956936e-08</v>
+        <v>8.620280299569363e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>3.125683757580924e-07</v>
+        <v>3.125683757580918e-07</v>
       </c>
       <c r="H5" t="n">
         <v>9.638256692936288e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>8.619822640620053e-08</v>
+        <v>8.619822640620055e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>1.384502327099093e-07</v>
+        <v>1.384502327099091e-07</v>
       </c>
       <c r="K5" t="n">
         <v>8.543903187372844e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>3.376787883442586e-06</v>
+        <v>3.376787883442579e-06</v>
       </c>
     </row>
     <row r="6">
@@ -7803,37 +7803,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.796333779972395e-08</v>
+        <v>5.796333779972397e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>4.942187370488377e-08</v>
+        <v>4.942187370488372e-08</v>
       </c>
       <c r="D6" t="n">
         <v>1.036495086575308e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>4.933972735012245e-08</v>
+        <v>4.933972735012246e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>4.977831259471581e-08</v>
+        <v>4.977831259471583e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>7.257907131620352e-08</v>
+        <v>7.257907131620347e-08</v>
       </c>
       <c r="H6" t="n">
         <v>5.95782035467242e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>5.833455217406729e-08</v>
+        <v>5.83345521740673e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>5.306509731980982e-08</v>
+        <v>5.306509731980984e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>4.974836712362387e-08</v>
+        <v>4.974836712362386e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>2.239956860126802e-07</v>
+        <v>2.239956860126801e-07</v>
       </c>
     </row>
     <row r="7">
@@ -7843,37 +7843,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.615399955543819e-08</v>
+        <v>5.61539995554382e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>5.652978293281046e-08</v>
+        <v>5.652978293281047e-08</v>
       </c>
       <c r="D7" t="n">
         <v>1.089430958742363e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>5.652089370138837e-08</v>
+        <v>5.65208937013884e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>5.652089370138837e-08</v>
+        <v>5.652089370138841e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>7.07697330719178e-08</v>
+        <v>7.076973307191774e-08</v>
       </c>
       <c r="H7" t="n">
         <v>5.712255238958361e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>5.652521392978156e-08</v>
+        <v>5.652521392978158e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>5.959769820937908e-08</v>
+        <v>5.95976982093791e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>5.677889854404242e-08</v>
+        <v>5.677889854404241e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>2.297258712546818e-07</v>
+        <v>2.297258712546817e-07</v>
       </c>
     </row>
     <row r="8">
@@ -7883,37 +7883,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.523736667725781e-08</v>
+        <v>6.523736667725787e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>7.778241576891959e-08</v>
+        <v>7.778241576891971e-08</v>
       </c>
       <c r="D8" t="n">
         <v>1.327257766713895e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>7.445310601875048e-08</v>
+        <v>7.44531060187506e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>6.599448458796323e-08</v>
+        <v>6.599448458796333e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>9.202685715366379e-08</v>
+        <v>9.202685715366389e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>7.837967647132584e-08</v>
+        <v>7.837967647132596e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>7.778233801152756e-08</v>
+        <v>7.778233801152769e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>8.085721478220732e-08</v>
+        <v>8.085721478220743e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>6.563613187994811e-08</v>
+        <v>6.563613187994815e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>2.636995024340078e-07</v>
+        <v>2.636995024340077e-07</v>
       </c>
     </row>
     <row r="9">
@@ -7926,34 +7926,34 @@
         <v>7.284964852093432e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>8.062930601267254e-08</v>
+        <v>8.062930601267252e-08</v>
       </c>
       <c r="D9" t="n">
         <v>1.330438799564725e-07</v>
       </c>
       <c r="E9" t="n">
-        <v>8.917323704556041e-08</v>
+        <v>8.917323704556038e-08</v>
       </c>
       <c r="F9" t="n">
         <v>8.062931261529983e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>9.486925615177984e-08</v>
+        <v>9.48692561517798e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>8.122207546944564e-08</v>
+        <v>8.122207546944561e-08</v>
       </c>
       <c r="I9" t="n">
         <v>8.062473700964358e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>8.36972212892411e-08</v>
+        <v>8.369722128924106e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>7.658859297287363e-08</v>
+        <v>7.658859297287352e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>2.538253943345439e-07</v>
+        <v>2.538253943345438e-07</v>
       </c>
     </row>
   </sheetData>
